--- a/content-export/국문영문글정리.xlsx
+++ b/content-export/국문영문글정리.xlsx
@@ -770,7 +770,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -806,7 +805,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -1890,10 +1888,15 @@
         </is>
       </c>
       <c r="G4" s="7" t="n"/>
-      <c r="H4" s="8" t="n"/>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Global Center (HQ)</t>
+        </is>
+      </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 2 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J4" s="9" t="inlineStr">
@@ -2117,8 +2120,16 @@
         </is>
       </c>
       <c r="G10" s="7" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="5" t="n"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Sihwa R&amp;D Center</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/section[2]/div[1]/div[2]/button[2]|text</t>
@@ -2152,8 +2163,16 @@
         </is>
       </c>
       <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="5" t="n"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Hwaseong Factory</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/section[2]/div[1]/div[2]/button[3]|text</t>
@@ -2557,10 +2576,16 @@
         </is>
       </c>
       <c r="G9" s="7" t="n"/>
-      <c r="H9" s="8" t="n"/>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Liabilities
+Equity</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 2 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
@@ -3788,10 +3813,15 @@
         </is>
       </c>
       <c r="G38" s="7" t="n"/>
-      <c r="H38" s="8" t="n"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 1 General Provisions</t>
+        </is>
+      </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 2 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
@@ -3827,10 +3857,15 @@
         </is>
       </c>
       <c r="G39" s="7" t="n"/>
-      <c r="H39" s="8" t="n"/>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 2 Management of Accounting Information</t>
+        </is>
+      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 2 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
@@ -3866,10 +3901,15 @@
         </is>
       </c>
       <c r="G40" s="7" t="n"/>
-      <c r="H40" s="8" t="n"/>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 3 Duties and Education of Executives and Employees Related to the Internal Accounting Management System, etc.</t>
+        </is>
+      </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 2 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J40" s="9" t="inlineStr">
@@ -3905,10 +3945,15 @@
         </is>
       </c>
       <c r="G41" s="7" t="n"/>
-      <c r="H41" s="8" t="n"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 5 Evaluation and Reporting of the Internal Accounting Management System</t>
+        </is>
+      </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 2 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
@@ -3944,10 +3989,15 @@
         </is>
       </c>
       <c r="G42" s="7" t="n"/>
-      <c r="H42" s="8" t="n"/>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 6 Measures in Case of Violation of Regulations, etc.</t>
+        </is>
+      </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 2 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
@@ -4022,10 +4072,15 @@
         </is>
       </c>
       <c r="G44" s="7" t="n"/>
-      <c r="H44" s="8" t="n"/>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Addenda</t>
+        </is>
+      </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 2 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
@@ -4061,8 +4116,16 @@
         </is>
       </c>
       <c r="G45" s="7" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="5" t="n"/>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Article 1 (Purpose)</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[1]|text</t>
@@ -4095,8 +4158,16 @@
         </is>
       </c>
       <c r="G46" s="7" t="n"/>
-      <c r="H46" s="8" t="n"/>
-      <c r="I46" s="5" t="n"/>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>The purpose of these regulations is to establish policies and procedures necessary for designing, operating, evaluating, and reporting the company's internal accounting management system (hereinafter referred to as the 'Internal Accounting Management System') in accordance with Article 8 of the Act on External Audit of Stock Companies, etc. (hereinafter referred to as the 'Act'), Article 9 of the Enforcement Decree of the same Act (hereinafter referred to as the 'Decree'), and Article 6 of the Regulations on External Audit and Accounting, etc. (hereinafter referred to as the 'External Audit Regulations'), thereby enhancing the reliability of financial statements by designing and operating a reasonable and effective internal accounting management system.</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/p[1]|text</t>
@@ -4171,8 +4242,16 @@
         </is>
       </c>
       <c r="G48" s="7" t="n"/>
-      <c r="H48" s="8" t="n"/>
-      <c r="I48" s="5" t="n"/>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Matters concerning the internal accounting management system shall be governed by these regulations unless otherwise provided for in laws or the articles of incorporation.</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[1]/li[1]|text</t>
@@ -4205,8 +4284,16 @@
         </is>
       </c>
       <c r="G49" s="7" t="n"/>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="5" t="n"/>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>These regulations shall apply to matters necessary for preparing and disclosing accounting information regarding consolidated financial statements.</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[1]/li[2]|text</t>
@@ -4239,8 +4326,16 @@
         </is>
       </c>
       <c r="G50" s="7" t="n"/>
-      <c r="H50" s="8" t="n"/>
-      <c r="I50" s="5" t="n"/>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Article 3 (Definition of Terms)</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[3]|text</t>
@@ -4273,8 +4368,16 @@
         </is>
       </c>
       <c r="G51" s="7" t="n"/>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="5" t="n"/>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>The definitions of terms used in these regulations are as follows:</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/p[2]|text</t>
@@ -4307,8 +4410,16 @@
         </is>
       </c>
       <c r="G52" s="7" t="n"/>
-      <c r="H52" s="8" t="n"/>
-      <c r="I52" s="5" t="n"/>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>'Internal Accounting Management System' refers to an internal control system designed and operated to provide reasonable assurance as to whether the company's financial statements have been prepared and disclosed in accordance with generally accepted accounting principles in order to achieve the objectives of internal accounting management, and refers to a process continuously executed by all members of the organization, including these regulations and the organization that manages and operates them.</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[2]/li[1]|text</t>
@@ -4341,8 +4452,16 @@
         </is>
       </c>
       <c r="G53" s="7" t="n"/>
-      <c r="H53" s="8" t="n"/>
-      <c r="I53" s="5" t="n"/>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>'Internal Accounting Manager' refers to a person designated by the representative director as the person responsible for the management and operation of the internal accounting management system in accordance with Article 8, Paragraph 3 of the Act.</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[2]/li[2]|text</t>
@@ -4375,8 +4494,16 @@
         </is>
       </c>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="8" t="n"/>
-      <c r="I54" s="5" t="n"/>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>'Internal Accounting Management System Evaluation' refers to a procedure for confirming whether the design and operation of the internal accounting management system are effective for a certain period, and includes the representative director's procedure for checking the effectiveness of the internal accounting management system and the auditor's (committee's) procedure for evaluating the actual status of the operation of the internal accounting management system.</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[2]/li[3]|text</t>
@@ -4409,8 +4536,16 @@
         </is>
       </c>
       <c r="G55" s="7" t="n"/>
-      <c r="H55" s="8" t="n"/>
-      <c r="I55" s="5" t="n"/>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>'Auditor' refers to an accounting firm in accordance with Article 2, Subparagraph 7, Item (a) of the Act.</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[2]/li[4]|text</t>
@@ -4443,8 +4578,16 @@
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="8" t="n"/>
-      <c r="I56" s="5" t="n"/>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Article 4 (General Principles of Accounting Information Processing)</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[4]|text</t>
@@ -4477,8 +4620,16 @@
         </is>
       </c>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="8" t="n"/>
-      <c r="I57" s="5" t="n"/>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>The company shall not prepare accounting information without following the internal accounting management system, nor shall it forge, alter, damage, or destroy accounting information prepared in accordance with the internal accounting management system.</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J57" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[3]/li[1]|text</t>
@@ -4511,8 +4662,16 @@
         </is>
       </c>
       <c r="G58" s="7" t="n"/>
-      <c r="H58" s="8" t="n"/>
-      <c r="I58" s="5" t="n"/>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>Accounting processing such as identification, measurement, classification, recording, and reporting of accounting information shall be in accordance with the accounting standards prescribed in Article 5, Paragraph 1 of the Act.</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[3]/li[2]|text</t>
@@ -4545,8 +4704,16 @@
         </is>
       </c>
       <c r="G59" s="7" t="n"/>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="5" t="n"/>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>Article 5 (Identification, Measurement, Classification, Recording, and Reporting of Accounting Information)</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[5]|text</t>
@@ -4579,8 +4746,16 @@
         </is>
       </c>
       <c r="G60" s="7" t="n"/>
-      <c r="H60" s="8" t="n"/>
-      <c r="I60" s="5" t="n"/>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>Matters concerning accounting processing methods and accounting records, such as identification, measurement, classification, and reporting of accounting information, shall be processed in accordance with the general principles of Article 4, but the following requirements must be met.</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[4]/li[1]|text</t>
@@ -4613,8 +4788,16 @@
         </is>
       </c>
       <c r="G61" s="7" t="n"/>
-      <c r="H61" s="8" t="n"/>
-      <c r="I61" s="5" t="n"/>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>Assets, liabilities, and capital recorded in the balance sheet must actually exist as of the end of the reporting period.</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[4]/li[1]/ol/li[1]|text</t>
@@ -4647,8 +4830,16 @@
         </is>
       </c>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="5" t="n"/>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>Assets shown in the balance sheet must be owned by the company, and liabilities must be debts that the company must repay.</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[4]/li[1]/ol/li[2]|text</t>
@@ -4681,8 +4872,16 @@
         </is>
       </c>
       <c r="G63" s="7" t="n"/>
-      <c r="H63" s="8" t="n"/>
-      <c r="I63" s="5" t="n"/>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>Transactions or events must have actually occurred during the accounting period.</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J63" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[4]/li[1]/ol/li[3]|text</t>
@@ -4715,8 +4914,16 @@
         </is>
       </c>
       <c r="G64" s="7" t="n"/>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="5" t="n"/>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>There should be no assets, liabilities, transactions, or events that are not recorded in the financial statements, or items that are not disclosed.</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[4]/li[1]/ol/li[4]|text</t>
@@ -4749,8 +4956,16 @@
         </is>
       </c>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="8" t="n"/>
-      <c r="I65" s="5" t="n"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Assets, liabilities, capital, revenue, and expense items in the financial statements must be displayed in appropriate amounts in accordance with the general principles of Article 4.</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J65" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[4]/li[1]/ol/li[5]|text</t>
@@ -4783,8 +4998,16 @@
         </is>
       </c>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="8" t="n"/>
-      <c r="I66" s="5" t="n"/>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Accounting transactions or events must be recorded in the financial statements in appropriate amounts, and revenue or expenses must be allocated to appropriate accounting periods in accordance with the accrual principle.</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[4]/li[1]/ol/li[6]|text</t>
@@ -4817,8 +5040,16 @@
         </is>
       </c>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="8" t="n"/>
-      <c r="I67" s="5" t="n"/>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>Components of the financial statements must be classified, described, and disclosed in accordance with the general principles of Article 4.</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[4]/li[1]/ol/li[7]|text</t>
@@ -4851,8 +5082,16 @@
         </is>
       </c>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="8" t="n"/>
-      <c r="I68" s="5" t="n"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>All accounting information of the company shall be recorded in slips (including computer facilities) together with original documents, etc.</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[4]/li[2]|text</t>
@@ -4885,8 +5124,16 @@
         </is>
       </c>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="8" t="n"/>
-      <c r="I69" s="5" t="n"/>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>Accounting information prepared by the internal accounting management system shall be regularly reported to the internal accounting manager.</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J69" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[4]/li[3]|text</t>
@@ -4919,8 +5166,16 @@
         </is>
       </c>
       <c r="G70" s="7" t="n"/>
-      <c r="H70" s="8" t="n"/>
-      <c r="I70" s="5" t="n"/>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>Article 6 (Error Control, Correction, and Internal Verification of Accounting Information)</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[6]|text</t>
@@ -4953,8 +5208,16 @@
         </is>
       </c>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="8" t="n"/>
-      <c r="I71" s="5" t="n"/>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>The company and the auditor (committee) shall confirm whether the company's accounting information has been prepared in accordance with Articles 4 and 5 through the inspection under Article 17 and the evaluation under Article 18 to prevent errors from occurring in the process of processing accounting information.</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J71" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/p[3]|text</t>
@@ -4987,8 +5250,16 @@
         </is>
       </c>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="8" t="n"/>
-      <c r="I72" s="5" t="n"/>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>Article 7 (Management and Preservation of Accounting Records)</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[7]|text</t>
@@ -5021,8 +5292,16 @@
         </is>
       </c>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="8" t="n"/>
-      <c r="I73" s="5" t="n"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>All accounting records, such as slips, accounting auxiliary books, and accounting books, shall be managed and preserved in the following manner.</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/p[4]|text</t>
@@ -5055,8 +5334,16 @@
         </is>
       </c>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="8" t="n"/>
-      <c r="I74" s="5" t="n"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Accounting books consist of accounting auxiliary books such as subsidiary ledgers and general ledgers, and financial statements, and these books are managed physically and electronically.</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[5]/li[1]|text</t>
@@ -5089,8 +5376,16 @@
         </is>
       </c>
       <c r="G75" s="7" t="n"/>
-      <c r="H75" s="8" t="n"/>
-      <c r="I75" s="5" t="n"/>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>Physical accounting books are stored in a document warehouse designated by the accounting department, and management such as reading, transfer, and disposal is performed under the control of the accounting department. In addition, electronic accounting books are stored in a computer device by a computer operating system, and access and modification are allowed only to authorized persons, and the records are kept.</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[5]/li[2]|text</t>
@@ -5123,8 +5418,16 @@
         </is>
       </c>
       <c r="G76" s="7" t="n"/>
-      <c r="H76" s="8" t="n"/>
-      <c r="I76" s="5" t="n"/>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>The company shall not prepare accounting information without following the internal accounting management system, nor shall it forge, alter, damage, or destroy accounting information prepared by the internal accounting management system, or instruct such acts.</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[5]/li[3]|text</t>
@@ -5157,8 +5460,16 @@
         </is>
       </c>
       <c r="G77" s="7" t="n"/>
-      <c r="H77" s="8" t="n"/>
-      <c r="I77" s="5" t="n"/>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>The company shall establish and operate necessary procedures such as security procedures and access control procedures to prevent forgery, alteration, damage, and destruction of accounting information.</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J77" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[5]/li[4]|text</t>
@@ -5191,8 +5502,16 @@
         </is>
       </c>
       <c r="G78" s="7" t="n"/>
-      <c r="H78" s="8" t="n"/>
-      <c r="I78" s="5" t="n"/>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>Article 8 (Division of Duties and Responsibility)</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[8]|text</t>
@@ -5225,8 +5544,16 @@
         </is>
       </c>
       <c r="G79" s="7" t="n"/>
-      <c r="H79" s="8" t="n"/>
-      <c r="I79" s="5" t="n"/>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>The company shall appropriately divide the duties of executives and employees in the department in charge of preparing and disclosing reliable accounting information, and define their authority and responsibility.</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J79" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/p[5]|text</t>
@@ -5259,8 +5586,16 @@
         </is>
       </c>
       <c r="G80" s="7" t="n"/>
-      <c r="H80" s="8" t="n"/>
-      <c r="I80" s="5" t="n"/>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>Article 9 (Representative Director)</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[9]|text</t>
@@ -5293,8 +5628,16 @@
         </is>
       </c>
       <c r="G81" s="7" t="n"/>
-      <c r="H81" s="8" t="n"/>
-      <c r="I81" s="5" t="n"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>The representative director is responsible for the management and operation of the internal accounting management system and supports all necessary matters.</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J81" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[6]/li[1]|text</t>
@@ -5327,8 +5670,16 @@
         </is>
       </c>
       <c r="G82" s="7" t="n"/>
-      <c r="H82" s="8" t="n"/>
-      <c r="I82" s="5" t="n"/>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>The representative director designates an internal accounting manager in accordance with Article 10-2.</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[6]/li[2]|text</t>
@@ -5361,8 +5712,16 @@
         </is>
       </c>
       <c r="G83" s="7" t="n"/>
-      <c r="H83" s="8" t="n"/>
-      <c r="I83" s="5" t="n"/>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>The representative director checks and reports the actual status of the operation of the internal accounting management system in accordance with Article 17. However, if the representative director deems it necessary, reporting to the board of directors and the auditor (committee) may be delegated to the internal accounting manager.</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J83" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[6]/li[3]|text</t>
@@ -5395,8 +5754,16 @@
         </is>
       </c>
       <c r="G84" s="7" t="n"/>
-      <c r="H84" s="8" t="n"/>
-      <c r="I84" s="5" t="n"/>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>If the representative director intends to delegate reporting to the internal accounting manager in accordance with the proviso of Paragraph 3, he/she shall submit the reason in writing to the board of directors and the auditor (committee) before reporting.</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[6]/li[4]|text</t>
@@ -5429,8 +5796,16 @@
         </is>
       </c>
       <c r="G85" s="7" t="n"/>
-      <c r="H85" s="8" t="n"/>
-      <c r="I85" s="5" t="n"/>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>The representative director shall follow without delay if there is a request from the auditor (committee) or a request from the auditor in accordance with Article 11, Paragraph 4. However, if there is a special reason, the request may be refused, and in this case, the reason shall be submitted in writing to the auditor (committee) or the auditor.</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[6]/li[5]|text</t>
@@ -5463,8 +5838,16 @@
         </is>
       </c>
       <c r="G86" s="7" t="n"/>
-      <c r="H86" s="8" t="n"/>
-      <c r="I86" s="5" t="n"/>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>Article 10 (Internal Accounting Manager)</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[10]|text</t>
@@ -5497,8 +5880,16 @@
         </is>
       </c>
       <c r="G87" s="7" t="n"/>
-      <c r="H87" s="8" t="n"/>
-      <c r="I87" s="5" t="n"/>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>The internal accounting manager oversees the design and operation of the internal accounting management system and supports all necessary matters.</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J87" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[7]/li[1]|text</t>
@@ -5531,8 +5922,16 @@
         </is>
       </c>
       <c r="G88" s="7" t="n"/>
-      <c r="H88" s="8" t="n"/>
-      <c r="I88" s="5" t="n"/>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>The internal accounting manager checks the effectiveness of the design and operation of the internal accounting management system.</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[7]/li[2]|text</t>
@@ -5565,8 +5964,16 @@
         </is>
       </c>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="8" t="n"/>
-      <c r="I89" s="5" t="n"/>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>The internal accounting manager reports the actual status of the operation of the internal accounting management system to the board of directors and the auditor (committee) in accordance with the proviso of Article 9, Paragraph 3.</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[7]/li[3]|text</t>
@@ -5599,8 +6006,16 @@
         </is>
       </c>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="8" t="n"/>
-      <c r="I90" s="5" t="n"/>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>Article 10-2 (Qualifications and Appointment/Dismissal Procedures for Internal Accounting Manager)</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[11]|text</t>
@@ -5633,8 +6048,16 @@
         </is>
       </c>
       <c r="G91" s="7" t="n"/>
-      <c r="H91" s="8" t="n"/>
-      <c r="I91" s="5" t="n"/>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>The internal accounting manager must meet all of the following requirements.</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J91" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[8]/li[1]|text</t>
@@ -5667,8 +6090,16 @@
         </is>
       </c>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="8" t="n"/>
-      <c r="I92" s="5" t="n"/>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>Must have expertise in accounting or internal control</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[8]/li[1]/ol/li[1]|text</t>
@@ -5701,8 +6132,16 @@
         </is>
       </c>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="8" t="n"/>
-      <c r="I93" s="5" t="n"/>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>Must be a full-time director</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J93" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[8]/li[1]/ol/li[2]|text</t>
@@ -5735,8 +6174,16 @@
         </is>
       </c>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="8" t="n"/>
-      <c r="I94" s="5" t="n"/>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>Notwithstanding Paragraph 1, if there is no person who meets the requirements of Paragraph 1, Subparagraph 2, Subparagraph 2 shall be applied by regarding it as 'a person who executes the duties of the corresponding director'.</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[8]/li[2]|text</t>
@@ -5769,8 +6216,16 @@
         </is>
       </c>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="8" t="n"/>
-      <c r="I95" s="5" t="n"/>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>The representative director re-designates the internal accounting manager if he/she deems that the performance of duties related to the internal accounting management system is impossible or inappropriate due to reasons such as personnel appointments.</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J95" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[8]/li[3]|text</t>
@@ -5803,8 +6258,16 @@
         </is>
       </c>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="8" t="n"/>
-      <c r="I96" s="5" t="n"/>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>The appointment and dismissal procedures for the internal accounting manager shall follow relevant regulations such as personnel management regulations.</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[8]/li[4]|text</t>
@@ -5837,8 +6300,16 @@
         </is>
       </c>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="8" t="n"/>
-      <c r="I97" s="5" t="n"/>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>Article 11 (Auditor or Audit Committee)</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[12]|text</t>
@@ -5871,8 +6342,16 @@
         </is>
       </c>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="8" t="n"/>
-      <c r="I98" s="5" t="n"/>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>The auditor (committee) evaluates and reports the actual status of the operation of the internal accounting management system in accordance with Article 18.</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[9]/li[1]|text</t>
@@ -5905,8 +6384,16 @@
         </is>
       </c>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="8" t="n"/>
-      <c r="I99" s="5" t="n"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>If the auditor (committee) is notified of a violation of accounting processing from the auditor, he/she shall appoint an external expert to investigate the violation, etc., and request the representative director to correct the violation, etc., based on the results.</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J99" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[9]/li[2]|text</t>
@@ -5939,8 +6426,16 @@
         </is>
       </c>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="8" t="n"/>
-      <c r="I100" s="5" t="n"/>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>The auditor (committee) shall immediately submit the investigation results under Paragraph 1 and the company's corrective action results under Paragraph 2 to the Securities and Futures Commission and the auditor.</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[9]/li[3]|text</t>
@@ -5973,8 +6468,16 @@
         </is>
       </c>
       <c r="G101" s="7" t="n"/>
-      <c r="H101" s="8" t="n"/>
-      <c r="I101" s="5" t="n"/>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>The auditor (committee) may request the representative director in writing to provide necessary data, information, and expenses when performing the duties under Paragraphs 1 through 3.</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[9]/li[4]|text</t>
@@ -6007,8 +6510,16 @@
         </is>
       </c>
       <c r="G102" s="7" t="n"/>
-      <c r="H102" s="8" t="n"/>
-      <c r="I102" s="5" t="n"/>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>If the auditor (committee) finds a fraudulent act or a significant fact violating laws or the articles of incorporation regarding the performance of duties by a director, he/she shall notify the auditor.</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[9]/li[5]|text</t>
@@ -6041,8 +6552,16 @@
         </is>
       </c>
       <c r="G103" s="7" t="n"/>
-      <c r="H103" s="8" t="n"/>
-      <c r="I103" s="5" t="n"/>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>Article 12 (Establishment and Implementation of Education Plans, etc.)</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J103" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[13]|text</t>
@@ -6075,8 +6594,16 @@
         </is>
       </c>
       <c r="G104" s="7" t="n"/>
-      <c r="H104" s="8" t="n"/>
-      <c r="I104" s="5" t="n"/>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>The company shall establish education plans necessary for understanding matters prescribed in laws related to the internal accounting management system and these regulations for the representative director, internal accounting manager, auditor (committee), and executives and employees who prepare and disclose accounting information (hereinafter referred to as 'representative director, etc.'), and conduct necessary education.</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[10]/li[1]|text</t>
@@ -6109,8 +6636,16 @@
         </is>
       </c>
       <c r="G105" s="7" t="n"/>
-      <c r="H105" s="8" t="n"/>
-      <c r="I105" s="5" t="n"/>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>The company conducts performance evaluation of the education under Paragraph 1, and the results are reflected in the education plan for the next business year.</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J105" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[10]/li[2]|text</t>
@@ -6143,8 +6678,16 @@
         </is>
       </c>
       <c r="G106" s="7" t="n"/>
-      <c r="H106" s="8" t="n"/>
-      <c r="I106" s="5" t="n"/>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>The evaluation results of Paragraph 2 may be operated in connection with the compensation policy prescribed in Article 13, Paragraph 1.</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[10]/li[3]|text</t>
@@ -6177,8 +6720,16 @@
         </is>
       </c>
       <c r="G107" s="7" t="n"/>
-      <c r="H107" s="8" t="n"/>
-      <c r="I107" s="5" t="n"/>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>Article 13 (Linkage between Audit Evaluation Results and Compensation Policy)</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J107" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[14]|text</t>
@@ -6211,8 +6762,16 @@
         </is>
       </c>
       <c r="G108" s="7" t="n"/>
-      <c r="H108" s="8" t="n"/>
-      <c r="I108" s="5" t="n"/>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>The company reflects the evaluation results of the auditor (committee) in accordance with Article 18 in the personnel, compensation, and establishment of the operation plan for the internal accounting management system for the next business year of the representative director, etc.</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[11]/li[1]|text</t>
@@ -6245,8 +6804,16 @@
         </is>
       </c>
       <c r="G109" s="7" t="n"/>
-      <c r="H109" s="8" t="n"/>
-      <c r="I109" s="5" t="n"/>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>Detailed matters for applying Paragraph 1 shall follow separate regulations prescribed by the representative director.</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[11]/li[2]|text</t>
@@ -6279,8 +6846,16 @@
         </is>
       </c>
       <c r="G110" s="7" t="n"/>
-      <c r="H110" s="8" t="n"/>
-      <c r="I110" s="5" t="n"/>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>Article 16 (Standards for Evaluation and Reporting of the Internal Accounting Management System)</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J110" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[15]|text</t>
@@ -6313,8 +6888,16 @@
         </is>
       </c>
       <c r="G111" s="7" t="n"/>
-      <c r="H111" s="8" t="n"/>
-      <c r="I111" s="5" t="n"/>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>The representative director, internal accounting manager, and auditor (committee) shall perform the inspection under Article 17 and the evaluation under Article 18 in accordance with the 'Best Practice for Evaluation and Reporting of Internal Accounting Management System' (hereinafter referred to as the 'Best Practice') announced by the Steering Committee.</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J111" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/p[6]|text</t>
@@ -6347,8 +6930,16 @@
         </is>
       </c>
       <c r="G112" s="7" t="n"/>
-      <c r="H112" s="8" t="n"/>
-      <c r="I112" s="5" t="n"/>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
+          <t>Article 17 (Standards and Procedures for the Representative Director's Evaluation and Reporting of the Actual Status of Operation)</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[16]|text</t>
@@ -6381,8 +6972,16 @@
         </is>
       </c>
       <c r="G113" s="7" t="n"/>
-      <c r="H113" s="8" t="n"/>
-      <c r="I113" s="5" t="n"/>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>The company shall prepare objective performance indicators for checking the effectiveness of the internal accounting management system.</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J113" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[12]/li[1]|text</t>
@@ -6415,8 +7014,16 @@
         </is>
       </c>
       <c r="G114" s="7" t="n"/>
-      <c r="H114" s="8" t="n"/>
-      <c r="I114" s="5" t="n"/>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>The representative director shall perform an inspection on the effectiveness of the internal accounting management system every business year and report to the general meeting of shareholders, the board of directors, and the auditor (committee).</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[12]/li[2]|text</t>
@@ -6449,8 +7056,16 @@
         </is>
       </c>
       <c r="G115" s="7" t="n"/>
-      <c r="H115" s="8" t="n"/>
-      <c r="I115" s="5" t="n"/>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>When the representative director reports the inspection results to the board of directors and the auditor (committee) in accordance with Paragraph 2, he/she shall prepare it in a document (hereinafter referred to as the 'Internal Accounting Management System Operation Status Report') and report it in person.</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J115" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[12]/li[3]|text</t>
@@ -6483,8 +7098,16 @@
         </is>
       </c>
       <c r="G116" s="7" t="n"/>
-      <c r="H116" s="8" t="n"/>
-      <c r="I116" s="5" t="n"/>
+      <c r="H116" s="8" t="inlineStr">
+        <is>
+          <t>The detailed standards and procedures for inspection and reporting under Paragraph 2 shall be determined by considering each of the following subparagraphs.</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J116" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[12]/li[4]|text</t>
@@ -6517,8 +7140,16 @@
         </is>
       </c>
       <c r="G117" s="7" t="n"/>
-      <c r="H117" s="8" t="n"/>
-      <c r="I117" s="5" t="n"/>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>The internal accounting management system shall be designed and operated in a form suitable for the company.</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J117" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[12]/li[4]/ol/li[1]|text</t>
@@ -6551,8 +7182,16 @@
         </is>
       </c>
       <c r="G118" s="7" t="n"/>
-      <c r="H118" s="8" t="n"/>
-      <c r="I118" s="5" t="n"/>
+      <c r="H118" s="8" t="inlineStr">
+        <is>
+          <t>A constant and regular inspection system shall be established to prevent or discover and take measures in a timely manner against risks that hinder the preparation and disclosure of reliable accounting information.</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J118" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[12]/li[4]/ol/li[2]|text</t>
@@ -6585,8 +7224,16 @@
         </is>
       </c>
       <c r="G119" s="7" t="n"/>
-      <c r="H119" s="8" t="n"/>
-      <c r="I119" s="5" t="n"/>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>Performance indicators under Paragraph 1</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J119" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[12]/li[4]/ol/li[3]|text</t>
@@ -6619,8 +7266,16 @@
         </is>
       </c>
       <c r="G120" s="7" t="n"/>
-      <c r="H120" s="8" t="n"/>
-      <c r="I120" s="5" t="n"/>
+      <c r="H120" s="8" t="inlineStr">
+        <is>
+          <t>The representative director shall present an opinion on whether the company's internal accounting management system is effective by considering the performance indicators under Subparagraph 3 and the inspection results on whether there are vulnerabilities in the internal accounting management system.</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J120" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[12]/li[4]/ol/li[4]|text</t>
@@ -6653,8 +7308,16 @@
         </is>
       </c>
       <c r="G121" s="7" t="n"/>
-      <c r="H121" s="8" t="n"/>
-      <c r="I121" s="5" t="n"/>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>If an audit has been received for the internal accounting management system, the corrective action plan following the audit shall be reflected in the internal accounting management system corrective action plan.</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J121" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[12]/li[4]/ol/li[5]|text</t>
@@ -6687,8 +7350,16 @@
         </is>
       </c>
       <c r="G122" s="7" t="n"/>
-      <c r="H122" s="8" t="n"/>
-      <c r="I122" s="5" t="n"/>
+      <c r="H122" s="8" t="inlineStr">
+        <is>
+          <t>Establishment of operation status inspection plan</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J122" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[12]/li[4]/ol/li[6]|text</t>
@@ -6721,8 +7392,16 @@
         </is>
       </c>
       <c r="G123" s="7" t="n"/>
-      <c r="H123" s="8" t="n"/>
-      <c r="I123" s="5" t="n"/>
+      <c r="H123" s="8" t="inlineStr">
+        <is>
+          <t>Performance of operation status inspection</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J123" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[12]/li[4]/ol/li[7]|text</t>
@@ -6755,8 +7434,16 @@
         </is>
       </c>
       <c r="G124" s="7" t="n"/>
-      <c r="H124" s="8" t="n"/>
-      <c r="I124" s="5" t="n"/>
+      <c r="H124" s="8" t="inlineStr">
+        <is>
+          <t>Evaluation of deficiencies and establishment of improvement plans</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J124" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[12]/li[4]/ol/li[8]|text</t>
@@ -6789,8 +7476,16 @@
         </is>
       </c>
       <c r="G125" s="7" t="n"/>
-      <c r="H125" s="8" t="n"/>
-      <c r="I125" s="5" t="n"/>
+      <c r="H125" s="8" t="inlineStr">
+        <is>
+          <t>Reporting of operation status</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J125" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[12]/li[4]/ol/li[9]|text</t>
@@ -6823,8 +7518,16 @@
         </is>
       </c>
       <c r="G126" s="7" t="n"/>
-      <c r="H126" s="8" t="n"/>
-      <c r="I126" s="5" t="n"/>
+      <c r="H126" s="8" t="inlineStr">
+        <is>
+          <t>The inspection and reporting under Paragraph 2 shall follow the procedures of each of the following subparagraphs.</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J126" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[12]/li[5]|text</t>
@@ -6857,8 +7560,16 @@
         </is>
       </c>
       <c r="G127" s="7" t="n"/>
-      <c r="H127" s="8" t="n"/>
-      <c r="I127" s="5" t="n"/>
+      <c r="H127" s="8" t="inlineStr">
+        <is>
+          <t>Article 18 (Standards and Procedures for the Auditor's Evaluation and Reporting of the Actual Status of Operation)</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J127" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[17]|text</t>
@@ -6891,8 +7602,16 @@
         </is>
       </c>
       <c r="G128" s="7" t="n"/>
-      <c r="H128" s="8" t="n"/>
-      <c r="I128" s="5" t="n"/>
+      <c r="H128" s="8" t="inlineStr">
+        <is>
+          <t>The auditor (committee) evaluates the internal accounting management system operation status report under Article 17, Paragraph 3, and prepares the evaluation results in a document (hereinafter referred to as the 'Internal Accounting Management System Evaluation Report') and reports it to the board of directors every business year. In this case, if there is a corrective opinion on the management and operation of the internal accounting management system, it shall be included in the report.</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J128" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[13]/li[1]|text</t>
@@ -6925,8 +7644,16 @@
         </is>
       </c>
       <c r="G129" s="7" t="n"/>
-      <c r="H129" s="8" t="n"/>
-      <c r="I129" s="5" t="n"/>
+      <c r="H129" s="8" t="inlineStr">
+        <is>
+          <t>For the evaluation under Paragraph 1, the auditor (committee) must hold an in-person meeting.</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J129" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[13]/li[2]|text</t>
@@ -6959,8 +7686,16 @@
         </is>
       </c>
       <c r="G130" s="7" t="n"/>
-      <c r="H130" s="8" t="n"/>
-      <c r="I130" s="5" t="n"/>
+      <c r="H130" s="8" t="inlineStr">
+        <is>
+          <t>The auditor (committee) shall report the internal accounting management system evaluation report in person to the board of directors at least one week before the regular general meeting is held.</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J130" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[13]/li[3]|text</t>
@@ -6993,8 +7728,16 @@
         </is>
       </c>
       <c r="G131" s="7" t="n"/>
-      <c r="H131" s="8" t="n"/>
-      <c r="I131" s="5" t="n"/>
+      <c r="H131" s="8" t="inlineStr">
+        <is>
+          <t>Detailed standards and procedures for evaluation and reporting under Paragraph 1 shall be determined by considering each of the following subparagraphs.</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J131" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[13]/li[4]|text</t>
@@ -7027,8 +7770,16 @@
         </is>
       </c>
       <c r="G132" s="7" t="n"/>
-      <c r="H132" s="8" t="n"/>
-      <c r="I132" s="5" t="n"/>
+      <c r="H132" s="8" t="inlineStr">
+        <is>
+          <t>Evaluate whether the internal accounting management system is designed and operated so that management and persons who can actually influence the management of the company cannot improperly intervene in the process of preparing and disclosing accounting information.</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J132" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[13]/li[4]/ol/li[1]|text</t>
@@ -7061,8 +7812,16 @@
         </is>
       </c>
       <c r="G133" s="7" t="n"/>
-      <c r="H133" s="8" t="n"/>
-      <c r="I133" s="5" t="n"/>
+      <c r="H133" s="8" t="inlineStr">
+        <is>
+          <t>Evaluate whether the internal accounting management regulations are substantially operated.</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J133" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[13]/li[4]/ol/li[2]|text</t>
@@ -7095,8 +7854,16 @@
         </is>
       </c>
       <c r="G134" s="7" t="n"/>
-      <c r="H134" s="8" t="n"/>
-      <c r="I134" s="5" t="n"/>
+      <c r="H134" s="8" t="inlineStr">
+        <is>
+          <t>Evaluate whether the representative director complies with the standards and procedures for preparing the internal accounting management system operation status report.</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J134" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[13]/li[4]/ol/li[3]|text</t>
@@ -7129,8 +7896,16 @@
         </is>
       </c>
       <c r="G135" s="7" t="n"/>
-      <c r="H135" s="8" t="n"/>
-      <c r="I135" s="5" t="n"/>
+      <c r="H135" s="8" t="inlineStr">
+        <is>
+          <t>Article 19 (Keeping Evaluation Reports)</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J135" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[18]|text</t>
@@ -7163,8 +7938,16 @@
         </is>
       </c>
       <c r="G136" s="7" t="n"/>
-      <c r="H136" s="8" t="n"/>
-      <c r="I136" s="5" t="n"/>
+      <c r="H136" s="8" t="inlineStr">
+        <is>
+          <t>The auditor (committee) shall keep the internal accounting management system evaluation report at the head office for five years.</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J136" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/p[7]|text</t>
@@ -7197,8 +7980,16 @@
         </is>
       </c>
       <c r="G137" s="7" t="n"/>
-      <c r="H137" s="8" t="n"/>
-      <c r="I137" s="5" t="n"/>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
+          <t>Article 20 (Disclosure of Evaluation Results)</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J137" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[19]|text</t>
@@ -7231,8 +8022,16 @@
         </is>
       </c>
       <c r="G138" s="7" t="n"/>
-      <c r="H138" s="8" t="n"/>
-      <c r="I138" s="5" t="n"/>
+      <c r="H138" s="8" t="inlineStr">
+        <is>
+          <t>The representative director and the internal accounting manager shall attach documents (hereinafter referred to as 'Internal Accounting Management System Operation Reports') stating the following matters to the business report submitted in accordance with Article 159 of the Financial Investment Services and Capital Markets Act.</t>
+        </is>
+      </c>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J138" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[14]/li[1]|text</t>
@@ -7265,8 +8064,16 @@
         </is>
       </c>
       <c r="G139" s="7" t="n"/>
-      <c r="H139" s="8" t="n"/>
-      <c r="I139" s="5" t="n"/>
+      <c r="H139" s="8" t="inlineStr">
+        <is>
+          <t>Matters concerning the internal accounting management regulations under Article 8, Paragraph 1 of the Act and the organization and personnel that manage and operate them</t>
+        </is>
+      </c>
+      <c r="I139" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J139" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[14]/li[1]/ol/li[1]|text</t>
@@ -7299,8 +8106,16 @@
         </is>
       </c>
       <c r="G140" s="7" t="n"/>
-      <c r="H140" s="8" t="n"/>
-      <c r="I140" s="5" t="n"/>
+      <c r="H140" s="8" t="inlineStr">
+        <is>
+          <t>Review opinion or audit opinion of the auditor under Article 8, Paragraph 6 of the Act</t>
+        </is>
+      </c>
+      <c r="I140" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J140" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[14]/li[1]/ol/li[2]|text</t>
@@ -7333,8 +8148,16 @@
         </is>
       </c>
       <c r="G141" s="7" t="n"/>
-      <c r="H141" s="8" t="n"/>
-      <c r="I141" s="5" t="n"/>
+      <c r="H141" s="8" t="inlineStr">
+        <is>
+          <t>Internal Accounting Management System Operation Status Report</t>
+        </is>
+      </c>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J141" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[14]/li[1]/ol/li[3]|text</t>
@@ -7367,8 +8190,16 @@
         </is>
       </c>
       <c r="G142" s="7" t="n"/>
-      <c r="H142" s="8" t="n"/>
-      <c r="I142" s="5" t="n"/>
+      <c r="H142" s="8" t="inlineStr">
+        <is>
+          <t>Internal Accounting Management System Evaluation Report</t>
+        </is>
+      </c>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J142" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[14]/li[1]/ol/li[4]|text</t>
@@ -7401,8 +8232,16 @@
         </is>
       </c>
       <c r="G143" s="7" t="n"/>
-      <c r="H143" s="8" t="n"/>
-      <c r="I143" s="5" t="n"/>
+      <c r="H143" s="8" t="inlineStr">
+        <is>
+          <t>The internal accounting management system operation report to be attached to the business report under Paragraph 1 shall refer to the form of Attachment 3 of the 'Detailed Enforcement Rules of the Regulations on External Audit and Accounting, etc.'</t>
+        </is>
+      </c>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J143" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[14]/li[2]|text</t>
@@ -7435,8 +8274,16 @@
         </is>
       </c>
       <c r="G144" s="7" t="n"/>
-      <c r="H144" s="8" t="n"/>
-      <c r="I144" s="5" t="n"/>
+      <c r="H144" s="8" t="inlineStr">
+        <is>
+          <t>Article 21 (Measures for Violation of Relevant Regulations, etc.)</t>
+        </is>
+      </c>
+      <c r="I144" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J144" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[20]|text</t>
@@ -7469,8 +8316,16 @@
         </is>
       </c>
       <c r="G145" s="7" t="n"/>
-      <c r="H145" s="8" t="n"/>
-      <c r="I145" s="5" t="n"/>
+      <c r="H145" s="8" t="inlineStr">
+        <is>
+          <t>Regarding the disciplinary action of executives and employees who violate the internal accounting management regulations, including the following matters, the matters prescribed in the 'Reward and Punishment Regulations' shall be followed.</t>
+        </is>
+      </c>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J145" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/p[8]|text</t>
@@ -7503,8 +8358,16 @@
         </is>
       </c>
       <c r="G146" s="7" t="n"/>
-      <c r="H146" s="8" t="n"/>
-      <c r="I146" s="5" t="n"/>
+      <c r="H146" s="8" t="inlineStr">
+        <is>
+          <t>In case of preparing accounting information in violation of regulations</t>
+        </is>
+      </c>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J146" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[15]/li[1]|text</t>
@@ -7537,8 +8400,16 @@
         </is>
       </c>
       <c r="G147" s="7" t="n"/>
-      <c r="H147" s="8" t="n"/>
-      <c r="I147" s="5" t="n"/>
+      <c r="H147" s="8" t="inlineStr">
+        <is>
+          <t>In case of forging, altering, damaging, or destroying accounting information</t>
+        </is>
+      </c>
+      <c r="I147" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J147" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[15]/li[2]|text</t>
@@ -7571,8 +8442,16 @@
         </is>
       </c>
       <c r="G148" s="7" t="n"/>
-      <c r="H148" s="8" t="n"/>
-      <c r="I148" s="5" t="n"/>
+      <c r="H148" s="8" t="inlineStr">
+        <is>
+          <t>In case of designing, operating, evaluating, and reporting the internal accounting management system in violation of regulations</t>
+        </is>
+      </c>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J148" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[15]/li[3]|text</t>
@@ -7605,8 +8484,16 @@
         </is>
       </c>
       <c r="G149" s="7" t="n"/>
-      <c r="H149" s="8" t="n"/>
-      <c r="I149" s="5" t="n"/>
+      <c r="H149" s="8" t="inlineStr">
+        <is>
+          <t>In case of instructing each of the above subparagraphs</t>
+        </is>
+      </c>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J149" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[15]/li[4]|text</t>
@@ -7639,8 +8526,16 @@
         </is>
       </c>
       <c r="G150" s="7" t="n"/>
-      <c r="H150" s="8" t="n"/>
-      <c r="I150" s="5" t="n"/>
+      <c r="H150" s="8" t="inlineStr">
+        <is>
+          <t>Article 22 (Countermeasures for Violation of Regulations)</t>
+        </is>
+      </c>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J150" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[21]|text</t>
@@ -7673,8 +8568,16 @@
         </is>
       </c>
       <c r="G151" s="7" t="n"/>
-      <c r="H151" s="8" t="n"/>
-      <c r="I151" s="5" t="n"/>
+      <c r="H151" s="8" t="inlineStr">
+        <is>
+          <t>If the representative of the company or other executives and employees instruct to prepare or disclose accounting information in violation of these regulations, the corresponding executive or employee shall report this to the internal accounting manager in writing or orally.</t>
+        </is>
+      </c>
+      <c r="I151" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J151" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[16]/li[1]|text</t>
@@ -7707,8 +8610,16 @@
         </is>
       </c>
       <c r="G152" s="7" t="n"/>
-      <c r="H152" s="8" t="n"/>
-      <c r="I152" s="5" t="n"/>
+      <c r="H152" s="8" t="inlineStr">
+        <is>
+          <t>Executives and employees or the company that instructed the violation of internal accounting management regulations shall not treat executives and employees of the company disadvantageously in connection therewith even if they refuse the instruction violating the internal accounting management regulations.</t>
+        </is>
+      </c>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J152" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[16]/li[2]|text</t>
@@ -7741,8 +8652,16 @@
         </is>
       </c>
       <c r="G153" s="7" t="n"/>
-      <c r="H153" s="8" t="n"/>
-      <c r="I153" s="5" t="n"/>
+      <c r="H153" s="8" t="inlineStr">
+        <is>
+          <t>In applying Paragraph 1, if it falls under any of the following subparagraphs, it shall be reported to the auditor (committee) or reported to the internal reporting system.</t>
+        </is>
+      </c>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J153" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[16]/li[3]|text</t>
@@ -7775,8 +8694,16 @@
         </is>
       </c>
       <c r="G154" s="7" t="n"/>
-      <c r="H154" s="8" t="n"/>
-      <c r="I154" s="5" t="n"/>
+      <c r="H154" s="8" t="inlineStr">
+        <is>
+          <t>If the internal accounting manager instructs a violation of internal accounting management regulations or is involved therewith</t>
+        </is>
+      </c>
+      <c r="I154" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J154" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[16]/li[3]/ol/li[1]|text</t>
@@ -7809,8 +8736,16 @@
         </is>
       </c>
       <c r="G155" s="7" t="n"/>
-      <c r="H155" s="8" t="n"/>
-      <c r="I155" s="5" t="n"/>
+      <c r="H155" s="8" t="inlineStr">
+        <is>
+          <t>If it is judged inappropriate to report in accordance with Paragraph 1</t>
+        </is>
+      </c>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J155" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[16]/li[3]/ol/li[2]|text</t>
@@ -7843,8 +8778,16 @@
         </is>
       </c>
       <c r="G156" s="7" t="n"/>
-      <c r="H156" s="8" t="n"/>
-      <c r="I156" s="5" t="n"/>
+      <c r="H156" s="8" t="inlineStr">
+        <is>
+          <t>If disadvantageous treatment is given notwithstanding Paragraph 2</t>
+        </is>
+      </c>
+      <c r="I156" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J156" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[16]/li[3]/ol/li[3]|text</t>
@@ -7877,8 +8820,16 @@
         </is>
       </c>
       <c r="G157" s="7" t="n"/>
-      <c r="H157" s="8" t="n"/>
-      <c r="I157" s="5" t="n"/>
+      <c r="H157" s="8" t="inlineStr">
+        <is>
+          <t>If the internal accounting manager receives a report in accordance with Paragraph 1 or if the auditor (committee) receives a report in accordance with Paragraph 3, the internal accounting manager and the auditor (committee) shall review the reported content and take necessary measures, and maintain confidentiality regarding the identity of the reporter, etc.</t>
+        </is>
+      </c>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J157" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/ol[16]/li[4]|text</t>
@@ -7911,8 +8862,16 @@
         </is>
       </c>
       <c r="G158" s="7" t="n"/>
-      <c r="H158" s="8" t="n"/>
-      <c r="I158" s="5" t="n"/>
+      <c r="H158" s="8" t="inlineStr">
+        <is>
+          <t>Article 23 (Operation of Internal Reporting System)</t>
+        </is>
+      </c>
+      <c r="I158" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J158" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[22]|text</t>
@@ -8149,8 +9108,16 @@
         </is>
       </c>
       <c r="G165" s="7" t="n"/>
-      <c r="H165" s="8" t="n"/>
-      <c r="I165" s="5" t="n"/>
+      <c r="H165" s="8" t="inlineStr">
+        <is>
+          <t>Article 1 (Enforcement Date)</t>
+        </is>
+      </c>
+      <c r="I165" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J165" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[24]|text</t>
@@ -8183,8 +9150,16 @@
         </is>
       </c>
       <c r="G166" s="7" t="n"/>
-      <c r="H166" s="8" t="n"/>
-      <c r="I166" s="5" t="n"/>
+      <c r="H166" s="8" t="inlineStr">
+        <is>
+          <t>These regulations shall apply from the 2023 fiscal year.</t>
+        </is>
+      </c>
+      <c r="I166" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J166" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/p[9]|text</t>
@@ -8217,8 +9192,16 @@
         </is>
       </c>
       <c r="G167" s="7" t="n"/>
-      <c r="H167" s="8" t="n"/>
-      <c r="I167" s="5" t="n"/>
+      <c r="H167" s="8" t="inlineStr">
+        <is>
+          <t>Article 2 (Examples of Application for Standards for Design/Operation and Evaluation/Reporting of the Internal Accounting Management System)</t>
+        </is>
+      </c>
+      <c r="I167" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J167" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[25]|text</t>
@@ -8251,8 +9234,16 @@
         </is>
       </c>
       <c r="G168" s="7" t="n"/>
-      <c r="H168" s="8" t="n"/>
-      <c r="I168" s="5" t="n"/>
+      <c r="H168" s="8" t="inlineStr">
+        <is>
+          <t>The 'Conceptual Framework' and 'Best Practice' in Articles 14 and 16 shall apply from the 2023 fiscal year.</t>
+        </is>
+      </c>
+      <c r="I168" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J168" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/p[10]|text</t>
@@ -8364,8 +9355,16 @@
         </is>
       </c>
       <c r="G2" s="7" t="n"/>
-      <c r="H2" s="8" t="n"/>
-      <c r="I2" s="5" t="n"/>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Disclosure</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J2" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/header/div/h1|text</t>
@@ -8754,10 +9753,15 @@
         </is>
       </c>
       <c r="G13" s="7" t="n"/>
-      <c r="H13" s="8" t="n"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 1 General Provisions</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 2 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
@@ -8949,10 +9953,15 @@
         </is>
       </c>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="8" t="n"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Addenda</t>
+        </is>
+      </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 2 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
@@ -8988,8 +9997,16 @@
         </is>
       </c>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="5" t="n"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Article 1 (Purpose)</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[4]/div[2]/div[2]/div/h4[1]|text</t>
@@ -12875,8 +13892,16 @@
         </is>
       </c>
       <c r="G2" s="7" t="n"/>
-      <c r="H2" s="8" t="n"/>
-      <c r="I2" s="5" t="n"/>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Stock Information</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글 (ir_page.stock.header.title)</t>
+        </is>
+      </c>
       <c r="J2" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/header/div[1]/h1|text</t>
@@ -12909,8 +13934,16 @@
         </is>
       </c>
       <c r="G3" s="7" t="n"/>
-      <c r="H3" s="8" t="n"/>
-      <c r="I3" s="5" t="n"/>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>We share A-PRO's future value and transparent corporate information.</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/header/div[1]/p|text</t>
@@ -13140,8 +14173,16 @@
         </is>
       </c>
       <c r="G9" s="7" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="5" t="n"/>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div[1]/table/thead/tr/th[3]|text</t>
@@ -13482,8 +14523,16 @@
         </is>
       </c>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="5" t="n"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[2]/div[1]/dl/div[1]/dt|text</t>
@@ -13516,8 +14565,16 @@
         </is>
       </c>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="5" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[2]/div[1]/dl/div[2]/dt|text</t>
@@ -13550,8 +14607,16 @@
         </is>
       </c>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="5" t="n"/>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[2]/div[1]/dl/div[3]/dt|text</t>
@@ -13584,8 +14649,16 @@
         </is>
       </c>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="5" t="n"/>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[2]/div[1]/dl/div[4]/dt|text</t>
@@ -14350,10 +15423,15 @@
         </is>
       </c>
       <c r="G7" s="7" t="n"/>
-      <c r="H7" s="8" t="n"/>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 1 General Provisions</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 4 곳 — 한 줄로 합침</t>
+          <t>같은 문구 4 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
@@ -14391,10 +15469,15 @@
         </is>
       </c>
       <c r="G8" s="7" t="n"/>
-      <c r="H8" s="8" t="n"/>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 2 Management of Accounting Information</t>
+        </is>
+      </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 2 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
@@ -14430,10 +15513,15 @@
         </is>
       </c>
       <c r="G9" s="7" t="n"/>
-      <c r="H9" s="8" t="n"/>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 3 Duties and Education of Executives and Employees Related to the Internal Accounting Management System, etc.</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 2 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
@@ -14469,10 +15557,15 @@
         </is>
       </c>
       <c r="G10" s="7" t="n"/>
-      <c r="H10" s="8" t="n"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 5 Evaluation and Reporting of the Internal Accounting Management System</t>
+        </is>
+      </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 2 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J10" s="9" t="inlineStr">
@@ -14508,10 +15601,15 @@
         </is>
       </c>
       <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 6 Measures in Case of Violation of Regulations, etc.</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 2 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
@@ -14586,10 +15684,15 @@
         </is>
       </c>
       <c r="G13" s="7" t="n"/>
-      <c r="H13" s="8" t="n"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Addenda</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 4 곳 — 한 줄로 합침</t>
+          <t>같은 문구 4 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
@@ -14627,10 +15730,15 @@
         </is>
       </c>
       <c r="G14" s="7" t="n"/>
-      <c r="H14" s="8" t="n"/>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Article 1 (Purpose)</t>
+        </is>
+      </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 2 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
@@ -14666,8 +15774,16 @@
         </is>
       </c>
       <c r="G15" s="7" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="5" t="n"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>The purpose of these regulations is to establish policies and procedures necessary for designing, operating, evaluating, and reporting the company's internal accounting management system (hereinafter referred to as the 'Internal Accounting Management System') in accordance with Article 8 of the Act on External Audit of Stock Companies, etc. (hereinafter referred to as the 'Act'), Article 9 of the Enforcement Decree of the same Act (hereinafter referred to as the 'Decree'), and Article 6 of the Regulations on External Audit and Accounting, etc. (hereinafter referred to as the 'External Audit Regulations'), thereby enhancing the reliability of financial statements by designing and operating a reasonable and effective internal accounting management system.</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/p[1]|text</t>
@@ -14742,8 +15858,16 @@
         </is>
       </c>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="5" t="n"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Matters concerning the internal accounting management system shall be governed by these regulations unless otherwise provided for in laws or the articles of incorporation.</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[1]/li[1]|text</t>
@@ -14776,8 +15900,16 @@
         </is>
       </c>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="5" t="n"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>These regulations shall apply to matters necessary for preparing and disclosing accounting information regarding consolidated financial statements.</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[1]/li[2]|text</t>
@@ -14810,8 +15942,16 @@
         </is>
       </c>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="5" t="n"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Article 3 (Definition of Terms)</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[3]|text</t>
@@ -14844,8 +15984,16 @@
         </is>
       </c>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="5" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>The definitions of terms used in these regulations are as follows:</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/p[2]|text</t>
@@ -14878,8 +16026,16 @@
         </is>
       </c>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="5" t="n"/>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>'Internal Accounting Management System' refers to an internal control system designed and operated to provide reasonable assurance as to whether the company's financial statements have been prepared and disclosed in accordance with generally accepted accounting principles in order to achieve the objectives of internal accounting management, and refers to a process continuously executed by all members of the organization, including these regulations and the organization that manages and operates them.</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[2]/li[1]|text</t>
@@ -14912,8 +16068,16 @@
         </is>
       </c>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="5" t="n"/>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>'Internal Accounting Manager' refers to a person designated by the representative director as the person responsible for the management and operation of the internal accounting management system in accordance with Article 8, Paragraph 3 of the Act.</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[2]/li[2]|text</t>
@@ -14946,8 +16110,16 @@
         </is>
       </c>
       <c r="G23" s="7" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="5" t="n"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>'Internal Accounting Management System Evaluation' refers to a procedure for confirming whether the design and operation of the internal accounting management system are effective for a certain period, and includes the representative director's procedure for checking the effectiveness of the internal accounting management system and the auditor's (committee's) procedure for evaluating the actual status of the operation of the internal accounting management system.</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[2]/li[3]|text</t>
@@ -14980,8 +16152,16 @@
         </is>
       </c>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="5" t="n"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>'Auditor' refers to an accounting firm in accordance with Article 2, Subparagraph 7, Item (a) of the Act.</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[2]/li[4]|text</t>
@@ -15014,8 +16194,16 @@
         </is>
       </c>
       <c r="G25" s="7" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="5" t="n"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Article 4 (General Principles of Accounting Information Processing)</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[4]|text</t>
@@ -15048,8 +16236,16 @@
         </is>
       </c>
       <c r="G26" s="7" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="5" t="n"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>The company shall not prepare accounting information without following the internal accounting management system, nor shall it forge, alter, damage, or destroy accounting information prepared in accordance with the internal accounting management system.</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[3]/li[1]|text</t>
@@ -15082,8 +16278,16 @@
         </is>
       </c>
       <c r="G27" s="7" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="5" t="n"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Accounting processing such as identification, measurement, classification, recording, and reporting of accounting information shall be in accordance with the accounting standards prescribed in Article 5, Paragraph 1 of the Act.</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[3]/li[2]|text</t>
@@ -15116,8 +16320,16 @@
         </is>
       </c>
       <c r="G28" s="7" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="5" t="n"/>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>Article 5 (Identification, Measurement, Classification, Recording, and Reporting of Accounting Information)</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[5]|text</t>
@@ -15150,8 +16362,16 @@
         </is>
       </c>
       <c r="G29" s="7" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="5" t="n"/>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>Matters concerning accounting processing methods and accounting records, such as identification, measurement, classification, and reporting of accounting information, shall be processed in accordance with the general principles of Article 4, but the following requirements must be met.</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[4]/li[1]|text</t>
@@ -15184,8 +16404,16 @@
         </is>
       </c>
       <c r="G30" s="7" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="5" t="n"/>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Assets, liabilities, and capital recorded in the balance sheet must actually exist as of the end of the reporting period.</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[4]/li[1]/ol/li[1]|text</t>
@@ -15218,8 +16446,16 @@
         </is>
       </c>
       <c r="G31" s="7" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="5" t="n"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Assets shown in the balance sheet must be owned by the company, and liabilities must be debts that the company must repay.</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[4]/li[1]/ol/li[2]|text</t>
@@ -15252,8 +16488,16 @@
         </is>
       </c>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="5" t="n"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Transactions or events must have actually occurred during the accounting period.</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[4]/li[1]/ol/li[3]|text</t>
@@ -15286,8 +16530,16 @@
         </is>
       </c>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="5" t="n"/>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>There should be no assets, liabilities, transactions, or events that are not recorded in the financial statements, or items that are not disclosed.</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[4]/li[1]/ol/li[4]|text</t>
@@ -15320,8 +16572,16 @@
         </is>
       </c>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="5" t="n"/>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Assets, liabilities, capital, revenue, and expense items in the financial statements must be displayed in appropriate amounts in accordance with the general principles of Article 4.</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[4]/li[1]/ol/li[5]|text</t>
@@ -15354,8 +16614,16 @@
         </is>
       </c>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="8" t="n"/>
-      <c r="I35" s="5" t="n"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Accounting transactions or events must be recorded in the financial statements in appropriate amounts, and revenue or expenses must be allocated to appropriate accounting periods in accordance with the accrual principle.</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[4]/li[1]/ol/li[6]|text</t>
@@ -15388,8 +16656,16 @@
         </is>
       </c>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="5" t="n"/>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Components of the financial statements must be classified, described, and disclosed in accordance with the general principles of Article 4.</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[4]/li[1]/ol/li[7]|text</t>
@@ -15422,8 +16698,16 @@
         </is>
       </c>
       <c r="G37" s="7" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="5" t="n"/>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>All accounting information of the company shall be recorded in slips (including computer facilities) together with original documents, etc.</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[4]/li[2]|text</t>
@@ -15456,8 +16740,16 @@
         </is>
       </c>
       <c r="G38" s="7" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="5" t="n"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Accounting information prepared by the internal accounting management system shall be regularly reported to the internal accounting manager.</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[4]/li[3]|text</t>
@@ -15490,8 +16782,16 @@
         </is>
       </c>
       <c r="G39" s="7" t="n"/>
-      <c r="H39" s="8" t="n"/>
-      <c r="I39" s="5" t="n"/>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Article 6 (Error Control, Correction, and Internal Verification of Accounting Information)</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[6]|text</t>
@@ -15524,8 +16824,16 @@
         </is>
       </c>
       <c r="G40" s="7" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="5" t="n"/>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>The company and the auditor (committee) shall confirm whether the company's accounting information has been prepared in accordance with Articles 4 and 5 through the inspection under Article 17 and the evaluation under Article 18 to prevent errors from occurring in the process of processing accounting information.</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/p[3]|text</t>
@@ -15558,8 +16866,16 @@
         </is>
       </c>
       <c r="G41" s="7" t="n"/>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="5" t="n"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Article 7 (Management and Preservation of Accounting Records)</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[7]|text</t>
@@ -15592,8 +16908,16 @@
         </is>
       </c>
       <c r="G42" s="7" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="5" t="n"/>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>All accounting records, such as slips, accounting auxiliary books, and accounting books, shall be managed and preserved in the following manner.</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/p[4]|text</t>
@@ -15626,8 +16950,16 @@
         </is>
       </c>
       <c r="G43" s="7" t="n"/>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="5" t="n"/>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>Accounting books consist of accounting auxiliary books such as subsidiary ledgers and general ledgers, and financial statements, and these books are managed physically and electronically.</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[5]/li[1]|text</t>
@@ -15660,8 +16992,16 @@
         </is>
       </c>
       <c r="G44" s="7" t="n"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="5" t="n"/>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Physical accounting books are stored in a document warehouse designated by the accounting department, and management such as reading, transfer, and disposal is performed under the control of the accounting department. In addition, electronic accounting books are stored in a computer device by a computer operating system, and access and modification are allowed only to authorized persons, and the records are kept.</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[5]/li[2]|text</t>
@@ -15694,8 +17034,16 @@
         </is>
       </c>
       <c r="G45" s="7" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="5" t="n"/>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>The company shall not prepare accounting information without following the internal accounting management system, nor shall it forge, alter, damage, or destroy accounting information prepared by the internal accounting management system, or instruct such acts.</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[5]/li[3]|text</t>
@@ -15728,8 +17076,16 @@
         </is>
       </c>
       <c r="G46" s="7" t="n"/>
-      <c r="H46" s="8" t="n"/>
-      <c r="I46" s="5" t="n"/>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>The company shall establish and operate necessary procedures such as security procedures and access control procedures to prevent forgery, alteration, damage, and destruction of accounting information.</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[5]/li[4]|text</t>
@@ -15762,8 +17118,16 @@
         </is>
       </c>
       <c r="G47" s="7" t="n"/>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="5" t="n"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Article 8 (Division of Duties and Responsibility)</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[8]|text</t>
@@ -15796,8 +17160,16 @@
         </is>
       </c>
       <c r="G48" s="7" t="n"/>
-      <c r="H48" s="8" t="n"/>
-      <c r="I48" s="5" t="n"/>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>The company shall appropriately divide the duties of executives and employees in the department in charge of preparing and disclosing reliable accounting information, and define their authority and responsibility.</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/p[5]|text</t>
@@ -15830,8 +17202,16 @@
         </is>
       </c>
       <c r="G49" s="7" t="n"/>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="5" t="n"/>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Article 9 (Representative Director)</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[9]|text</t>
@@ -15864,8 +17244,16 @@
         </is>
       </c>
       <c r="G50" s="7" t="n"/>
-      <c r="H50" s="8" t="n"/>
-      <c r="I50" s="5" t="n"/>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>The representative director is responsible for the management and operation of the internal accounting management system and supports all necessary matters.</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[6]/li[1]|text</t>
@@ -15898,8 +17286,16 @@
         </is>
       </c>
       <c r="G51" s="7" t="n"/>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="5" t="n"/>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>The representative director designates an internal accounting manager in accordance with Article 10-2.</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[6]/li[2]|text</t>
@@ -15932,8 +17328,16 @@
         </is>
       </c>
       <c r="G52" s="7" t="n"/>
-      <c r="H52" s="8" t="n"/>
-      <c r="I52" s="5" t="n"/>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>The representative director checks and reports the actual status of the operation of the internal accounting management system in accordance with Article 17. However, if the representative director deems it necessary, reporting to the board of directors and the auditor (committee) may be delegated to the internal accounting manager.</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[6]/li[3]|text</t>
@@ -15966,8 +17370,16 @@
         </is>
       </c>
       <c r="G53" s="7" t="n"/>
-      <c r="H53" s="8" t="n"/>
-      <c r="I53" s="5" t="n"/>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>If the representative director intends to delegate reporting to the internal accounting manager in accordance with the proviso of Paragraph 3, he/she shall submit the reason in writing to the board of directors and the auditor (committee) before reporting.</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[6]/li[4]|text</t>
@@ -16000,8 +17412,16 @@
         </is>
       </c>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="8" t="n"/>
-      <c r="I54" s="5" t="n"/>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>The representative director shall follow without delay if there is a request from the auditor (committee) or a request from the auditor in accordance with Article 11, Paragraph 4. However, if there is a special reason, the request may be refused, and in this case, the reason shall be submitted in writing to the auditor (committee) or the auditor.</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[6]/li[5]|text</t>
@@ -16034,8 +17454,16 @@
         </is>
       </c>
       <c r="G55" s="7" t="n"/>
-      <c r="H55" s="8" t="n"/>
-      <c r="I55" s="5" t="n"/>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>Article 10 (Internal Accounting Manager)</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[10]|text</t>
@@ -16068,8 +17496,16 @@
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="8" t="n"/>
-      <c r="I56" s="5" t="n"/>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>The internal accounting manager oversees the design and operation of the internal accounting management system and supports all necessary matters.</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[7]/li[1]|text</t>
@@ -16102,8 +17538,16 @@
         </is>
       </c>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="8" t="n"/>
-      <c r="I57" s="5" t="n"/>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>The internal accounting manager checks the effectiveness of the design and operation of the internal accounting management system.</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J57" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[7]/li[2]|text</t>
@@ -16136,8 +17580,16 @@
         </is>
       </c>
       <c r="G58" s="7" t="n"/>
-      <c r="H58" s="8" t="n"/>
-      <c r="I58" s="5" t="n"/>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>The internal accounting manager reports the actual status of the operation of the internal accounting management system to the board of directors and the auditor (committee) in accordance with the proviso of Article 9, Paragraph 3.</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[7]/li[3]|text</t>
@@ -16170,8 +17622,16 @@
         </is>
       </c>
       <c r="G59" s="7" t="n"/>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="5" t="n"/>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>Article 10-2 (Qualifications and Appointment/Dismissal Procedures for Internal Accounting Manager)</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[11]|text</t>
@@ -16204,8 +17664,16 @@
         </is>
       </c>
       <c r="G60" s="7" t="n"/>
-      <c r="H60" s="8" t="n"/>
-      <c r="I60" s="5" t="n"/>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>The internal accounting manager must meet all of the following requirements.</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[8]/li[1]|text</t>
@@ -16238,8 +17706,16 @@
         </is>
       </c>
       <c r="G61" s="7" t="n"/>
-      <c r="H61" s="8" t="n"/>
-      <c r="I61" s="5" t="n"/>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>Must have expertise in accounting or internal control</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[8]/li[1]/ol/li[1]|text</t>
@@ -16272,8 +17748,16 @@
         </is>
       </c>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="5" t="n"/>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>Must be a full-time director</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[8]/li[1]/ol/li[2]|text</t>
@@ -16306,8 +17790,16 @@
         </is>
       </c>
       <c r="G63" s="7" t="n"/>
-      <c r="H63" s="8" t="n"/>
-      <c r="I63" s="5" t="n"/>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>Notwithstanding Paragraph 1, if there is no person who meets the requirements of Paragraph 1, Subparagraph 2, Subparagraph 2 shall be applied by regarding it as 'a person who executes the duties of the corresponding director'.</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J63" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[8]/li[2]|text</t>
@@ -16340,8 +17832,16 @@
         </is>
       </c>
       <c r="G64" s="7" t="n"/>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="5" t="n"/>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>The representative director re-designates the internal accounting manager if he/she deems that the performance of duties related to the internal accounting management system is impossible or inappropriate due to reasons such as personnel appointments.</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[8]/li[3]|text</t>
@@ -16374,8 +17874,16 @@
         </is>
       </c>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="8" t="n"/>
-      <c r="I65" s="5" t="n"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>The appointment and dismissal procedures for the internal accounting manager shall follow relevant regulations such as personnel management regulations.</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J65" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[8]/li[4]|text</t>
@@ -16408,8 +17916,16 @@
         </is>
       </c>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="8" t="n"/>
-      <c r="I66" s="5" t="n"/>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Article 11 (Auditor or Audit Committee)</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[12]|text</t>
@@ -16442,8 +17958,16 @@
         </is>
       </c>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="8" t="n"/>
-      <c r="I67" s="5" t="n"/>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>The auditor (committee) evaluates and reports the actual status of the operation of the internal accounting management system in accordance with Article 18.</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[9]/li[1]|text</t>
@@ -16476,8 +18000,16 @@
         </is>
       </c>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="8" t="n"/>
-      <c r="I68" s="5" t="n"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>If the auditor (committee) is notified of a violation of accounting processing from the auditor, he/she shall appoint an external expert to investigate the violation, etc., and request the representative director to correct the violation, etc., based on the results.</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[9]/li[2]|text</t>
@@ -16510,8 +18042,16 @@
         </is>
       </c>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="8" t="n"/>
-      <c r="I69" s="5" t="n"/>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>The auditor (committee) shall immediately submit the investigation results under Paragraph 1 and the company's corrective action results under Paragraph 2 to the Securities and Futures Commission and the auditor.</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J69" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[9]/li[3]|text</t>
@@ -16544,8 +18084,16 @@
         </is>
       </c>
       <c r="G70" s="7" t="n"/>
-      <c r="H70" s="8" t="n"/>
-      <c r="I70" s="5" t="n"/>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>The auditor (committee) may request the representative director in writing to provide necessary data, information, and expenses when performing the duties under Paragraphs 1 through 3.</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[9]/li[4]|text</t>
@@ -16578,8 +18126,16 @@
         </is>
       </c>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="8" t="n"/>
-      <c r="I71" s="5" t="n"/>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>If the auditor (committee) finds a fraudulent act or a significant fact violating laws or the articles of incorporation regarding the performance of duties by a director, he/she shall notify the auditor.</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J71" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[9]/li[5]|text</t>
@@ -16612,8 +18168,16 @@
         </is>
       </c>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="8" t="n"/>
-      <c r="I72" s="5" t="n"/>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>Article 12 (Establishment and Implementation of Education Plans, etc.)</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[13]|text</t>
@@ -16646,8 +18210,16 @@
         </is>
       </c>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="8" t="n"/>
-      <c r="I73" s="5" t="n"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>The company shall establish education plans necessary for understanding matters prescribed in laws related to the internal accounting management system and these regulations for the representative director, internal accounting manager, auditor (committee), and executives and employees who prepare and disclose accounting information (hereinafter referred to as 'representative director, etc.'), and conduct necessary education.</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[10]/li[1]|text</t>
@@ -16680,8 +18252,16 @@
         </is>
       </c>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="8" t="n"/>
-      <c r="I74" s="5" t="n"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>The company conducts performance evaluation of the education under Paragraph 1, and the results are reflected in the education plan for the next business year.</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[10]/li[2]|text</t>
@@ -16714,8 +18294,16 @@
         </is>
       </c>
       <c r="G75" s="7" t="n"/>
-      <c r="H75" s="8" t="n"/>
-      <c r="I75" s="5" t="n"/>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>The evaluation results of Paragraph 2 may be operated in connection with the compensation policy prescribed in Article 13, Paragraph 1.</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[10]/li[3]|text</t>
@@ -16748,8 +18336,16 @@
         </is>
       </c>
       <c r="G76" s="7" t="n"/>
-      <c r="H76" s="8" t="n"/>
-      <c r="I76" s="5" t="n"/>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>Article 13 (Linkage between Audit Evaluation Results and Compensation Policy)</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[14]|text</t>
@@ -16782,8 +18378,16 @@
         </is>
       </c>
       <c r="G77" s="7" t="n"/>
-      <c r="H77" s="8" t="n"/>
-      <c r="I77" s="5" t="n"/>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>The company reflects the evaluation results of the auditor (committee) in accordance with Article 18 in the personnel, compensation, and establishment of the operation plan for the internal accounting management system for the next business year of the representative director, etc.</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J77" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[11]/li[1]|text</t>
@@ -16816,8 +18420,16 @@
         </is>
       </c>
       <c r="G78" s="7" t="n"/>
-      <c r="H78" s="8" t="n"/>
-      <c r="I78" s="5" t="n"/>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>Detailed matters for applying Paragraph 1 shall follow separate regulations prescribed by the representative director.</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[11]/li[2]|text</t>
@@ -16850,8 +18462,16 @@
         </is>
       </c>
       <c r="G79" s="7" t="n"/>
-      <c r="H79" s="8" t="n"/>
-      <c r="I79" s="5" t="n"/>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>Article 16 (Standards for Evaluation and Reporting of the Internal Accounting Management System)</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J79" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[15]|text</t>
@@ -16884,8 +18504,16 @@
         </is>
       </c>
       <c r="G80" s="7" t="n"/>
-      <c r="H80" s="8" t="n"/>
-      <c r="I80" s="5" t="n"/>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>The representative director, internal accounting manager, and auditor (committee) shall perform the inspection under Article 17 and the evaluation under Article 18 in accordance with the 'Best Practice for Evaluation and Reporting of Internal Accounting Management System' (hereinafter referred to as the 'Best Practice') announced by the Steering Committee.</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/p[6]|text</t>
@@ -16918,8 +18546,16 @@
         </is>
       </c>
       <c r="G81" s="7" t="n"/>
-      <c r="H81" s="8" t="n"/>
-      <c r="I81" s="5" t="n"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>Article 17 (Standards and Procedures for the Representative Director's Evaluation and Reporting of the Actual Status of Operation)</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J81" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[16]|text</t>
@@ -16952,8 +18588,16 @@
         </is>
       </c>
       <c r="G82" s="7" t="n"/>
-      <c r="H82" s="8" t="n"/>
-      <c r="I82" s="5" t="n"/>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>The company shall prepare objective performance indicators for checking the effectiveness of the internal accounting management system.</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[12]/li[1]|text</t>
@@ -16986,8 +18630,16 @@
         </is>
       </c>
       <c r="G83" s="7" t="n"/>
-      <c r="H83" s="8" t="n"/>
-      <c r="I83" s="5" t="n"/>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>The representative director shall perform an inspection on the effectiveness of the internal accounting management system every business year and report to the general meeting of shareholders, the board of directors, and the auditor (committee).</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J83" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[12]/li[2]|text</t>
@@ -17020,8 +18672,16 @@
         </is>
       </c>
       <c r="G84" s="7" t="n"/>
-      <c r="H84" s="8" t="n"/>
-      <c r="I84" s="5" t="n"/>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>When the representative director reports the inspection results to the board of directors and the auditor (committee) in accordance with Paragraph 2, he/she shall prepare it in a document (hereinafter referred to as the 'Internal Accounting Management System Operation Status Report') and report it in person.</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[12]/li[3]|text</t>
@@ -17054,8 +18714,16 @@
         </is>
       </c>
       <c r="G85" s="7" t="n"/>
-      <c r="H85" s="8" t="n"/>
-      <c r="I85" s="5" t="n"/>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>The detailed standards and procedures for inspection and reporting under Paragraph 2 shall be determined by considering each of the following subparagraphs.</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[12]/li[4]|text</t>
@@ -17088,8 +18756,16 @@
         </is>
       </c>
       <c r="G86" s="7" t="n"/>
-      <c r="H86" s="8" t="n"/>
-      <c r="I86" s="5" t="n"/>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>The internal accounting management system shall be designed and operated in a form suitable for the company.</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[12]/li[4]/ol/li[1]|text</t>
@@ -17122,8 +18798,16 @@
         </is>
       </c>
       <c r="G87" s="7" t="n"/>
-      <c r="H87" s="8" t="n"/>
-      <c r="I87" s="5" t="n"/>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>A constant and regular inspection system shall be established to prevent or discover and take measures in a timely manner against risks that hinder the preparation and disclosure of reliable accounting information.</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J87" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[12]/li[4]/ol/li[2]|text</t>
@@ -17156,8 +18840,16 @@
         </is>
       </c>
       <c r="G88" s="7" t="n"/>
-      <c r="H88" s="8" t="n"/>
-      <c r="I88" s="5" t="n"/>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>Performance indicators under Paragraph 1</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[12]/li[4]/ol/li[3]|text</t>
@@ -17190,8 +18882,16 @@
         </is>
       </c>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="8" t="n"/>
-      <c r="I89" s="5" t="n"/>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>The representative director shall present an opinion on whether the company's internal accounting management system is effective by considering the performance indicators under Subparagraph 3 and the inspection results on whether there are vulnerabilities in the internal accounting management system.</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[12]/li[4]/ol/li[4]|text</t>
@@ -17224,8 +18924,16 @@
         </is>
       </c>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="8" t="n"/>
-      <c r="I90" s="5" t="n"/>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>If an audit has been received for the internal accounting management system, the corrective action plan following the audit shall be reflected in the internal accounting management system corrective action plan.</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[12]/li[4]/ol/li[5]|text</t>
@@ -17258,8 +18966,16 @@
         </is>
       </c>
       <c r="G91" s="7" t="n"/>
-      <c r="H91" s="8" t="n"/>
-      <c r="I91" s="5" t="n"/>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>Establishment of operation status inspection plan</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J91" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[12]/li[4]/ol/li[6]|text</t>
@@ -17292,8 +19008,16 @@
         </is>
       </c>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="8" t="n"/>
-      <c r="I92" s="5" t="n"/>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>Performance of operation status inspection</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[12]/li[4]/ol/li[7]|text</t>
@@ -17326,8 +19050,16 @@
         </is>
       </c>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="8" t="n"/>
-      <c r="I93" s="5" t="n"/>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>Evaluation of deficiencies and establishment of improvement plans</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J93" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[12]/li[4]/ol/li[8]|text</t>
@@ -17360,8 +19092,16 @@
         </is>
       </c>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="8" t="n"/>
-      <c r="I94" s="5" t="n"/>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>Reporting of operation status</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[12]/li[4]/ol/li[9]|text</t>
@@ -17394,8 +19134,16 @@
         </is>
       </c>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="8" t="n"/>
-      <c r="I95" s="5" t="n"/>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>The inspection and reporting under Paragraph 2 shall follow the procedures of each of the following subparagraphs.</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J95" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[12]/li[5]|text</t>
@@ -17428,8 +19176,16 @@
         </is>
       </c>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="8" t="n"/>
-      <c r="I96" s="5" t="n"/>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>Article 18 (Standards and Procedures for the Auditor's Evaluation and Reporting of the Actual Status of Operation)</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[17]|text</t>
@@ -17462,8 +19218,16 @@
         </is>
       </c>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="8" t="n"/>
-      <c r="I97" s="5" t="n"/>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>The auditor (committee) evaluates the internal accounting management system operation status report under Article 17, Paragraph 3, and prepares the evaluation results in a document (hereinafter referred to as the 'Internal Accounting Management System Evaluation Report') and reports it to the board of directors every business year. In this case, if there is a corrective opinion on the management and operation of the internal accounting management system, it shall be included in the report.</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[13]/li[1]|text</t>
@@ -17496,8 +19260,16 @@
         </is>
       </c>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="8" t="n"/>
-      <c r="I98" s="5" t="n"/>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>For the evaluation under Paragraph 1, the auditor (committee) must hold an in-person meeting.</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[13]/li[2]|text</t>
@@ -17530,8 +19302,16 @@
         </is>
       </c>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="8" t="n"/>
-      <c r="I99" s="5" t="n"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>The auditor (committee) shall report the internal accounting management system evaluation report in person to the board of directors at least one week before the regular general meeting is held.</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J99" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[13]/li[3]|text</t>
@@ -17564,8 +19344,16 @@
         </is>
       </c>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="8" t="n"/>
-      <c r="I100" s="5" t="n"/>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>Detailed standards and procedures for evaluation and reporting under Paragraph 1 shall be determined by considering each of the following subparagraphs.</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[13]/li[4]|text</t>
@@ -17598,8 +19386,16 @@
         </is>
       </c>
       <c r="G101" s="7" t="n"/>
-      <c r="H101" s="8" t="n"/>
-      <c r="I101" s="5" t="n"/>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>Evaluate whether the internal accounting management system is designed and operated so that management and persons who can actually influence the management of the company cannot improperly intervene in the process of preparing and disclosing accounting information.</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[13]/li[4]/ol/li[1]|text</t>
@@ -17632,8 +19428,16 @@
         </is>
       </c>
       <c r="G102" s="7" t="n"/>
-      <c r="H102" s="8" t="n"/>
-      <c r="I102" s="5" t="n"/>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>Evaluate whether the internal accounting management regulations are substantially operated.</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[13]/li[4]/ol/li[2]|text</t>
@@ -17666,8 +19470,16 @@
         </is>
       </c>
       <c r="G103" s="7" t="n"/>
-      <c r="H103" s="8" t="n"/>
-      <c r="I103" s="5" t="n"/>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>Evaluate whether the representative director complies with the standards and procedures for preparing the internal accounting management system operation status report.</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J103" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[13]/li[4]/ol/li[3]|text</t>
@@ -17700,8 +19512,16 @@
         </is>
       </c>
       <c r="G104" s="7" t="n"/>
-      <c r="H104" s="8" t="n"/>
-      <c r="I104" s="5" t="n"/>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>Article 19 (Keeping Evaluation Reports)</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[18]|text</t>
@@ -17734,8 +19554,16 @@
         </is>
       </c>
       <c r="G105" s="7" t="n"/>
-      <c r="H105" s="8" t="n"/>
-      <c r="I105" s="5" t="n"/>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>The auditor (committee) shall keep the internal accounting management system evaluation report at the head office for five years.</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J105" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/p[7]|text</t>
@@ -17768,8 +19596,16 @@
         </is>
       </c>
       <c r="G106" s="7" t="n"/>
-      <c r="H106" s="8" t="n"/>
-      <c r="I106" s="5" t="n"/>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>Article 20 (Disclosure of Evaluation Results)</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[19]|text</t>
@@ -17802,8 +19638,16 @@
         </is>
       </c>
       <c r="G107" s="7" t="n"/>
-      <c r="H107" s="8" t="n"/>
-      <c r="I107" s="5" t="n"/>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>The representative director and the internal accounting manager shall attach documents (hereinafter referred to as 'Internal Accounting Management System Operation Reports') stating the following matters to the business report submitted in accordance with Article 159 of the Financial Investment Services and Capital Markets Act.</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J107" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[14]/li[1]|text</t>
@@ -17836,8 +19680,16 @@
         </is>
       </c>
       <c r="G108" s="7" t="n"/>
-      <c r="H108" s="8" t="n"/>
-      <c r="I108" s="5" t="n"/>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>Matters concerning the internal accounting management regulations under Article 8, Paragraph 1 of the Act and the organization and personnel that manage and operate them</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[14]/li[1]/ol/li[1]|text</t>
@@ -17870,8 +19722,16 @@
         </is>
       </c>
       <c r="G109" s="7" t="n"/>
-      <c r="H109" s="8" t="n"/>
-      <c r="I109" s="5" t="n"/>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>Review opinion or audit opinion of the auditor under Article 8, Paragraph 6 of the Act</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[14]/li[1]/ol/li[2]|text</t>
@@ -17904,8 +19764,16 @@
         </is>
       </c>
       <c r="G110" s="7" t="n"/>
-      <c r="H110" s="8" t="n"/>
-      <c r="I110" s="5" t="n"/>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>Internal Accounting Management System Operation Status Report</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J110" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[14]/li[1]/ol/li[3]|text</t>
@@ -17938,8 +19806,16 @@
         </is>
       </c>
       <c r="G111" s="7" t="n"/>
-      <c r="H111" s="8" t="n"/>
-      <c r="I111" s="5" t="n"/>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>Internal Accounting Management System Evaluation Report</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J111" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[14]/li[1]/ol/li[4]|text</t>
@@ -17972,8 +19848,16 @@
         </is>
       </c>
       <c r="G112" s="7" t="n"/>
-      <c r="H112" s="8" t="n"/>
-      <c r="I112" s="5" t="n"/>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
+          <t>The internal accounting management system operation report to be attached to the business report under Paragraph 1 shall refer to the form of Attachment 3 of the 'Detailed Enforcement Rules of the Regulations on External Audit and Accounting, etc.'</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[14]/li[2]|text</t>
@@ -18006,8 +19890,16 @@
         </is>
       </c>
       <c r="G113" s="7" t="n"/>
-      <c r="H113" s="8" t="n"/>
-      <c r="I113" s="5" t="n"/>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>Article 21 (Measures for Violation of Relevant Regulations, etc.)</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J113" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[20]|text</t>
@@ -18040,8 +19932,16 @@
         </is>
       </c>
       <c r="G114" s="7" t="n"/>
-      <c r="H114" s="8" t="n"/>
-      <c r="I114" s="5" t="n"/>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>Regarding the disciplinary action of executives and employees who violate the internal accounting management regulations, including the following matters, the matters prescribed in the 'Reward and Punishment Regulations' shall be followed.</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/p[8]|text</t>
@@ -18074,8 +19974,16 @@
         </is>
       </c>
       <c r="G115" s="7" t="n"/>
-      <c r="H115" s="8" t="n"/>
-      <c r="I115" s="5" t="n"/>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>In case of preparing accounting information in violation of regulations</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J115" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[15]/li[1]|text</t>
@@ -18108,8 +20016,16 @@
         </is>
       </c>
       <c r="G116" s="7" t="n"/>
-      <c r="H116" s="8" t="n"/>
-      <c r="I116" s="5" t="n"/>
+      <c r="H116" s="8" t="inlineStr">
+        <is>
+          <t>In case of forging, altering, damaging, or destroying accounting information</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J116" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[15]/li[2]|text</t>
@@ -18142,8 +20058,16 @@
         </is>
       </c>
       <c r="G117" s="7" t="n"/>
-      <c r="H117" s="8" t="n"/>
-      <c r="I117" s="5" t="n"/>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>In case of designing, operating, evaluating, and reporting the internal accounting management system in violation of regulations</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J117" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[15]/li[3]|text</t>
@@ -18176,8 +20100,16 @@
         </is>
       </c>
       <c r="G118" s="7" t="n"/>
-      <c r="H118" s="8" t="n"/>
-      <c r="I118" s="5" t="n"/>
+      <c r="H118" s="8" t="inlineStr">
+        <is>
+          <t>In case of instructing each of the above subparagraphs</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J118" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[15]/li[4]|text</t>
@@ -18210,8 +20142,16 @@
         </is>
       </c>
       <c r="G119" s="7" t="n"/>
-      <c r="H119" s="8" t="n"/>
-      <c r="I119" s="5" t="n"/>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>Article 22 (Countermeasures for Violation of Regulations)</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J119" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[21]|text</t>
@@ -18244,8 +20184,16 @@
         </is>
       </c>
       <c r="G120" s="7" t="n"/>
-      <c r="H120" s="8" t="n"/>
-      <c r="I120" s="5" t="n"/>
+      <c r="H120" s="8" t="inlineStr">
+        <is>
+          <t>If the representative of the company or other executives and employees instruct to prepare or disclose accounting information in violation of these regulations, the corresponding executive or employee shall report this to the internal accounting manager in writing or orally.</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J120" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[16]/li[1]|text</t>
@@ -18278,8 +20226,16 @@
         </is>
       </c>
       <c r="G121" s="7" t="n"/>
-      <c r="H121" s="8" t="n"/>
-      <c r="I121" s="5" t="n"/>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>Executives and employees or the company that instructed the violation of internal accounting management regulations shall not treat executives and employees of the company disadvantageously in connection therewith even if they refuse the instruction violating the internal accounting management regulations.</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J121" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[16]/li[2]|text</t>
@@ -18312,8 +20268,16 @@
         </is>
       </c>
       <c r="G122" s="7" t="n"/>
-      <c r="H122" s="8" t="n"/>
-      <c r="I122" s="5" t="n"/>
+      <c r="H122" s="8" t="inlineStr">
+        <is>
+          <t>In applying Paragraph 1, if it falls under any of the following subparagraphs, it shall be reported to the auditor (committee) or reported to the internal reporting system.</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J122" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[16]/li[3]|text</t>
@@ -18346,8 +20310,16 @@
         </is>
       </c>
       <c r="G123" s="7" t="n"/>
-      <c r="H123" s="8" t="n"/>
-      <c r="I123" s="5" t="n"/>
+      <c r="H123" s="8" t="inlineStr">
+        <is>
+          <t>If the internal accounting manager instructs a violation of internal accounting management regulations or is involved therewith</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J123" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[16]/li[3]/ol/li[1]|text</t>
@@ -18380,8 +20352,16 @@
         </is>
       </c>
       <c r="G124" s="7" t="n"/>
-      <c r="H124" s="8" t="n"/>
-      <c r="I124" s="5" t="n"/>
+      <c r="H124" s="8" t="inlineStr">
+        <is>
+          <t>If it is judged inappropriate to report in accordance with Paragraph 1</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J124" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[16]/li[3]/ol/li[2]|text</t>
@@ -18414,8 +20394,16 @@
         </is>
       </c>
       <c r="G125" s="7" t="n"/>
-      <c r="H125" s="8" t="n"/>
-      <c r="I125" s="5" t="n"/>
+      <c r="H125" s="8" t="inlineStr">
+        <is>
+          <t>If disadvantageous treatment is given notwithstanding Paragraph 2</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J125" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[16]/li[3]/ol/li[3]|text</t>
@@ -18448,8 +20436,16 @@
         </is>
       </c>
       <c r="G126" s="7" t="n"/>
-      <c r="H126" s="8" t="n"/>
-      <c r="I126" s="5" t="n"/>
+      <c r="H126" s="8" t="inlineStr">
+        <is>
+          <t>If the internal accounting manager receives a report in accordance with Paragraph 1 or if the auditor (committee) receives a report in accordance with Paragraph 3, the internal accounting manager and the auditor (committee) shall review the reported content and take necessary measures, and maintain confidentiality regarding the identity of the reporter, etc.</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J126" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/ol[16]/li[4]|text</t>
@@ -18482,8 +20478,16 @@
         </is>
       </c>
       <c r="G127" s="7" t="n"/>
-      <c r="H127" s="8" t="n"/>
-      <c r="I127" s="5" t="n"/>
+      <c r="H127" s="8" t="inlineStr">
+        <is>
+          <t>Article 23 (Operation of Internal Reporting System)</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J127" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[22]|text</t>
@@ -18720,8 +20724,16 @@
         </is>
       </c>
       <c r="G134" s="7" t="n"/>
-      <c r="H134" s="8" t="n"/>
-      <c r="I134" s="5" t="n"/>
+      <c r="H134" s="8" t="inlineStr">
+        <is>
+          <t>Article 1 (Enforcement Date)</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J134" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[24]|text</t>
@@ -18754,8 +20766,16 @@
         </is>
       </c>
       <c r="G135" s="7" t="n"/>
-      <c r="H135" s="8" t="n"/>
-      <c r="I135" s="5" t="n"/>
+      <c r="H135" s="8" t="inlineStr">
+        <is>
+          <t>These regulations shall apply from the 2023 fiscal year.</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J135" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/p[9]|text</t>
@@ -18788,8 +20808,16 @@
         </is>
       </c>
       <c r="G136" s="7" t="n"/>
-      <c r="H136" s="8" t="n"/>
-      <c r="I136" s="5" t="n"/>
+      <c r="H136" s="8" t="inlineStr">
+        <is>
+          <t>Article 2 (Examples of Application for Standards for Design/Operation and Evaluation/Reporting of the Internal Accounting Management System)</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J136" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/h4[25]|text</t>
@@ -18822,8 +20850,16 @@
         </is>
       </c>
       <c r="G137" s="7" t="n"/>
-      <c r="H137" s="8" t="n"/>
-      <c r="I137" s="5" t="n"/>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
+          <t>The 'Conceptual Framework' and 'Best Practice' in Articles 14 and 16 shall apply from the 2023 fiscal year.</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J137" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[1]/div/p[10]|text</t>
@@ -23607,8 +25643,16 @@
         </is>
       </c>
       <c r="G23" s="7" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="5" t="n"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Article 1 (Purpose)</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[3]/details/div/h3[1]|text</t>
@@ -29396,8 +31440,16 @@
         </is>
       </c>
       <c r="G130" s="7" t="n"/>
-      <c r="H130" s="8" t="n"/>
-      <c r="I130" s="5" t="n"/>
+      <c r="H130" s="8" t="inlineStr">
+        <is>
+          <t>Addendum</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글 (esg_modals.supplier_code.addendum)</t>
+        </is>
+      </c>
       <c r="J130" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[2]/details/div/h3[10]|text</t>
@@ -35962,8 +38014,16 @@
         </is>
       </c>
       <c r="G162" s="7" t="n"/>
-      <c r="H162" s="8" t="n"/>
-      <c r="I162" s="5" t="n"/>
+      <c r="H162" s="8" t="inlineStr">
+        <is>
+          <t>Addendum</t>
+        </is>
+      </c>
+      <c r="I162" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글 (esg_modals.ethics_charter.addendum.title)</t>
+        </is>
+      </c>
       <c r="J162" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[3]/details/div/h3[5]|text</t>
@@ -37606,8 +39666,16 @@
         </is>
       </c>
       <c r="G42" s="7" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="5" t="n"/>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/main/section[5]/form/div[5]/label|text</t>
@@ -38281,12 +40349,17 @@
         </is>
       </c>
       <c r="G9" s="7" t="n"/>
-      <c r="H9" s="8" t="n"/>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Compound Power Semiconductors</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>같은 문구 3 곳 — 한 줄로 합침
 카드 제목 자리는 두 줄로 나눠 보입니다 — 줄 나눌 곳이 따로 있으면 비고에 적어 주세요
-GNB · 메가 메뉴 · 푸터의 사업영역 이름도 함께 고칩니다</t>
+GNB · 메가 메뉴 · 푸터의 사업영역 이름도 함께 고칩니다
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
@@ -38361,8 +40434,16 @@
         </is>
       </c>
       <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="5" t="n"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글 (header.business)</t>
+        </is>
+      </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/section[2]/div[1]/h2/span|text</t>
@@ -39049,10 +41130,15 @@
         </is>
       </c>
       <c r="G29" s="7" t="n"/>
-      <c r="H29" s="8" t="n"/>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO SEMICON</t>
+        </is>
+      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>사업영역 세부 시트의 소분류 이름과 같은 글 — 한쪽을 바꾸면 함께 고칩니다</t>
+          <t>사업영역 세부 시트의 소분류 이름과 같은 글 — 한쪽을 바꾸면 함께 고칩니다
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
@@ -39125,8 +41211,16 @@
         </is>
       </c>
       <c r="G31" s="7" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="5" t="n"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Core Capability</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/section[3]/h2/span|text</t>
@@ -39637,8 +41731,16 @@
         </is>
       </c>
       <c r="G45" s="7" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="5" t="n"/>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Press Release</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/section[4]/div[1]/div/h2/span|text</t>
@@ -39705,10 +41807,15 @@
         </is>
       </c>
       <c r="G47" s="7" t="n"/>
-      <c r="H47" s="8" t="n"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>View More</t>
+        </is>
+      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 5 곳 — 한 줄로 합침</t>
+          <t>같은 문구 5 곳 — 한 줄로 합침
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J47" s="9" t="inlineStr">
@@ -40568,7 +42675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -40837,10 +42944,15 @@
         </is>
       </c>
       <c r="G2" s="7" t="n"/>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>GNB · 메가 메뉴 · 전체 메뉴의 대분류 이름과 같은 글</t>
+          <t>GNB · 메가 메뉴 · 전체 메뉴의 대분류 이름과 같은 글
+영문: 옛 홈페이지 글 (header.business)</t>
         </is>
       </c>
       <c r="J2" s="9" t="inlineStr">
@@ -40989,10 +43101,15 @@
         </is>
       </c>
       <c r="G6" s="7" t="n"/>
-      <c r="H6" s="8" t="n"/>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Compound Power Semiconductors</t>
+        </is>
+      </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글</t>
+          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
@@ -41103,10 +43220,15 @@
         </is>
       </c>
       <c r="G9" s="7" t="n"/>
-      <c r="H9" s="8" t="n"/>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Global Network</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글</t>
+          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
@@ -41141,10 +43263,15 @@
         </is>
       </c>
       <c r="G10" s="7" t="n"/>
-      <c r="H10" s="8" t="n"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글</t>
+          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J10" s="9" t="inlineStr">
@@ -41179,10 +43306,15 @@
         </is>
       </c>
       <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>IR</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>GNB · 메가 메뉴 · 전체 메뉴의 대분류 이름과 같은 글</t>
+          <t>GNB · 메가 메뉴 · 전체 메뉴의 대분류 이름과 같은 글
+영문: 옛 홈페이지 글 (header.ir)</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
@@ -41217,10 +43349,15 @@
         </is>
       </c>
       <c r="G12" s="7" t="n"/>
-      <c r="H12" s="8" t="n"/>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Financial Info</t>
+        </is>
+      </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글</t>
+          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
@@ -41255,10 +43392,15 @@
         </is>
       </c>
       <c r="G13" s="7" t="n"/>
-      <c r="H13" s="8" t="n"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Disclosure</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글</t>
+          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
@@ -41293,10 +43435,15 @@
         </is>
       </c>
       <c r="G14" s="7" t="n"/>
-      <c r="H14" s="8" t="n"/>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Stock Info</t>
+        </is>
+      </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글</t>
+          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글
+영문: 옛 홈페이지 글 (header.sitemap.stock)</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
@@ -41331,10 +43478,15 @@
         </is>
       </c>
       <c r="G15" s="7" t="n"/>
-      <c r="H15" s="8" t="n"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>GNB · 메가 메뉴 · 전체 메뉴의 대분류 이름과 같은 글</t>
+          <t>GNB · 메가 메뉴 · 전체 메뉴의 대분류 이름과 같은 글
+영문: 옛 홈페이지 글 (header.esg)</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
@@ -41369,10 +43521,15 @@
         </is>
       </c>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="8" t="n"/>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글</t>
+          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
@@ -41407,10 +43564,15 @@
         </is>
       </c>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="8" t="n"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글</t>
+          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
@@ -41521,10 +43683,15 @@
         </is>
       </c>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="8" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>ESG Board</t>
+        </is>
+      </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글</t>
+          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
@@ -41559,10 +43726,15 @@
         </is>
       </c>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="8" t="n"/>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>GNB · 메가 메뉴 · 전체 메뉴의 대분류 이름과 같은 글</t>
+          <t>GNB · 메가 메뉴 · 전체 메뉴의 대분류 이름과 같은 글
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
@@ -41597,10 +43769,15 @@
         </is>
       </c>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="8" t="n"/>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Notice</t>
+        </is>
+      </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글</t>
+          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
@@ -41635,10 +43812,15 @@
         </is>
       </c>
       <c r="G23" s="7" t="n"/>
-      <c r="H23" s="8" t="n"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Press Release</t>
+        </is>
+      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글</t>
+          <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글
+영문: 옛 홈페이지 글</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
@@ -42037,8 +44219,16 @@
         </is>
       </c>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="5" t="n"/>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO SEMICON</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
           <t>footer|목록|에이프로 세미콘</t>
@@ -58577,8 +60767,16 @@
         </is>
       </c>
       <c r="G2" s="7" t="n"/>
-      <c r="H2" s="8" t="n"/>
-      <c r="I2" s="5" t="n"/>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Compound Power Semiconductors</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J2" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[1]/div/div/h1/span[1]|text</t>
@@ -60216,8 +62414,16 @@
         </is>
       </c>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="5" t="n"/>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Compound Power Semiconductors</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
           <t>/html/body/section/div/a[4]/div[1]/div/p[1]|text</t>
@@ -60364,8 +62570,16 @@
         </is>
       </c>
       <c r="G25" s="7" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="5" t="n"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO SEMICON</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
           <t>/html/body/section/div/a[4]/div[2]/span[3]/span[2]|text</t>

--- a/content-export/국문영문글정리.xlsx
+++ b/content-export/국문영문글정리.xlsx
@@ -32,7 +32,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보관" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'홈'!$A$1:$J$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'홈'!$A$1:$J$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'푸터'!$A$1:$J$112</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'스마트 제조'!$A$1:$J$140</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'에너지 인프라'!$A$1:$J$179</definedName>
@@ -770,6 +770,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -805,6 +806,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -39994,7 +39996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -41233,31 +41235,31 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Who we are · 01</t>
+          <t>Who we are</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>소개 굵은 줄</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
+          <t>에너지의 내일을 설계하는 Total Energy Solution Provider, 에이프로입니다.</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="8" t="n"/>
       <c r="I32" s="5" t="n"/>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[3]/section[3]/ol/li[1]/div/div/div/div/span|text</t>
+          <t>/html/body/div[3]/section[3]/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -41267,12 +41269,12 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Who we are · 01</t>
+          <t>Who we are</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>소개 문단</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -41283,19 +41285,15 @@
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>전력 변환 기술 기반의 Total Energy Solution</t>
+          <t>에이프로는 독보적인 전력 변환 및 정밀 제어 기술을 바탕으로 글로벌 친환경 에너지 산업의 성장을 이끄는 혁신 기업입니다. 배터리 제조 공정부터 차세대 모빌리티, 스마트 그리드에 이르기까지, 에너지가 생산되고 소비되는 모든 과정에 최적화된 통합 솔루션을 제공합니다.</t>
         </is>
       </c>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>Total Energy Solutions Powered by Advanced Power Conversion</t>
-        </is>
-      </c>
+      <c r="H33" s="8" t="n"/>
       <c r="I33" s="5" t="n"/>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[3]/section[3]/ol/li[1]/div/div/div/div/h3|text</t>
+          <t>/html/body/div[3]/section[3]/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -41310,30 +41308,26 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>문단</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E34" s="5" t="n"/>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>에이프로는 2차전지 활성화 공정 장비부터 ESS, 초고속 전기차 충전 인프라, 우주 발사체 전원 시스템까지 폭넓은 포트폴리오를 구축하고 있습니다. 끊임없는 연구개발을 통해 고효율, 고밀도 전력 변환 기술을 고도화하며 지속 가능한 미래 에너지 생태계를 완성해 나갑니다.</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO has built a comprehensive portfolio spanning secondary battery formation equipment, Energy Storage Systems (ESS), ultra-fast EV charging infrastructure, and power systems for space launch vehicles. Through continuous R&amp;D, we advance high-efficiency, high-density power conversion technologies to shape a sustainable future energy ecosystem.</t>
-        </is>
-      </c>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
       <c r="I34" s="5" t="n"/>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[3]/section[3]/ol/li[1]/div/div/div/p|text</t>
+          <t>/html/body/div[3]/section[3]/ol/li[1]/div/div/div/div/span|text</t>
         </is>
       </c>
     </row>
@@ -41343,31 +41337,35 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Who we are · 02</t>
+          <t>Who we are · 01</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>제목</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E35" s="5" t="n"/>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="6" t="n"/>
+          <t>전력 변환 기술 기반의 Total Energy Solution</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Total Energy Solutions Powered by Advanced Power Conversion</t>
+        </is>
+      </c>
       <c r="I35" s="5" t="n"/>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[3]/section[3]/ol/li[2]/div/div/div/div/span|text</t>
+          <t>/html/body/div[3]/section[3]/ol/li[1]/div/div/div/div/h3|text</t>
         </is>
       </c>
     </row>
@@ -41377,12 +41375,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Who we are · 02</t>
+          <t>Who we are · 01</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -41393,19 +41391,19 @@
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>소재부터 시스템까지 잇는 수직 계열화 역량 (Materials to System)</t>
+          <t>에이프로는 2차전지 활성화 공정 장비부터 ESS, 초고속 전기차 충전 인프라, 우주 발사체 전원 시스템까지 폭넓은 포트폴리오를 구축하고 있습니다. 끊임없는 연구개발을 통해 고효율, 고밀도 전력 변환 기술을 고도화하며 지속 가능한 미래 에너지 생태계를 완성해 나갑니다.</t>
         </is>
       </c>
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Vertical Integration: From Materials to Systems</t>
+          <t>A-PRO has built a comprehensive portfolio spanning secondary battery formation equipment, Energy Storage Systems (ESS), ultra-fast EV charging infrastructure, and power systems for space launch vehicles. Through continuous R&amp;D, we advance high-efficiency, high-density power conversion technologies to shape a sustainable future energy ecosystem.</t>
         </is>
       </c>
       <c r="I36" s="5" t="n"/>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[3]/section[3]/ol/li[2]/div/div/div/div/h3|text</t>
+          <t>/html/body/div[3]/section[3]/ol/li[1]/div/div/div/p|text</t>
         </is>
       </c>
     </row>
@@ -41420,30 +41418,26 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>문단</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E37" s="5" t="n"/>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>우리의 혁신은 시스템의 가장 깊은 곳, '반도체'에서 시작됩니다. 차세대 고효율 질화갈륨(GaN) 전력반도체 핵심 소재(Epi-Wafer)와 소자를 직접 설계하고 내재화함으로써, 기존의 한계를 뛰어넘는 초소형·초고효율 전력 변환 모듈을 실현합니다.</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Our innovation originates at the foundational level of systems—semiconductors. By designing and vertically integrating core next-generation Gallium Nitride (GaN) power semiconductor materials (Epi-Wafers) and devices in-house, we achieve ultra-compact, ultra-high-efficiency power conversion modules that surpass conventional limits.</t>
-        </is>
-      </c>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
       <c r="I37" s="5" t="n"/>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[3]/section[3]/ol/li[2]/div/div/div/p|text</t>
+          <t>/html/body/div[3]/section[3]/ol/li[2]/div/div/div/div/span|text</t>
         </is>
       </c>
     </row>
@@ -41453,31 +41447,35 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Who we are · 03</t>
+          <t>Who we are · 02</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>제목</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E38" s="5" t="n"/>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="6" t="n"/>
+          <t>소재부터 시스템까지 잇는 수직 계열화 역량 (Materials to System)</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Vertical Integration: From Materials to Systems</t>
+        </is>
+      </c>
       <c r="I38" s="5" t="n"/>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[3]/section[3]/ol/li[3]/div/div/div/div/span|text</t>
+          <t>/html/body/div[3]/section[3]/ol/li[2]/div/div/div/div/h3|text</t>
         </is>
       </c>
     </row>
@@ -41487,12 +41485,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Who we are · 03</t>
+          <t>Who we are · 02</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -41503,19 +41501,19 @@
       <c r="E39" s="5" t="n"/>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>In-house 설계를 통한 완벽한 시스템 통합 (SI) 및 지능형 플랫폼</t>
+          <t>우리의 혁신은 시스템의 가장 깊은 곳, '반도체'에서 시작됩니다. 차세대 고효율 질화갈륨(GaN) 전력반도체 핵심 소재(Epi-Wafer)와 소자를 직접 설계하고 내재화함으로써, 기존의 한계를 뛰어넘는 초소형·초고효율 전력 변환 모듈을 실현합니다.</t>
         </is>
       </c>
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>100% In-House System Integration (SI) &amp; Intelligent Platforms</t>
+          <t>Our innovation originates at the foundational level of systems—semiconductors. By designing and vertically integrating core next-generation Gallium Nitride (GaN) power semiconductor materials (Epi-Wafers) and devices in-house, we achieve ultra-compact, ultra-high-efficiency power conversion modules that surpass conventional limits.</t>
         </is>
       </c>
       <c r="I39" s="5" t="n"/>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[3]/section[3]/ol/li[3]/div/div/div/div/h3|text</t>
+          <t>/html/body/div[3]/section[3]/ol/li[2]/div/div/div/p|text</t>
         </is>
       </c>
     </row>
@@ -41530,30 +41528,26 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>문단</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E40" s="5" t="n"/>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>기구, 회로, 소프트웨어에 이르는 100% In-house 설계 역량을 통해 고객의 다양한 요구에 최적화된 하드웨어 시스템을 구축합니다. 나아가 AI 기반의 배터리 진단 플랫폼과 산업 안전 로보틱스 등 지능형 소프트웨어를 융합하여, 시스템의 안정성과 운영 효율을 극대화하는 스마트 솔루션을 제공합니다.</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>With full in-house engineering across mechanical, circuitry, and software domains, we engineer hardware systems precisely tailored to diverse customer needs. Furthermore, by integrating intelligent software—such as AI-driven battery diagnostics and industrial safety robotics—we deliver smart solutions that maximize operational efficiency and system reliability.</t>
-        </is>
-      </c>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
       <c r="I40" s="5" t="n"/>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[3]/section[3]/ol/li[3]/div/div/div/p|text</t>
+          <t>/html/body/div[3]/section[3]/ol/li[3]/div/div/div/div/span|text</t>
         </is>
       </c>
     </row>
@@ -41563,31 +41557,35 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Who we are · 04</t>
+          <t>Who we are · 03</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>제목</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E41" s="5" t="n"/>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="n"/>
-      <c r="H41" s="6" t="n"/>
+          <t>In-house 설계를 통한 완벽한 시스템 통합 (SI) 및 지능형 플랫폼</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>100% In-House System Integration (SI) &amp; Intelligent Platforms</t>
+        </is>
+      </c>
       <c r="I41" s="5" t="n"/>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[3]/section[3]/ol/li[4]/div/div/div/div/span|text</t>
+          <t>/html/body/div[3]/section[3]/ol/li[3]/div/div/div/div/h3|text</t>
         </is>
       </c>
     </row>
@@ -41597,12 +41595,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Who we are · 04</t>
+          <t>Who we are · 03</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -41613,19 +41611,19 @@
       <c r="E42" s="5" t="n"/>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>세계를 무대로 하는 글로벌 파트너</t>
+          <t>기구, 회로, 소프트웨어에 이르는 100% In-house 설계 역량을 통해 고객의 다양한 요구에 최적화된 하드웨어 시스템을 구축합니다. 나아가 AI 기반의 배터리 진단 플랫폼과 산업 안전 로보틱스 등 지능형 소프트웨어를 융합하여, 시스템의 안정성과 운영 효율을 극대화하는 스마트 솔루션을 제공합니다.</t>
         </is>
       </c>
       <c r="G42" s="7" t="n"/>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>A Trusted Global Partner with Worldwide Reach</t>
+          <t>With full in-house engineering across mechanical, circuitry, and software domains, we engineer hardware systems precisely tailored to diverse customer needs. Furthermore, by integrating intelligent software—such as AI-driven battery diagnostics and industrial safety robotics—we deliver smart solutions that maximize operational efficiency and system reliability.</t>
         </is>
       </c>
       <c r="I42" s="5" t="n"/>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[3]/section[3]/ol/li[4]/div/div/div/div/h3|text</t>
+          <t>/html/body/div[3]/section[3]/ol/li[3]/div/div/div/p|text</t>
         </is>
       </c>
     </row>
@@ -41640,30 +41638,26 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>문단</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E43" s="5" t="n"/>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>미국, 유럽, 중국, 동남아시아 등 전 세계 핵심 거점에 현지 법인과 전문가 네트워크를 구축했습니다. 글로벌 탑티어 배터리 제조사 및 완성차 기업들과 긴밀히 협력하며, 어떤 환경에서도 기민(Agile)하게 대응하고 최고 품질의 고객 지원을 약속합니다.</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="n"/>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t>We operate local subsidiaries and specialized networks across key global hubs in the United States, Europe, China, and Southeast Asia. Collaborating closely with world-leading battery manufacturers and automotive OEMs, we ensure agile responsiveness and deliver premium customer support in any operating environment.</t>
-        </is>
-      </c>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="6" t="n"/>
       <c r="I43" s="5" t="n"/>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[3]/section[3]/ol/li[4]/div/div/div/p|text</t>
+          <t>/html/body/div[3]/section[3]/ol/li[4]/div/div/div/div/span|text</t>
         </is>
       </c>
     </row>
@@ -41673,12 +41667,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Who we are · 04</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>섹션 제목</t>
+          <t>제목</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -41689,19 +41683,19 @@
       <c r="E44" s="5" t="n"/>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>세계를 무대로 하는 글로벌 파트너</t>
         </is>
       </c>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>A Trusted Global Partner with Worldwide Reach</t>
         </is>
       </c>
       <c r="I44" s="5" t="n"/>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[3]/section[4]/div[1]/div/h2|text</t>
+          <t>/html/body/div[3]/section[3]/ol/li[4]/div/div/div/div/h3|text</t>
         </is>
       </c>
     </row>
@@ -41711,12 +41705,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Who we are · 04</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>섹션 라벨</t>
+          <t>문단</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -41727,23 +41721,19 @@
       <c r="E45" s="5" t="n"/>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>미국, 유럽, 중국, 동남아시아 등 전 세계 핵심 거점에 현지 법인과 전문가 네트워크를 구축했습니다. 글로벌 탑티어 배터리 제조사 및 완성차 기업들과 긴밀히 협력하며, 어떤 환경에서도 기민(Agile)하게 대응하고 최고 품질의 고객 지원을 약속합니다.</t>
         </is>
       </c>
       <c r="G45" s="7" t="n"/>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>Press Release</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>영문: 옛 홈페이지 글</t>
-        </is>
-      </c>
+          <t>We operate local subsidiaries and specialized networks across key global hubs in the United States, Europe, China, and Southeast Asia. Collaborating closely with world-leading battery manufacturers and automotive OEMs, we ensure agile responsiveness and deliver premium customer support in any operating environment.</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="n"/>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[3]/section[4]/div[1]/div/h2/span|text</t>
+          <t>/html/body/div[3]/section[3]/ol/li[4]/div/div/div/p|text</t>
         </is>
       </c>
     </row>
@@ -41758,7 +41748,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>더보기 단추</t>
+          <t>섹션 제목</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -41769,15 +41759,19 @@
       <c r="E46" s="5" t="n"/>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>더보기</t>
+          <t>News</t>
         </is>
       </c>
       <c r="G46" s="7" t="n"/>
-      <c r="H46" s="8" t="n"/>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
       <c r="I46" s="5" t="n"/>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[3]/section[4]/div[1]/a|text</t>
+          <t>/html/body/div[3]/section[4]/div[1]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -41792,7 +41786,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>목록 '자세히 보기'</t>
+          <t>섹션 라벨</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -41803,22 +41797,98 @@
       <c r="E47" s="5" t="n"/>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>자세히 보기</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="G47" s="7" t="n"/>
       <c r="H47" s="8" t="inlineStr">
         <is>
+          <t>Press Release</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>영문: 옛 홈페이지 글</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[4]/div[1]/div/h2/span|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>더보기 단추</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>더보기</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n"/>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[4]/div[1]/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>목록 '자세히 보기'</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n"/>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
           <t>View More</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>같은 문구 5 곳 — 한 줄로 합침
 영문: 옛 홈페이지 글</t>
         </is>
       </c>
-      <c r="J47" s="9" t="inlineStr">
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[3]/section[4]/ul/li[1]/a/span[3]/span|text
 /html/body/div[3]/section[4]/ul/li[2]/a/span[3]/span|text
@@ -41829,7 +41899,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J47"/>
+  <autoFilter ref="A1:J49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -42675,7 +42745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>

--- a/content-export/국문영문글정리.xlsx
+++ b/content-export/국문영문글정리.xlsx
@@ -612,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B50"/>
+  <dimension ref="B1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -840,6 +840,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -875,6 +876,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -903,6 +905,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -41724,7 +41727,7 @@
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>SOLUTION</t>
+          <t>Solution</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -59527,7 +59530,7 @@
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>SOLUTION</t>
+          <t>Solution</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -69843,7 +69846,7 @@
       <c r="G14" s="7" t="n"/>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>SOLUTION</t>
+          <t>Solution</t>
         </is>
       </c>
       <c r="I14" s="5" t="n"/>

--- a/content-export/국문영문글정리.xlsx
+++ b/content-export/국문영문글정리.xlsx
@@ -612,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:F50"/>
+  <dimension ref="B1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -48940,7 +48940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -66468,13 +66468,13 @@
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>AI platform</t>
+          <t>AI Platform</t>
         </is>
       </c>
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>AI platform</t>
+          <t>AI Platform</t>
         </is>
       </c>
       <c r="I3" s="5" t="n"/>

--- a/content-export/국문영문글정리.xlsx
+++ b/content-export/국문영문글정리.xlsx
@@ -612,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H50"/>
+  <dimension ref="B1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -840,7 +840,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -876,7 +875,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -905,7 +903,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -43722,7 +43719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -48929,6 +48926,132 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="11" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>영문 보기 보충</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>화면 글 · 대체 글</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="n"/>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>자동입력 방지</t>
+        </is>
+      </c>
+      <c r="G124" s="13" t="n"/>
+      <c r="H124" s="14" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+      <c r="I124" s="11" t="inlineStr">
+        <is>
+          <t>영문 초벌 번역(Claude, 2026-10-08) — 검토 필요</t>
+        </is>
+      </c>
+      <c r="J124" s="11" t="inlineStr">
+        <is>
+          <t>i18n|보충</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="11" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>영문 보기 보충</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>화면 글 · 대체 글</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="n"/>
+      <c r="F125" s="12" t="inlineStr">
+        <is>
+          <t>로봇이 아닌지 확인을 마친 뒤 다시 눌러 주세요.</t>
+        </is>
+      </c>
+      <c r="G125" s="13" t="n"/>
+      <c r="H125" s="14" t="inlineStr">
+        <is>
+          <t>Please complete the verification, then press Submit again.</t>
+        </is>
+      </c>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
+          <t>영문 초벌 번역(Claude, 2026-10-08) — 검토 필요</t>
+        </is>
+      </c>
+      <c r="J125" s="11" t="inlineStr">
+        <is>
+          <t>i18n|보충</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="11" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>영문 보기 보충</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>화면 글 · 대체 글</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="n"/>
+      <c r="F126" s="12" t="inlineStr">
+        <is>
+          <t>로봇 확인을 불러오지 못했습니다. 새로고침한 뒤 다시 시도해 주세요.</t>
+        </is>
+      </c>
+      <c r="G126" s="13" t="n"/>
+      <c r="H126" s="14" t="inlineStr">
+        <is>
+          <t>The verification could not be loaded. Please refresh the page and try again.</t>
+        </is>
+      </c>
+      <c r="I126" s="11" t="inlineStr">
+        <is>
+          <t>영문 초벌 번역(Claude, 2026-10-08) — 검토 필요</t>
+        </is>
+      </c>
+      <c r="J126" s="11" t="inlineStr">
+        <is>
+          <t>i18n|보충</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -48940,7 +49063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>

--- a/content-export/국문영문글정리.xlsx
+++ b/content-export/국문영문글정리.xlsx
@@ -123,7 +123,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -163,6 +163,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F1FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9D9DE"/>
       </patternFill>
     </fill>
   </fills>
@@ -207,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -245,6 +250,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -612,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B50"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -921,6 +933,14 @@
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>비고에 '영문 초벌 번역(Claude)'이 적힌 칸은 제가 번역한 것이라 검토가 필요합니다. 고치면 다음에 다시 반영합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="n"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>순번 칸이 분홍색인 줄이 그 초벌 번역 줄입니다(2026-10-12, 모든 시트 437 줄). 검토를 마치신 줄은 순번 칸 색을 지우셔도 됩니다.</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1175,7 @@
       </c>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -1199,7 +1219,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -1241,7 +1261,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -1283,7 +1303,7 @@
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1327,7 +1347,7 @@
       </c>
     </row>
     <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1371,7 +1391,7 @@
       </c>
     </row>
     <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1415,7 +1435,7 @@
       </c>
     </row>
     <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1459,7 +1479,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1501,7 +1521,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1543,7 +1563,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1585,7 +1605,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1627,7 +1647,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1669,7 +1689,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1711,7 +1731,7 @@
       </c>
     </row>
     <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -2010,7 +2030,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -9557,7 +9577,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -9599,7 +9619,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -9759,7 +9779,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -9869,7 +9889,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -14170,7 +14190,7 @@
       </c>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -14214,7 +14234,7 @@
       </c>
     </row>
     <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -14343,7 +14363,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -14427,7 +14447,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -14469,7 +14489,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -14511,7 +14531,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -14553,7 +14573,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -14595,7 +14615,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -14637,7 +14657,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -14951,7 +14971,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="16" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -14993,7 +15013,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="16" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -15035,7 +15055,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="16" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -15077,7 +15097,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="16" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -15119,7 +15139,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="16" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -15161,7 +15181,7 @@
       </c>
     </row>
     <row r="28" ht="27" customHeight="1">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="16" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -15203,7 +15223,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="16" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -15659,7 +15679,7 @@
       </c>
     </row>
     <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -25264,7 +25284,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -25306,7 +25326,7 @@
       </c>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -25350,7 +25370,7 @@
       </c>
     </row>
     <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -25394,7 +25414,7 @@
       </c>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -25438,7 +25458,7 @@
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -25480,7 +25500,7 @@
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -25522,7 +25542,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -25564,7 +25584,7 @@
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -25606,7 +25626,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -25648,7 +25668,7 @@
       </c>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -25690,7 +25710,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -25732,7 +25752,7 @@
       </c>
     </row>
     <row r="14" ht="40.5" customHeight="1">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -25774,7 +25794,7 @@
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -25818,7 +25838,7 @@
       </c>
     </row>
     <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -25860,7 +25880,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -25902,7 +25922,7 @@
       </c>
     </row>
     <row r="18" ht="40.5" customHeight="1">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -25944,7 +25964,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -25986,7 +26006,7 @@
       </c>
     </row>
     <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -26028,7 +26048,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="16" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -26070,7 +26090,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="16" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -27501,7 +27521,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -27543,7 +27563,7 @@
       </c>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -27587,7 +27607,7 @@
       </c>
     </row>
     <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -27631,7 +27651,7 @@
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -27673,7 +27693,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -27715,7 +27735,7 @@
       </c>
     </row>
     <row r="8" ht="67.5" customHeight="1">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -27757,7 +27777,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -27799,7 +27819,7 @@
       </c>
     </row>
     <row r="10" ht="40.5" customHeight="1">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -27841,7 +27861,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -27883,7 +27903,7 @@
       </c>
     </row>
     <row r="12" ht="40.5" customHeight="1">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -27925,7 +27945,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -29913,7 +29933,7 @@
       </c>
     </row>
     <row r="69" ht="54" customHeight="1">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="16" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -29955,7 +29975,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="16" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -29997,7 +30017,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n">
+      <c r="A71" s="16" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -30039,7 +30059,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n">
+      <c r="A72" s="16" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -30081,7 +30101,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n">
+      <c r="A73" s="16" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -30123,7 +30143,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="n">
+      <c r="A74" s="16" t="n">
         <v>73</v>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -30165,7 +30185,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n">
+      <c r="A75" s="16" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -30207,7 +30227,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="n">
+      <c r="A76" s="16" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -30249,7 +30269,7 @@
       </c>
     </row>
     <row r="77" ht="108" customHeight="1">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="16" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -30291,7 +30311,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="n">
+      <c r="A78" s="16" t="n">
         <v>77</v>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -32264,7 +32284,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -32394,7 +32414,7 @@
       </c>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -32988,7 +33008,7 @@
       </c>
     </row>
     <row r="21" ht="108" customHeight="1">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="16" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -33030,7 +33050,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="16" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -35920,7 +35940,7 @@
       </c>
     </row>
     <row r="91" ht="27" customHeight="1">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="16" t="n">
         <v>90</v>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -36004,7 +36024,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n">
+      <c r="A93" s="16" t="n">
         <v>92</v>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -38847,7 +38867,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -38889,7 +38909,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -39107,7 +39127,7 @@
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -39151,7 +39171,7 @@
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -39193,7 +39213,7 @@
       </c>
     </row>
     <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -39665,7 +39685,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="16" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -39742,7 +39762,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="16" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -39784,7 +39804,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="16" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -39861,7 +39881,7 @@
       </c>
     </row>
     <row r="26" ht="40.5" customHeight="1">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="16" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -39903,7 +39923,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="16" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -39945,7 +39965,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="16" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -39987,7 +40007,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="16" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -40029,7 +40049,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="16" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -40071,7 +40091,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="16" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -40113,7 +40133,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="16" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -40155,7 +40175,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="16" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -40197,7 +40217,7 @@
       </c>
     </row>
     <row r="34" ht="27" customHeight="1">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="16" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -40239,7 +40259,7 @@
       </c>
     </row>
     <row r="35" ht="27" customHeight="1">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="16" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -40281,7 +40301,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="16" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -40323,7 +40343,7 @@
       </c>
     </row>
     <row r="37" ht="40.5" customHeight="1">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="16" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -40467,7 +40487,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="16" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -40551,7 +40571,7 @@
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="16" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -40783,7 +40803,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="16" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -40944,7 +40964,7 @@
       </c>
     </row>
     <row r="2" ht="27" customHeight="1">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -41020,7 +41040,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -41062,7 +41082,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -41104,7 +41124,7 @@
       </c>
     </row>
     <row r="6" ht="121.5" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -41151,7 +41171,7 @@
       </c>
     </row>
     <row r="7" ht="121.5" customHeight="1">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -41198,7 +41218,7 @@
       </c>
     </row>
     <row r="8" ht="121.5" customHeight="1">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -41407,7 +41427,7 @@
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -41492,7 +41512,7 @@
       </c>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -41535,7 +41555,7 @@
       </c>
     </row>
     <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -41774,7 +41794,7 @@
       </c>
     </row>
     <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="16" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -41817,7 +41837,7 @@
       </c>
     </row>
     <row r="23" ht="54" customHeight="1">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="16" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -42782,7 +42802,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="16" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -42990,7 +43010,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -43787,7 +43807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n">
+      <c r="A2" s="17" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="11" t="inlineStr">
@@ -43829,7 +43849,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n">
+      <c r="A3" s="17" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
@@ -43871,7 +43891,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n">
+      <c r="A4" s="17" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="inlineStr">
@@ -43913,7 +43933,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="17" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -43955,7 +43975,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="17" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="11" t="inlineStr">
@@ -43997,7 +44017,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="17" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -44039,7 +44059,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="17" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -44081,7 +44101,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="17" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
@@ -44123,7 +44143,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="17" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="11" t="inlineStr">
@@ -44165,7 +44185,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="17" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -44207,7 +44227,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="17" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -44249,7 +44269,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="17" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -44291,7 +44311,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="17" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -44333,7 +44353,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="17" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
@@ -44375,7 +44395,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="17" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="11" t="inlineStr">
@@ -44417,7 +44437,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="17" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -44459,7 +44479,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="17" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="11" t="inlineStr">
@@ -44501,7 +44521,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="17" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -44543,7 +44563,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="17" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="11" t="inlineStr">
@@ -44585,7 +44605,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="17" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
@@ -44627,7 +44647,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="17" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="11" t="inlineStr">
@@ -44669,7 +44689,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="17" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
@@ -44711,7 +44731,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="17" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="11" t="inlineStr">
@@ -44753,7 +44773,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="17" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -44795,7 +44815,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="17" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="11" t="inlineStr">
@@ -44837,7 +44857,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="17" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="11" t="inlineStr">
@@ -44879,7 +44899,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="17" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="11" t="inlineStr">
@@ -44921,7 +44941,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="17" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="11" t="inlineStr">
@@ -44963,7 +44983,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="17" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="11" t="inlineStr">
@@ -45005,7 +45025,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="17" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="11" t="inlineStr">
@@ -45047,7 +45067,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="17" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="11" t="inlineStr">
@@ -45089,7 +45109,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="17" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="11" t="inlineStr">
@@ -45131,7 +45151,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n">
+      <c r="A34" s="17" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="11" t="inlineStr">
@@ -45173,7 +45193,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n">
+      <c r="A35" s="17" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="11" t="inlineStr">
@@ -45215,7 +45235,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n">
+      <c r="A36" s="17" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="11" t="inlineStr">
@@ -45257,7 +45277,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n">
+      <c r="A37" s="17" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="11" t="inlineStr">
@@ -45299,7 +45319,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n">
+      <c r="A38" s="17" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="11" t="inlineStr">
@@ -45341,7 +45361,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n">
+      <c r="A39" s="17" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="11" t="inlineStr">
@@ -45383,7 +45403,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n">
+      <c r="A40" s="17" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="11" t="inlineStr">
@@ -45425,7 +45445,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n">
+      <c r="A41" s="17" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="11" t="inlineStr">
@@ -45467,7 +45487,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="n">
+      <c r="A42" s="17" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="11" t="inlineStr">
@@ -45509,7 +45529,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="n">
+      <c r="A43" s="17" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="11" t="inlineStr">
@@ -45551,7 +45571,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="n">
+      <c r="A44" s="17" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="11" t="inlineStr">
@@ -45593,7 +45613,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="n">
+      <c r="A45" s="17" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="11" t="inlineStr">
@@ -45635,7 +45655,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="n">
+      <c r="A46" s="17" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="11" t="inlineStr">
@@ -45679,7 +45699,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="n">
+      <c r="A47" s="17" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="11" t="inlineStr">
@@ -45721,7 +45741,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="n">
+      <c r="A48" s="17" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="11" t="inlineStr">
@@ -45763,7 +45783,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="n">
+      <c r="A49" s="17" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="11" t="inlineStr">
@@ -45805,7 +45825,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="n">
+      <c r="A50" s="17" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -45847,7 +45867,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="n">
+      <c r="A51" s="17" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -45889,7 +45909,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="n">
+      <c r="A52" s="17" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -45931,7 +45951,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="n">
+      <c r="A53" s="17" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -45973,7 +45993,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="11" t="n">
+      <c r="A54" s="17" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="11" t="inlineStr">
@@ -46015,7 +46035,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="n">
+      <c r="A55" s="17" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="11" t="inlineStr">
@@ -46057,7 +46077,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="n">
+      <c r="A56" s="17" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -46099,7 +46119,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="11" t="n">
+      <c r="A57" s="17" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="11" t="inlineStr">
@@ -46141,7 +46161,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="n">
+      <c r="A58" s="17" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="11" t="inlineStr">
@@ -46183,7 +46203,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="n">
+      <c r="A59" s="17" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="11" t="inlineStr">
@@ -46225,7 +46245,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="11" t="n">
+      <c r="A60" s="17" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -46267,7 +46287,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="n">
+      <c r="A61" s="17" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="11" t="inlineStr">
@@ -46309,7 +46329,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="11" t="n">
+      <c r="A62" s="17" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="11" t="inlineStr">
@@ -46351,7 +46371,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="11" t="n">
+      <c r="A63" s="17" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="11" t="inlineStr">
@@ -46393,7 +46413,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="11" t="n">
+      <c r="A64" s="17" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="11" t="inlineStr">
@@ -46435,7 +46455,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="11" t="n">
+      <c r="A65" s="17" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="11" t="inlineStr">
@@ -46477,7 +46497,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="11" t="n">
+      <c r="A66" s="17" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="11" t="inlineStr">
@@ -46519,7 +46539,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="11" t="n">
+      <c r="A67" s="17" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="11" t="inlineStr">
@@ -46561,7 +46581,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="11" t="n">
+      <c r="A68" s="17" t="n">
         <v>67</v>
       </c>
       <c r="B68" s="11" t="inlineStr">
@@ -46603,7 +46623,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="11" t="n">
+      <c r="A69" s="17" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="11" t="inlineStr">
@@ -46645,7 +46665,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="11" t="n">
+      <c r="A70" s="17" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="11" t="inlineStr">
@@ -46687,7 +46707,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="11" t="n">
+      <c r="A71" s="17" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="11" t="inlineStr">
@@ -46729,7 +46749,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="11" t="n">
+      <c r="A72" s="17" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="11" t="inlineStr">
@@ -46771,7 +46791,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="11" t="n">
+      <c r="A73" s="17" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="11" t="inlineStr">
@@ -46813,7 +46833,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="11" t="n">
+      <c r="A74" s="17" t="n">
         <v>73</v>
       </c>
       <c r="B74" s="11" t="inlineStr">
@@ -46855,7 +46875,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="11" t="n">
+      <c r="A75" s="17" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="11" t="inlineStr">
@@ -46897,7 +46917,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="11" t="n">
+      <c r="A76" s="17" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="11" t="inlineStr">
@@ -46939,7 +46959,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="11" t="n">
+      <c r="A77" s="17" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="11" t="inlineStr">
@@ -46981,7 +47001,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="11" t="n">
+      <c r="A78" s="17" t="n">
         <v>77</v>
       </c>
       <c r="B78" s="11" t="inlineStr">
@@ -47023,7 +47043,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="11" t="n">
+      <c r="A79" s="17" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="11" t="inlineStr">
@@ -47065,7 +47085,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="11" t="n">
+      <c r="A80" s="17" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="11" t="inlineStr">
@@ -47107,7 +47127,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="11" t="n">
+      <c r="A81" s="17" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="11" t="inlineStr">
@@ -47151,7 +47171,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="11" t="n">
+      <c r="A82" s="17" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="11" t="inlineStr">
@@ -47193,7 +47213,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="11" t="n">
+      <c r="A83" s="17" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="11" t="inlineStr">
@@ -47235,7 +47255,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="11" t="n">
+      <c r="A84" s="17" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="11" t="inlineStr">
@@ -47277,7 +47297,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="11" t="n">
+      <c r="A85" s="17" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="11" t="inlineStr">
@@ -47319,7 +47339,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="11" t="n">
+      <c r="A86" s="17" t="n">
         <v>85</v>
       </c>
       <c r="B86" s="11" t="inlineStr">
@@ -47361,7 +47381,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="11" t="n">
+      <c r="A87" s="17" t="n">
         <v>86</v>
       </c>
       <c r="B87" s="11" t="inlineStr">
@@ -47403,7 +47423,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="11" t="n">
+      <c r="A88" s="17" t="n">
         <v>87</v>
       </c>
       <c r="B88" s="11" t="inlineStr">
@@ -47445,7 +47465,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="11" t="n">
+      <c r="A89" s="17" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="11" t="inlineStr">
@@ -47487,7 +47507,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="11" t="n">
+      <c r="A90" s="17" t="n">
         <v>89</v>
       </c>
       <c r="B90" s="11" t="inlineStr">
@@ -47529,7 +47549,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="11" t="n">
+      <c r="A91" s="17" t="n">
         <v>90</v>
       </c>
       <c r="B91" s="11" t="inlineStr">
@@ -47571,7 +47591,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="11" t="n">
+      <c r="A92" s="17" t="n">
         <v>91</v>
       </c>
       <c r="B92" s="11" t="inlineStr">
@@ -47613,7 +47633,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="11" t="n">
+      <c r="A93" s="17" t="n">
         <v>92</v>
       </c>
       <c r="B93" s="11" t="inlineStr">
@@ -47655,7 +47675,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="11" t="n">
+      <c r="A94" s="17" t="n">
         <v>93</v>
       </c>
       <c r="B94" s="11" t="inlineStr">
@@ -47697,7 +47717,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="11" t="n">
+      <c r="A95" s="17" t="n">
         <v>94</v>
       </c>
       <c r="B95" s="11" t="inlineStr">
@@ -47739,7 +47759,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="11" t="n">
+      <c r="A96" s="17" t="n">
         <v>95</v>
       </c>
       <c r="B96" s="11" t="inlineStr">
@@ -47781,7 +47801,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="11" t="n">
+      <c r="A97" s="17" t="n">
         <v>96</v>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -47823,7 +47843,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="11" t="n">
+      <c r="A98" s="17" t="n">
         <v>97</v>
       </c>
       <c r="B98" s="11" t="inlineStr">
@@ -47865,7 +47885,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="11" t="n">
+      <c r="A99" s="17" t="n">
         <v>98</v>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -47907,7 +47927,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="11" t="n">
+      <c r="A100" s="17" t="n">
         <v>99</v>
       </c>
       <c r="B100" s="11" t="inlineStr">
@@ -47949,7 +47969,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="11" t="n">
+      <c r="A101" s="17" t="n">
         <v>100</v>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -47991,7 +48011,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="11" t="n">
+      <c r="A102" s="17" t="n">
         <v>101</v>
       </c>
       <c r="B102" s="11" t="inlineStr">
@@ -48033,7 +48053,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="11" t="n">
+      <c r="A103" s="17" t="n">
         <v>102</v>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -48075,7 +48095,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="11" t="n">
+      <c r="A104" s="17" t="n">
         <v>103</v>
       </c>
       <c r="B104" s="11" t="inlineStr">
@@ -48117,7 +48137,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="11" t="n">
+      <c r="A105" s="17" t="n">
         <v>104</v>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -48159,7 +48179,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="11" t="n">
+      <c r="A106" s="17" t="n">
         <v>105</v>
       </c>
       <c r="B106" s="11" t="inlineStr">
@@ -48201,7 +48221,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="11" t="n">
+      <c r="A107" s="17" t="n">
         <v>106</v>
       </c>
       <c r="B107" s="11" t="inlineStr">
@@ -48243,7 +48263,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="11" t="n">
+      <c r="A108" s="17" t="n">
         <v>107</v>
       </c>
       <c r="B108" s="11" t="inlineStr">
@@ -48285,7 +48305,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="11" t="n">
+      <c r="A109" s="17" t="n">
         <v>108</v>
       </c>
       <c r="B109" s="11" t="inlineStr">
@@ -48327,7 +48347,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="11" t="n">
+      <c r="A110" s="17" t="n">
         <v>109</v>
       </c>
       <c r="B110" s="11" t="inlineStr">
@@ -48369,7 +48389,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="11" t="n">
+      <c r="A111" s="17" t="n">
         <v>110</v>
       </c>
       <c r="B111" s="11" t="inlineStr">
@@ -48411,7 +48431,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="11" t="n">
+      <c r="A112" s="17" t="n">
         <v>111</v>
       </c>
       <c r="B112" s="11" t="inlineStr">
@@ -48453,7 +48473,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="11" t="n">
+      <c r="A113" s="17" t="n">
         <v>112</v>
       </c>
       <c r="B113" s="11" t="inlineStr">
@@ -48495,7 +48515,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="11" t="n">
+      <c r="A114" s="17" t="n">
         <v>113</v>
       </c>
       <c r="B114" s="11" t="inlineStr">
@@ -48537,7 +48557,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="11" t="n">
+      <c r="A115" s="17" t="n">
         <v>114</v>
       </c>
       <c r="B115" s="11" t="inlineStr">
@@ -48579,7 +48599,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="11" t="n">
+      <c r="A116" s="17" t="n">
         <v>115</v>
       </c>
       <c r="B116" s="11" t="inlineStr">
@@ -48623,7 +48643,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="11" t="n">
+      <c r="A117" s="17" t="n">
         <v>116</v>
       </c>
       <c r="B117" s="11" t="inlineStr">
@@ -48665,7 +48685,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="11" t="n">
+      <c r="A118" s="17" t="n">
         <v>117</v>
       </c>
       <c r="B118" s="11" t="inlineStr">
@@ -48709,7 +48729,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="11" t="n">
+      <c r="A119" s="17" t="n">
         <v>118</v>
       </c>
       <c r="B119" s="11" t="inlineStr">
@@ -48751,7 +48771,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="11" t="n">
+      <c r="A120" s="17" t="n">
         <v>119</v>
       </c>
       <c r="B120" s="11" t="inlineStr">
@@ -48795,7 +48815,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="11" t="n">
+      <c r="A121" s="17" t="n">
         <v>120</v>
       </c>
       <c r="B121" s="11" t="inlineStr">
@@ -48839,7 +48859,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="11" t="n">
+      <c r="A122" s="17" t="n">
         <v>121</v>
       </c>
       <c r="B122" s="11" t="inlineStr">
@@ -48883,7 +48903,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="11" t="n">
+      <c r="A123" s="17" t="n">
         <v>122</v>
       </c>
       <c r="B123" s="11" t="inlineStr">
@@ -48927,7 +48947,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="11" t="n">
+      <c r="A124" s="17" t="n">
         <v>123</v>
       </c>
       <c r="B124" s="11" t="inlineStr">
@@ -48969,7 +48989,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="11" t="n">
+      <c r="A125" s="17" t="n">
         <v>124</v>
       </c>
       <c r="B125" s="11" t="inlineStr">
@@ -49011,7 +49031,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="11" t="n">
+      <c r="A126" s="17" t="n">
         <v>125</v>
       </c>
       <c r="B126" s="11" t="inlineStr">
@@ -49348,7 +49368,7 @@
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -49391,7 +49411,7 @@
       </c>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -49434,7 +49454,7 @@
       </c>
     </row>
     <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -49520,7 +49540,7 @@
       </c>
     </row>
     <row r="7" ht="40.5" customHeight="1">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -49563,7 +49583,7 @@
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -50031,7 +50051,7 @@
       </c>
     </row>
     <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -50246,7 +50266,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="16" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -50288,7 +50308,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="16" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -50330,7 +50350,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="16" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -50372,7 +50392,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="16" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -50684,7 +50704,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="16" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -53729,7 +53749,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -53885,7 +53905,7 @@
       </c>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -53927,7 +53947,7 @@
       </c>
     </row>
     <row r="7" ht="27" customHeight="1">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -54016,7 +54036,7 @@
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -54060,7 +54080,7 @@
       </c>
     </row>
     <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -54542,7 +54562,7 @@
       </c>
     </row>
     <row r="22" ht="27" customHeight="1">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="16" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -54663,7 +54683,7 @@
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="16" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -55039,7 +55059,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="16" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -55081,7 +55101,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="16" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -55123,7 +55143,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="16" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -55165,7 +55185,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="16" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -55207,7 +55227,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="16" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -55249,7 +55269,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="16" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -55291,7 +55311,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="16" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -55333,7 +55353,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="16" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -55375,7 +55395,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="16" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -55417,7 +55437,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="16" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -55459,7 +55479,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="16" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -55501,7 +55521,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="16" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -55543,7 +55563,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="16" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -55585,7 +55605,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="16" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -55627,7 +55647,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="16" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -55669,7 +55689,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="16" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -55821,7 +55841,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="16" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -55897,7 +55917,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="16" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -55973,7 +55993,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="16" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -56087,7 +56107,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="16" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -56129,7 +56149,7 @@
       </c>
     </row>
     <row r="61" ht="22.5" customHeight="1">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="16" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -56205,7 +56225,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="16" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -56281,7 +56301,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="16" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -57159,7 +57179,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="n">
+      <c r="A88" s="16" t="n">
         <v>87</v>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -57201,7 +57221,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n">
+      <c r="A89" s="16" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -57243,7 +57263,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="n">
+      <c r="A90" s="16" t="n">
         <v>89</v>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -57285,7 +57305,7 @@
       </c>
     </row>
     <row r="91" ht="27" customHeight="1">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="16" t="n">
         <v>90</v>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -57327,7 +57347,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="n">
+      <c r="A92" s="16" t="n">
         <v>91</v>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -57369,7 +57389,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n">
+      <c r="A93" s="16" t="n">
         <v>92</v>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -57411,7 +57431,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="n">
+      <c r="A94" s="16" t="n">
         <v>93</v>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -57453,7 +57473,7 @@
       </c>
     </row>
     <row r="95" ht="27" customHeight="1">
-      <c r="A95" s="5" t="n">
+      <c r="A95" s="16" t="n">
         <v>94</v>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -57761,7 +57781,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n">
+      <c r="A103" s="16" t="n">
         <v>102</v>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -57803,7 +57823,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n">
+      <c r="A104" s="16" t="n">
         <v>103</v>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -57845,7 +57865,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n">
+      <c r="A105" s="16" t="n">
         <v>104</v>
       </c>
       <c r="B105" s="5" t="inlineStr">
@@ -57887,7 +57907,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="n">
+      <c r="A106" s="16" t="n">
         <v>105</v>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -57929,7 +57949,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n">
+      <c r="A107" s="16" t="n">
         <v>106</v>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -57971,7 +57991,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n">
+      <c r="A108" s="16" t="n">
         <v>107</v>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -58013,7 +58033,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="n">
+      <c r="A109" s="16" t="n">
         <v>108</v>
       </c>
       <c r="B109" s="5" t="inlineStr">
@@ -58055,7 +58075,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="n">
+      <c r="A110" s="16" t="n">
         <v>109</v>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -58097,7 +58117,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="n">
+      <c r="A111" s="16" t="n">
         <v>110</v>
       </c>
       <c r="B111" s="5" t="inlineStr">
@@ -58139,7 +58159,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="n">
+      <c r="A112" s="16" t="n">
         <v>111</v>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -58181,7 +58201,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="n">
+      <c r="A113" s="16" t="n">
         <v>112</v>
       </c>
       <c r="B113" s="5" t="inlineStr">
@@ -58223,7 +58243,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="n">
+      <c r="A114" s="16" t="n">
         <v>113</v>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -58265,7 +58285,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="n">
+      <c r="A115" s="16" t="n">
         <v>114</v>
       </c>
       <c r="B115" s="5" t="inlineStr">
@@ -58307,7 +58327,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="n">
+      <c r="A116" s="16" t="n">
         <v>115</v>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -58349,7 +58369,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="n">
+      <c r="A117" s="16" t="n">
         <v>116</v>
       </c>
       <c r="B117" s="5" t="inlineStr">
@@ -58501,7 +58521,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n">
+      <c r="A121" s="16" t="n">
         <v>120</v>
       </c>
       <c r="B121" s="5" t="inlineStr">
@@ -58577,7 +58597,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="n">
+      <c r="A123" s="16" t="n">
         <v>122</v>
       </c>
       <c r="B123" s="5" t="inlineStr">
@@ -58653,7 +58673,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="n">
+      <c r="A125" s="16" t="n">
         <v>124</v>
       </c>
       <c r="B125" s="5" t="inlineStr">
@@ -58729,7 +58749,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="n">
+      <c r="A127" s="16" t="n">
         <v>126</v>
       </c>
       <c r="B127" s="5" t="inlineStr">
@@ -58805,7 +58825,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="n">
+      <c r="A129" s="16" t="n">
         <v>128</v>
       </c>
       <c r="B129" s="5" t="inlineStr">
@@ -58995,7 +59015,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n">
+      <c r="A134" s="16" t="n">
         <v>133</v>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -59071,7 +59091,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="n">
+      <c r="A136" s="16" t="n">
         <v>135</v>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -59147,7 +59167,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="n">
+      <c r="A138" s="16" t="n">
         <v>137</v>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -59223,7 +59243,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="n">
+      <c r="A140" s="16" t="n">
         <v>139</v>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -59342,7 +59362,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -59498,7 +59518,7 @@
       </c>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -60235,7 +60255,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="16" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -60277,7 +60297,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="16" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -60319,7 +60339,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="16" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -60361,7 +60381,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="16" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -60403,7 +60423,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="16" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -60445,7 +60465,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="16" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -62740,7 +62760,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="16" t="n">
         <v>90</v>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -62782,7 +62802,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="n">
+      <c r="A92" s="16" t="n">
         <v>91</v>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -62824,7 +62844,7 @@
       </c>
     </row>
     <row r="93" ht="22.5" customHeight="1">
-      <c r="A93" s="5" t="n">
+      <c r="A93" s="16" t="n">
         <v>92</v>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -62866,7 +62886,7 @@
       </c>
     </row>
     <row r="94" ht="22.5" customHeight="1">
-      <c r="A94" s="5" t="n">
+      <c r="A94" s="16" t="n">
         <v>93</v>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -62908,7 +62928,7 @@
       </c>
     </row>
     <row r="95" ht="22.5" customHeight="1">
-      <c r="A95" s="5" t="n">
+      <c r="A95" s="16" t="n">
         <v>94</v>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -62950,7 +62970,7 @@
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
-      <c r="A96" s="5" t="n">
+      <c r="A96" s="16" t="n">
         <v>95</v>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -62992,7 +63012,7 @@
       </c>
     </row>
     <row r="97" ht="22.5" customHeight="1">
-      <c r="A97" s="5" t="n">
+      <c r="A97" s="16" t="n">
         <v>96</v>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -63034,7 +63054,7 @@
       </c>
     </row>
     <row r="98" ht="22.5" customHeight="1">
-      <c r="A98" s="5" t="n">
+      <c r="A98" s="16" t="n">
         <v>97</v>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -63076,7 +63096,7 @@
       </c>
     </row>
     <row r="99" ht="45" customHeight="1">
-      <c r="A99" s="5" t="n">
+      <c r="A99" s="16" t="n">
         <v>98</v>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -63120,7 +63140,7 @@
       </c>
     </row>
     <row r="100" ht="22.5" customHeight="1">
-      <c r="A100" s="5" t="n">
+      <c r="A100" s="16" t="n">
         <v>99</v>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -63162,7 +63182,7 @@
       </c>
     </row>
     <row r="101" ht="202.5" customHeight="1">
-      <c r="A101" s="5" t="n">
+      <c r="A101" s="16" t="n">
         <v>100</v>
       </c>
       <c r="B101" s="5" t="inlineStr">
@@ -63213,7 +63233,7 @@
       </c>
     </row>
     <row r="102" ht="202.5" customHeight="1">
-      <c r="A102" s="5" t="n">
+      <c r="A102" s="16" t="n">
         <v>101</v>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -63264,7 +63284,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n">
+      <c r="A103" s="16" t="n">
         <v>102</v>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -63306,7 +63326,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n">
+      <c r="A104" s="16" t="n">
         <v>103</v>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -63348,7 +63368,7 @@
       </c>
     </row>
     <row r="105" ht="45" customHeight="1">
-      <c r="A105" s="5" t="n">
+      <c r="A105" s="16" t="n">
         <v>104</v>
       </c>
       <c r="B105" s="5" t="inlineStr">
@@ -63392,7 +63412,7 @@
       </c>
     </row>
     <row r="106" ht="27" customHeight="1">
-      <c r="A106" s="5" t="n">
+      <c r="A106" s="16" t="n">
         <v>105</v>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -63434,7 +63454,7 @@
       </c>
     </row>
     <row r="107" ht="67.5" customHeight="1">
-      <c r="A107" s="5" t="n">
+      <c r="A107" s="16" t="n">
         <v>106</v>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -63479,7 +63499,7 @@
       </c>
     </row>
     <row r="108" ht="27" customHeight="1">
-      <c r="A108" s="5" t="n">
+      <c r="A108" s="16" t="n">
         <v>107</v>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -63521,7 +63541,7 @@
       </c>
     </row>
     <row r="109" ht="45" customHeight="1">
-      <c r="A109" s="5" t="n">
+      <c r="A109" s="16" t="n">
         <v>108</v>
       </c>
       <c r="B109" s="5" t="inlineStr">
@@ -63565,7 +63585,7 @@
       </c>
     </row>
     <row r="110" ht="45" customHeight="1">
-      <c r="A110" s="5" t="n">
+      <c r="A110" s="16" t="n">
         <v>109</v>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -63609,7 +63629,7 @@
       </c>
     </row>
     <row r="111" ht="45" customHeight="1">
-      <c r="A111" s="5" t="n">
+      <c r="A111" s="16" t="n">
         <v>110</v>
       </c>
       <c r="B111" s="5" t="inlineStr">
@@ -63653,7 +63673,7 @@
       </c>
     </row>
     <row r="112" ht="45" customHeight="1">
-      <c r="A112" s="5" t="n">
+      <c r="A112" s="16" t="n">
         <v>111</v>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -63731,7 +63751,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="n">
+      <c r="A114" s="16" t="n">
         <v>113</v>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -63811,7 +63831,7 @@
       </c>
     </row>
     <row r="116" ht="22.5" customHeight="1">
-      <c r="A116" s="5" t="n">
+      <c r="A116" s="16" t="n">
         <v>115</v>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -63853,7 +63873,7 @@
       </c>
     </row>
     <row r="117" ht="22.5" customHeight="1">
-      <c r="A117" s="5" t="n">
+      <c r="A117" s="16" t="n">
         <v>116</v>
       </c>
       <c r="B117" s="5" t="inlineStr">
@@ -63895,7 +63915,7 @@
       </c>
     </row>
     <row r="118" ht="22.5" customHeight="1">
-      <c r="A118" s="5" t="n">
+      <c r="A118" s="16" t="n">
         <v>117</v>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -63937,7 +63957,7 @@
       </c>
     </row>
     <row r="119" ht="27" customHeight="1">
-      <c r="A119" s="5" t="n">
+      <c r="A119" s="16" t="n">
         <v>118</v>
       </c>
       <c r="B119" s="5" t="inlineStr">
@@ -63979,7 +63999,7 @@
       </c>
     </row>
     <row r="120" ht="22.5" customHeight="1">
-      <c r="A120" s="5" t="n">
+      <c r="A120" s="16" t="n">
         <v>119</v>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -64021,7 +64041,7 @@
       </c>
     </row>
     <row r="121" ht="27" customHeight="1">
-      <c r="A121" s="5" t="n">
+      <c r="A121" s="16" t="n">
         <v>120</v>
       </c>
       <c r="B121" s="5" t="inlineStr">
@@ -64063,7 +64083,7 @@
       </c>
     </row>
     <row r="122" ht="22.5" customHeight="1">
-      <c r="A122" s="5" t="n">
+      <c r="A122" s="16" t="n">
         <v>121</v>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -64105,7 +64125,7 @@
       </c>
     </row>
     <row r="123" ht="22.5" customHeight="1">
-      <c r="A123" s="5" t="n">
+      <c r="A123" s="16" t="n">
         <v>122</v>
       </c>
       <c r="B123" s="5" t="inlineStr">
@@ -64147,7 +64167,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="n">
+      <c r="A124" s="16" t="n">
         <v>123</v>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -64227,7 +64247,7 @@
       </c>
     </row>
     <row r="126" ht="22.5" customHeight="1">
-      <c r="A126" s="5" t="n">
+      <c r="A126" s="16" t="n">
         <v>125</v>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -64269,7 +64289,7 @@
       </c>
     </row>
     <row r="127" ht="22.5" customHeight="1">
-      <c r="A127" s="5" t="n">
+      <c r="A127" s="16" t="n">
         <v>126</v>
       </c>
       <c r="B127" s="5" t="inlineStr">
@@ -64311,7 +64331,7 @@
       </c>
     </row>
     <row r="128" ht="22.5" customHeight="1">
-      <c r="A128" s="5" t="n">
+      <c r="A128" s="16" t="n">
         <v>127</v>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -64353,7 +64373,7 @@
       </c>
     </row>
     <row r="129" ht="27" customHeight="1">
-      <c r="A129" s="5" t="n">
+      <c r="A129" s="16" t="n">
         <v>128</v>
       </c>
       <c r="B129" s="5" t="inlineStr">
@@ -64395,7 +64415,7 @@
       </c>
     </row>
     <row r="130" ht="27" customHeight="1">
-      <c r="A130" s="5" t="n">
+      <c r="A130" s="16" t="n">
         <v>129</v>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -64437,7 +64457,7 @@
       </c>
     </row>
     <row r="131" ht="22.5" customHeight="1">
-      <c r="A131" s="5" t="n">
+      <c r="A131" s="16" t="n">
         <v>130</v>
       </c>
       <c r="B131" s="5" t="inlineStr">
@@ -64479,7 +64499,7 @@
       </c>
     </row>
     <row r="132" ht="27" customHeight="1">
-      <c r="A132" s="5" t="n">
+      <c r="A132" s="16" t="n">
         <v>131</v>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -64555,7 +64575,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n">
+      <c r="A134" s="16" t="n">
         <v>133</v>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -64635,7 +64655,7 @@
       </c>
     </row>
     <row r="136" ht="22.5" customHeight="1">
-      <c r="A136" s="5" t="n">
+      <c r="A136" s="16" t="n">
         <v>135</v>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -64677,7 +64697,7 @@
       </c>
     </row>
     <row r="137" ht="22.5" customHeight="1">
-      <c r="A137" s="5" t="n">
+      <c r="A137" s="16" t="n">
         <v>136</v>
       </c>
       <c r="B137" s="5" t="inlineStr">
@@ -64719,7 +64739,7 @@
       </c>
     </row>
     <row r="138" ht="22.5" customHeight="1">
-      <c r="A138" s="5" t="n">
+      <c r="A138" s="16" t="n">
         <v>137</v>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -64761,7 +64781,7 @@
       </c>
     </row>
     <row r="139" ht="27" customHeight="1">
-      <c r="A139" s="5" t="n">
+      <c r="A139" s="16" t="n">
         <v>138</v>
       </c>
       <c r="B139" s="5" t="inlineStr">
@@ -64803,7 +64823,7 @@
       </c>
     </row>
     <row r="140" ht="22.5" customHeight="1">
-      <c r="A140" s="5" t="n">
+      <c r="A140" s="16" t="n">
         <v>139</v>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -64845,7 +64865,7 @@
       </c>
     </row>
     <row r="141" ht="27" customHeight="1">
-      <c r="A141" s="5" t="n">
+      <c r="A141" s="16" t="n">
         <v>140</v>
       </c>
       <c r="B141" s="5" t="inlineStr">
@@ -64887,7 +64907,7 @@
       </c>
     </row>
     <row r="142" ht="27" customHeight="1">
-      <c r="A142" s="5" t="n">
+      <c r="A142" s="16" t="n">
         <v>141</v>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -64929,7 +64949,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="n">
+      <c r="A143" s="16" t="n">
         <v>142</v>
       </c>
       <c r="B143" s="5" t="inlineStr">
@@ -65009,7 +65029,7 @@
       </c>
     </row>
     <row r="145" ht="27" customHeight="1">
-      <c r="A145" s="5" t="n">
+      <c r="A145" s="16" t="n">
         <v>144</v>
       </c>
       <c r="B145" s="5" t="inlineStr">
@@ -65051,7 +65071,7 @@
       </c>
     </row>
     <row r="146" ht="27" customHeight="1">
-      <c r="A146" s="5" t="n">
+      <c r="A146" s="16" t="n">
         <v>145</v>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -65203,7 +65223,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="n">
+      <c r="A150" s="16" t="n">
         <v>149</v>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -65283,7 +65303,7 @@
       </c>
     </row>
     <row r="152" ht="22.5" customHeight="1">
-      <c r="A152" s="5" t="n">
+      <c r="A152" s="16" t="n">
         <v>151</v>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -65325,7 +65345,7 @@
       </c>
     </row>
     <row r="153" ht="27" customHeight="1">
-      <c r="A153" s="5" t="n">
+      <c r="A153" s="16" t="n">
         <v>152</v>
       </c>
       <c r="B153" s="5" t="inlineStr">
@@ -65367,7 +65387,7 @@
       </c>
     </row>
     <row r="154" ht="22.5" customHeight="1">
-      <c r="A154" s="5" t="n">
+      <c r="A154" s="16" t="n">
         <v>153</v>
       </c>
       <c r="B154" s="5" t="inlineStr">
@@ -65409,7 +65429,7 @@
       </c>
     </row>
     <row r="155" ht="27" customHeight="1">
-      <c r="A155" s="5" t="n">
+      <c r="A155" s="16" t="n">
         <v>154</v>
       </c>
       <c r="B155" s="5" t="inlineStr">
@@ -65451,7 +65471,7 @@
       </c>
     </row>
     <row r="156" ht="22.5" customHeight="1">
-      <c r="A156" s="5" t="n">
+      <c r="A156" s="16" t="n">
         <v>155</v>
       </c>
       <c r="B156" s="5" t="inlineStr">
@@ -65493,7 +65513,7 @@
       </c>
     </row>
     <row r="157" ht="27" customHeight="1">
-      <c r="A157" s="5" t="n">
+      <c r="A157" s="16" t="n">
         <v>156</v>
       </c>
       <c r="B157" s="5" t="inlineStr">
@@ -65535,7 +65555,7 @@
       </c>
     </row>
     <row r="158" ht="22.5" customHeight="1">
-      <c r="A158" s="5" t="n">
+      <c r="A158" s="16" t="n">
         <v>157</v>
       </c>
       <c r="B158" s="5" t="inlineStr">
@@ -65577,7 +65597,7 @@
       </c>
     </row>
     <row r="159" ht="27" customHeight="1">
-      <c r="A159" s="5" t="n">
+      <c r="A159" s="16" t="n">
         <v>158</v>
       </c>
       <c r="B159" s="5" t="inlineStr">
@@ -65619,7 +65639,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="5" t="n">
+      <c r="A160" s="16" t="n">
         <v>159</v>
       </c>
       <c r="B160" s="5" t="inlineStr">
@@ -65699,7 +65719,7 @@
       </c>
     </row>
     <row r="162" ht="22.5" customHeight="1">
-      <c r="A162" s="5" t="n">
+      <c r="A162" s="16" t="n">
         <v>161</v>
       </c>
       <c r="B162" s="5" t="inlineStr">
@@ -65741,7 +65761,7 @@
       </c>
     </row>
     <row r="163" ht="27" customHeight="1">
-      <c r="A163" s="5" t="n">
+      <c r="A163" s="16" t="n">
         <v>162</v>
       </c>
       <c r="B163" s="5" t="inlineStr">
@@ -65783,7 +65803,7 @@
       </c>
     </row>
     <row r="164" ht="22.5" customHeight="1">
-      <c r="A164" s="5" t="n">
+      <c r="A164" s="16" t="n">
         <v>163</v>
       </c>
       <c r="B164" s="5" t="inlineStr">
@@ -65825,7 +65845,7 @@
       </c>
     </row>
     <row r="165" ht="27" customHeight="1">
-      <c r="A165" s="5" t="n">
+      <c r="A165" s="16" t="n">
         <v>164</v>
       </c>
       <c r="B165" s="5" t="inlineStr">
@@ -65867,7 +65887,7 @@
       </c>
     </row>
     <row r="166" ht="22.5" customHeight="1">
-      <c r="A166" s="5" t="n">
+      <c r="A166" s="16" t="n">
         <v>165</v>
       </c>
       <c r="B166" s="5" t="inlineStr">
@@ -65909,7 +65929,7 @@
       </c>
     </row>
     <row r="167" ht="27" customHeight="1">
-      <c r="A167" s="5" t="n">
+      <c r="A167" s="16" t="n">
         <v>166</v>
       </c>
       <c r="B167" s="5" t="inlineStr">
@@ -65951,7 +65971,7 @@
       </c>
     </row>
     <row r="168" ht="22.5" customHeight="1">
-      <c r="A168" s="5" t="n">
+      <c r="A168" s="16" t="n">
         <v>167</v>
       </c>
       <c r="B168" s="5" t="inlineStr">
@@ -65993,7 +66013,7 @@
       </c>
     </row>
     <row r="169" ht="27" customHeight="1">
-      <c r="A169" s="5" t="n">
+      <c r="A169" s="16" t="n">
         <v>168</v>
       </c>
       <c r="B169" s="5" t="inlineStr">
@@ -66035,7 +66055,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="5" t="n">
+      <c r="A170" s="16" t="n">
         <v>169</v>
       </c>
       <c r="B170" s="5" t="inlineStr">
@@ -66115,7 +66135,7 @@
       </c>
     </row>
     <row r="172" ht="22.5" customHeight="1">
-      <c r="A172" s="5" t="n">
+      <c r="A172" s="16" t="n">
         <v>171</v>
       </c>
       <c r="B172" s="5" t="inlineStr">
@@ -66157,7 +66177,7 @@
       </c>
     </row>
     <row r="173" ht="27" customHeight="1">
-      <c r="A173" s="5" t="n">
+      <c r="A173" s="16" t="n">
         <v>172</v>
       </c>
       <c r="B173" s="5" t="inlineStr">
@@ -66199,7 +66219,7 @@
       </c>
     </row>
     <row r="174" ht="22.5" customHeight="1">
-      <c r="A174" s="5" t="n">
+      <c r="A174" s="16" t="n">
         <v>173</v>
       </c>
       <c r="B174" s="5" t="inlineStr">
@@ -66241,7 +66261,7 @@
       </c>
     </row>
     <row r="175" ht="27" customHeight="1">
-      <c r="A175" s="5" t="n">
+      <c r="A175" s="16" t="n">
         <v>174</v>
       </c>
       <c r="B175" s="5" t="inlineStr">
@@ -66283,7 +66303,7 @@
       </c>
     </row>
     <row r="176" ht="22.5" customHeight="1">
-      <c r="A176" s="5" t="n">
+      <c r="A176" s="16" t="n">
         <v>175</v>
       </c>
       <c r="B176" s="5" t="inlineStr">
@@ -66325,7 +66345,7 @@
       </c>
     </row>
     <row r="177" ht="27" customHeight="1">
-      <c r="A177" s="5" t="n">
+      <c r="A177" s="16" t="n">
         <v>176</v>
       </c>
       <c r="B177" s="5" t="inlineStr">
@@ -66367,7 +66387,7 @@
       </c>
     </row>
     <row r="178" ht="22.5" customHeight="1">
-      <c r="A178" s="5" t="n">
+      <c r="A178" s="16" t="n">
         <v>177</v>
       </c>
       <c r="B178" s="5" t="inlineStr">
@@ -66409,7 +66429,7 @@
       </c>
     </row>
     <row r="179" ht="27" customHeight="1">
-      <c r="A179" s="5" t="n">
+      <c r="A179" s="16" t="n">
         <v>178</v>
       </c>
       <c r="B179" s="5" t="inlineStr">
@@ -66528,7 +66548,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -66684,7 +66704,7 @@
       </c>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -66726,7 +66746,7 @@
       </c>
     </row>
     <row r="7" ht="27" customHeight="1">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -66770,7 +66790,7 @@
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -67287,7 +67307,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="16" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -67329,7 +67349,7 @@
       </c>
     </row>
     <row r="22" ht="27" customHeight="1">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="16" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -67371,7 +67391,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="16" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -67413,7 +67433,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="16" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -67455,7 +67475,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="16" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -67497,7 +67517,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="16" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -67539,7 +67559,7 @@
       </c>
     </row>
     <row r="27" ht="27" customHeight="1">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="16" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -67581,7 +67601,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="16" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -67927,7 +67947,7 @@
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="16" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -67969,7 +67989,7 @@
       </c>
     </row>
     <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="16" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -68586,7 +68606,7 @@
       </c>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -68899,7 +68919,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -68941,7 +68961,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -68983,7 +69003,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -69025,7 +69045,7 @@
       </c>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -69067,7 +69087,7 @@
       </c>
     </row>
     <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -69109,7 +69129,7 @@
       </c>
     </row>
     <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -69456,7 +69476,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -69498,7 +69518,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -69578,7 +69598,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -69658,7 +69678,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -69700,7 +69720,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -69742,7 +69762,7 @@
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -69786,7 +69806,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -69980,7 +70000,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -70060,7 +70080,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -70102,7 +70122,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -70418,7 +70438,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="16" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -70804,7 +70824,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -70924,7 +70944,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -71044,7 +71064,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="inlineStr">

--- a/content-export/국문영문글정리.xlsx
+++ b/content-export/국문영문글정리.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="9" activeTab="19" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
@@ -61,7 +61,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -120,10 +120,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -152,22 +163,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4F6F8"/>
+        <fgColor rgb="FFF4F6F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF6D6"/>
+        <fgColor rgb="FFFFF6D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F1FB"/>
+        <fgColor rgb="FFE8F1FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF9D9DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
       </patternFill>
     </fill>
   </fills>
@@ -196,23 +212,27 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D5DB"/>
+        <color rgb="FFD0D5DB"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D5DB"/>
+        <color rgb="FFD0D5DB"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D5DB"/>
+        <color rgb="FFD0D5DB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D5DB"/>
+        <color rgb="FFD0D5DB"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -259,9 +279,13 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="강조색5" xfId="1" builtinId="45"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -922,7 +946,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="27" customHeight="1">
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>페이지 영문 보기(KOR/ENG 단추)에 쓰는 글 중 다른 시트에 없는 것 — 메뉴 · 단추 · 사진 설명(대체 글) 등입니다. 엑셀이 이 글을 갖게 하려고 따로 모았습니다.</t>
@@ -1218,7 +1242,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="27" customHeight="1">
       <c r="A7" s="16" t="n">
         <v>6</v>
       </c>
@@ -1260,7 +1284,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="27" customHeight="1">
       <c r="A8" s="16" t="n">
         <v>7</v>
       </c>
@@ -1478,7 +1502,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="27" customHeight="1">
       <c r="A13" s="16" t="n">
         <v>12</v>
       </c>
@@ -1520,7 +1544,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="27" customHeight="1">
       <c r="A14" s="16" t="n">
         <v>13</v>
       </c>
@@ -1562,7 +1586,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="27" customHeight="1">
       <c r="A15" s="16" t="n">
         <v>14</v>
       </c>
@@ -1604,7 +1628,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="27" customHeight="1">
       <c r="A16" s="16" t="n">
         <v>15</v>
       </c>
@@ -1646,7 +1670,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="27" customHeight="1">
       <c r="A17" s="16" t="n">
         <v>16</v>
       </c>
@@ -1688,7 +1712,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="27" customHeight="1">
       <c r="A18" s="16" t="n">
         <v>17</v>
       </c>
@@ -2029,8 +2053,8 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="16" t="n">
+    <row r="3" ht="27" customHeight="1">
+      <c r="A3" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -2508,7 +2532,7 @@
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -2529,12 +2553,15 @@
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>자연이 숨 쉬게 하는 기술력으로
-더불어 사는 세상을 만들어 갑니다.</t>
+          <t>A-PRO의 미래 가치와 투명한 기업 정보를 공유합니다.</t>
         </is>
       </c>
       <c r="G3" s="7" t="n"/>
-      <c r="H3" s="8" t="n"/>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>We share A-PRO's future value and transparent corporate information.</t>
+        </is>
+      </c>
       <c r="I3" s="5" t="n"/>
       <c r="J3" s="9" t="inlineStr">
         <is>
@@ -9576,8 +9603,8 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="16" t="n">
+    <row r="3" ht="27" customHeight="1">
+      <c r="A3" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -9598,13 +9625,13 @@
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>투명하고 정확한 기업 정보를 적시에 공개합니다.</t>
+          <t>에이프로의 기업가치와 투자 정보를 투명하게 공개합니다.</t>
         </is>
       </c>
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>We disclose transparent and accurate corporate information in a timely manner.</t>
+          <t>We transparently disclose A-PRO's corporate value and investment information.</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -9618,7 +9645,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="27" customHeight="1">
       <c r="A4" s="16" t="n">
         <v>3</v>
       </c>
@@ -9778,7 +9805,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="27" customHeight="1">
       <c r="A8" s="16" t="n">
         <v>7</v>
       </c>
@@ -9888,7 +9915,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="27" customHeight="1">
       <c r="A11" s="16" t="n">
         <v>10</v>
       </c>
@@ -14148,7 +14175,7 @@
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -14169,13 +14196,13 @@
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>A-PRO의 미래 가치와 투명한 기업 정보를 공유합니다.</t>
+          <t>실시간 주가 정보와 시장 현황을 확인하실 수 있습니다.</t>
         </is>
       </c>
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>We share A-PRO's future value and transparent corporate information.</t>
+          <t>You can check real-time stock price and market status.</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -14362,7 +14389,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="27" customHeight="1">
       <c r="A8" s="16" t="n">
         <v>7</v>
       </c>
@@ -14446,7 +14473,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="27" customHeight="1">
       <c r="A10" s="16" t="n">
         <v>9</v>
       </c>
@@ -14488,7 +14515,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="27" customHeight="1">
       <c r="A11" s="16" t="n">
         <v>10</v>
       </c>
@@ -14530,7 +14557,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="27" customHeight="1">
       <c r="A12" s="16" t="n">
         <v>11</v>
       </c>
@@ -14572,7 +14599,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="27" customHeight="1">
       <c r="A13" s="16" t="n">
         <v>12</v>
       </c>
@@ -14614,7 +14641,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="27" customHeight="1">
       <c r="A14" s="16" t="n">
         <v>13</v>
       </c>
@@ -14656,7 +14683,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="27" customHeight="1">
       <c r="A15" s="16" t="n">
         <v>14</v>
       </c>
@@ -14970,7 +14997,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="27" customHeight="1">
       <c r="A23" s="16" t="n">
         <v>22</v>
       </c>
@@ -15012,7 +15039,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="27" customHeight="1">
       <c r="A24" s="16" t="n">
         <v>23</v>
       </c>
@@ -15054,7 +15081,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="27" customHeight="1">
       <c r="A25" s="16" t="n">
         <v>24</v>
       </c>
@@ -15096,7 +15123,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="27" customHeight="1">
       <c r="A26" s="16" t="n">
         <v>25</v>
       </c>
@@ -15138,7 +15165,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="27" customHeight="1">
       <c r="A27" s="16" t="n">
         <v>26</v>
       </c>
@@ -15222,7 +15249,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="27" customHeight="1">
       <c r="A29" s="16" t="n">
         <v>28</v>
       </c>
@@ -25283,7 +25310,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="27" customHeight="1">
       <c r="A3" s="16" t="n">
         <v>2</v>
       </c>
@@ -25541,7 +25568,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="27" customHeight="1">
       <c r="A9" s="16" t="n">
         <v>8</v>
       </c>
@@ -25625,7 +25652,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="27" customHeight="1">
       <c r="A11" s="16" t="n">
         <v>10</v>
       </c>
@@ -25709,7 +25736,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="27" customHeight="1">
       <c r="A13" s="16" t="n">
         <v>12</v>
       </c>
@@ -25879,7 +25906,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="27" customHeight="1">
       <c r="A17" s="16" t="n">
         <v>16</v>
       </c>
@@ -25963,7 +25990,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="27" customHeight="1">
       <c r="A19" s="16" t="n">
         <v>18</v>
       </c>
@@ -26047,7 +26074,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="27" customHeight="1">
       <c r="A21" s="16" t="n">
         <v>20</v>
       </c>
@@ -26089,7 +26116,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="27" customHeight="1">
       <c r="A22" s="16" t="n">
         <v>21</v>
       </c>
@@ -27520,7 +27547,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="27" customHeight="1">
       <c r="A3" s="16" t="n">
         <v>2</v>
       </c>
@@ -27692,7 +27719,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="27" customHeight="1">
       <c r="A7" s="16" t="n">
         <v>6</v>
       </c>
@@ -27776,7 +27803,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="27" customHeight="1">
       <c r="A9" s="16" t="n">
         <v>8</v>
       </c>
@@ -27860,7 +27887,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="27" customHeight="1">
       <c r="A11" s="16" t="n">
         <v>10</v>
       </c>
@@ -27944,7 +27971,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="27" customHeight="1">
       <c r="A13" s="16" t="n">
         <v>12</v>
       </c>
@@ -29974,7 +30001,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="27" customHeight="1">
       <c r="A70" s="16" t="n">
         <v>69</v>
       </c>
@@ -30016,7 +30043,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="27" customHeight="1">
       <c r="A71" s="16" t="n">
         <v>70</v>
       </c>
@@ -30058,7 +30085,7 @@
         </is>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="27" customHeight="1">
       <c r="A72" s="16" t="n">
         <v>71</v>
       </c>
@@ -30100,7 +30127,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="27" customHeight="1">
       <c r="A73" s="16" t="n">
         <v>72</v>
       </c>
@@ -30142,7 +30169,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="27" customHeight="1">
       <c r="A74" s="16" t="n">
         <v>73</v>
       </c>
@@ -30184,7 +30211,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="27" customHeight="1">
       <c r="A75" s="16" t="n">
         <v>74</v>
       </c>
@@ -30226,7 +30253,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="27" customHeight="1">
       <c r="A76" s="16" t="n">
         <v>75</v>
       </c>
@@ -30310,7 +30337,7 @@
         </is>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="27" customHeight="1">
       <c r="A78" s="16" t="n">
         <v>77</v>
       </c>
@@ -32283,7 +32310,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="27" customHeight="1">
       <c r="A3" s="16" t="n">
         <v>2</v>
       </c>
@@ -33049,7 +33076,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="27" customHeight="1">
       <c r="A22" s="16" t="n">
         <v>21</v>
       </c>
@@ -36023,7 +36050,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="27" customHeight="1">
       <c r="A93" s="16" t="n">
         <v>92</v>
       </c>
@@ -38866,7 +38893,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="27" customHeight="1">
       <c r="A2" s="16" t="n">
         <v>1</v>
       </c>
@@ -38894,7 +38921,7 @@
       <c r="G2" s="7" t="n"/>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Reporting Channels</t>
+          <t>Reporting Center</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -38908,7 +38935,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="27" customHeight="1">
       <c r="A3" s="16" t="n">
         <v>2</v>
       </c>
@@ -39684,7 +39711,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="27" customHeight="1">
       <c r="A21" s="16" t="n">
         <v>20</v>
       </c>
@@ -39761,7 +39788,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="27" customHeight="1">
       <c r="A23" s="16" t="n">
         <v>22</v>
       </c>
@@ -39803,7 +39830,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="27" customHeight="1">
       <c r="A24" s="16" t="n">
         <v>23</v>
       </c>
@@ -39922,7 +39949,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="27" customHeight="1">
       <c r="A27" s="16" t="n">
         <v>26</v>
       </c>
@@ -39964,7 +39991,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="27" customHeight="1">
       <c r="A28" s="16" t="n">
         <v>27</v>
       </c>
@@ -40006,7 +40033,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="27" customHeight="1">
       <c r="A29" s="16" t="n">
         <v>28</v>
       </c>
@@ -40048,7 +40075,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="27" customHeight="1">
       <c r="A30" s="16" t="n">
         <v>29</v>
       </c>
@@ -40090,7 +40117,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="27" customHeight="1">
       <c r="A31" s="16" t="n">
         <v>30</v>
       </c>
@@ -40132,7 +40159,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="27" customHeight="1">
       <c r="A32" s="16" t="n">
         <v>31</v>
       </c>
@@ -40174,7 +40201,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="27" customHeight="1">
       <c r="A33" s="16" t="n">
         <v>32</v>
       </c>
@@ -40300,7 +40327,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="27" customHeight="1">
       <c r="A36" s="16" t="n">
         <v>35</v>
       </c>
@@ -40486,7 +40513,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="27" customHeight="1">
       <c r="A41" s="16" t="n">
         <v>40</v>
       </c>
@@ -40802,7 +40829,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="27" customHeight="1">
       <c r="A49" s="16" t="n">
         <v>48</v>
       </c>
@@ -41039,7 +41066,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="27" customHeight="1">
       <c r="A4" s="16" t="n">
         <v>3</v>
       </c>
@@ -41081,8 +41108,8 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="16" t="n">
+    <row r="5" ht="27" customHeight="1">
+      <c r="A5" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -41124,7 +41151,7 @@
       </c>
     </row>
     <row r="6" ht="121.5" customHeight="1">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -41151,7 +41178,7 @@
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Smart Manufacturing</t>
+          <t>Smart Factory</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -41171,7 +41198,7 @@
       </c>
     </row>
     <row r="7" ht="121.5" customHeight="1">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -41218,7 +41245,7 @@
       </c>
     </row>
     <row r="8" ht="121.5" customHeight="1">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -41265,7 +41292,7 @@
       </c>
     </row>
     <row r="9" ht="135" customHeight="1">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -41292,7 +41319,7 @@
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Compound Power Semiconductors</t>
+          <t>Compound GaN Semiconductors</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -41418,7 +41445,12 @@
         </is>
       </c>
       <c r="G12" s="7" t="n"/>
-      <c r="H12" s="8" t="n"/>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>We develop and manufacture core equipment for the secondary battery activation process using our proprietary technologies.
+A-PRO takes full ownership of the final process that determines cell performance and quality.</t>
+        </is>
+      </c>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="9" t="inlineStr">
         <is>
@@ -41427,7 +41459,7 @@
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="16" t="n">
+      <c r="A13" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -41454,7 +41486,7 @@
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Battery Formation</t>
+          <t>Secondary Battery Activation</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -41512,7 +41544,7 @@
       </c>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -41539,7 +41571,7 @@
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>Automation Systems</t>
+          <t>Automation System</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -41582,7 +41614,7 @@
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Battery Materials</t>
+          <t>Secondary Battery Materials</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -42801,7 +42833,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="27" customHeight="1">
       <c r="A48" s="16" t="n">
         <v>47</v>
       </c>
@@ -43009,7 +43041,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="27" customHeight="1">
       <c r="A3" s="16" t="n">
         <v>2</v>
       </c>
@@ -43740,16 +43772,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J126"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="54" customWidth="1" min="6" max="6"/>
-    <col width="54" customWidth="1" min="7" max="7"/>
-    <col width="54" customWidth="1" min="8" max="8"/>
+    <col width="54" customWidth="1" min="6" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
@@ -43806,7 +43836,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="27" customHeight="1">
       <c r="A2" s="17" t="n">
         <v>1</v>
       </c>
@@ -43834,7 +43864,7 @@
       <c r="G2" s="13" t="n"/>
       <c r="H2" s="14" t="inlineStr">
         <is>
-          <t>Compound Power Semiconductors</t>
+          <t>Compound GaN Semiconductors</t>
         </is>
       </c>
       <c r="I2" s="11" t="inlineStr">
@@ -43848,7 +43878,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="27" customHeight="1">
       <c r="A3" s="17" t="n">
         <v>2</v>
       </c>
@@ -43890,7 +43920,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="27" customHeight="1">
       <c r="A4" s="17" t="n">
         <v>3</v>
       </c>
@@ -43918,7 +43948,7 @@
       <c r="G4" s="13" t="n"/>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>About</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
@@ -43932,7 +43962,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="27" customHeight="1">
       <c r="A5" s="17" t="n">
         <v>4</v>
       </c>
@@ -43974,7 +44004,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="27" customHeight="1">
       <c r="A6" s="17" t="n">
         <v>5</v>
       </c>
@@ -44016,7 +44046,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="27" customHeight="1">
       <c r="A7" s="17" t="n">
         <v>6</v>
       </c>
@@ -44058,7 +44088,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="27" customHeight="1">
       <c r="A8" s="17" t="n">
         <v>7</v>
       </c>
@@ -44100,7 +44130,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="27" customHeight="1">
       <c r="A9" s="17" t="n">
         <v>8</v>
       </c>
@@ -44142,7 +44172,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="27" customHeight="1">
       <c r="A10" s="17" t="n">
         <v>9</v>
       </c>
@@ -44184,7 +44214,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="27" customHeight="1">
       <c r="A11" s="17" t="n">
         <v>10</v>
       </c>
@@ -44226,7 +44256,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="27" customHeight="1">
       <c r="A12" s="17" t="n">
         <v>11</v>
       </c>
@@ -44268,7 +44298,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="27" customHeight="1">
       <c r="A13" s="17" t="n">
         <v>12</v>
       </c>
@@ -44310,7 +44340,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="27" customHeight="1">
       <c r="A14" s="17" t="n">
         <v>13</v>
       </c>
@@ -44352,7 +44382,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="27" customHeight="1">
       <c r="A15" s="17" t="n">
         <v>14</v>
       </c>
@@ -44394,7 +44424,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="27" customHeight="1">
       <c r="A16" s="17" t="n">
         <v>15</v>
       </c>
@@ -44436,7 +44466,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="27" customHeight="1">
       <c r="A17" s="17" t="n">
         <v>16</v>
       </c>
@@ -44478,7 +44508,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="27" customHeight="1">
       <c r="A18" s="17" t="n">
         <v>17</v>
       </c>
@@ -44520,7 +44550,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="27" customHeight="1">
       <c r="A19" s="17" t="n">
         <v>18</v>
       </c>
@@ -44562,7 +44592,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="27" customHeight="1">
       <c r="A20" s="17" t="n">
         <v>19</v>
       </c>
@@ -44604,7 +44634,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="27" customHeight="1">
       <c r="A21" s="17" t="n">
         <v>20</v>
       </c>
@@ -44646,7 +44676,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="27" customHeight="1">
       <c r="A22" s="17" t="n">
         <v>21</v>
       </c>
@@ -44688,7 +44718,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="27" customHeight="1">
       <c r="A23" s="17" t="n">
         <v>22</v>
       </c>
@@ -44730,7 +44760,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="27" customHeight="1">
       <c r="A24" s="17" t="n">
         <v>23</v>
       </c>
@@ -44772,7 +44802,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="27" customHeight="1">
       <c r="A25" s="17" t="n">
         <v>24</v>
       </c>
@@ -44814,7 +44844,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="27" customHeight="1">
       <c r="A26" s="17" t="n">
         <v>25</v>
       </c>
@@ -44856,7 +44886,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="27" customHeight="1">
       <c r="A27" s="17" t="n">
         <v>26</v>
       </c>
@@ -44898,7 +44928,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="27" customHeight="1">
       <c r="A28" s="17" t="n">
         <v>27</v>
       </c>
@@ -44940,7 +44970,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="27" customHeight="1">
       <c r="A29" s="17" t="n">
         <v>28</v>
       </c>
@@ -44982,7 +45012,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="27" customHeight="1">
       <c r="A30" s="17" t="n">
         <v>29</v>
       </c>
@@ -45024,7 +45054,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="27" customHeight="1">
       <c r="A31" s="17" t="n">
         <v>30</v>
       </c>
@@ -45066,7 +45096,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="27" customHeight="1">
       <c r="A32" s="17" t="n">
         <v>31</v>
       </c>
@@ -45108,7 +45138,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="27" customHeight="1">
       <c r="A33" s="17" t="n">
         <v>32</v>
       </c>
@@ -45150,7 +45180,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="27" customHeight="1">
       <c r="A34" s="17" t="n">
         <v>33</v>
       </c>
@@ -45192,7 +45222,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="27" customHeight="1">
       <c r="A35" s="17" t="n">
         <v>34</v>
       </c>
@@ -45220,7 +45250,7 @@
       <c r="G35" s="13" t="n"/>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Smart Manufacturing categories</t>
+          <t>Smart Factory categories</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -45234,7 +45264,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="27" customHeight="1">
       <c r="A36" s="17" t="n">
         <v>35</v>
       </c>
@@ -45276,7 +45306,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="27" customHeight="1">
       <c r="A37" s="17" t="n">
         <v>36</v>
       </c>
@@ -45318,7 +45348,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="27" customHeight="1">
       <c r="A38" s="17" t="n">
         <v>37</v>
       </c>
@@ -45360,7 +45390,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="27" customHeight="1">
       <c r="A39" s="17" t="n">
         <v>38</v>
       </c>
@@ -45402,7 +45432,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="27" customHeight="1">
       <c r="A40" s="17" t="n">
         <v>39</v>
       </c>
@@ -45444,7 +45474,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="27" customHeight="1">
       <c r="A41" s="17" t="n">
         <v>40</v>
       </c>
@@ -45486,7 +45516,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="27" customHeight="1">
       <c r="A42" s="17" t="n">
         <v>41</v>
       </c>
@@ -45528,7 +45558,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="27" customHeight="1">
       <c r="A43" s="17" t="n">
         <v>42</v>
       </c>
@@ -45570,7 +45600,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="27" customHeight="1">
       <c r="A44" s="17" t="n">
         <v>43</v>
       </c>
@@ -45612,7 +45642,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="27" customHeight="1">
       <c r="A45" s="17" t="n">
         <v>44</v>
       </c>
@@ -45640,7 +45670,7 @@
       <c r="G45" s="13" t="n"/>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Compound Power Semiconductors overview</t>
+          <t>Compound GaN Semiconductors overview</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
@@ -45654,7 +45684,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="27" customHeight="1">
       <c r="A46" s="17" t="n">
         <v>45</v>
       </c>
@@ -45698,7 +45728,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="27" customHeight="1">
       <c r="A47" s="17" t="n">
         <v>46</v>
       </c>
@@ -45740,7 +45770,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="27" customHeight="1">
       <c r="A48" s="17" t="n">
         <v>47</v>
       </c>
@@ -45768,7 +45798,7 @@
       <c r="G48" s="13" t="n"/>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Smart Manufacturing overview</t>
+          <t>Smart Factory overview</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -45782,7 +45812,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="27" customHeight="1">
       <c r="A49" s="17" t="n">
         <v>48</v>
       </c>
@@ -45824,7 +45854,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="27" customHeight="1">
       <c r="A50" s="17" t="n">
         <v>49</v>
       </c>
@@ -45866,7 +45896,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="54" customHeight="1">
       <c r="A51" s="17" t="n">
         <v>50</v>
       </c>
@@ -45908,7 +45938,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="27" customHeight="1">
       <c r="A52" s="17" t="n">
         <v>51</v>
       </c>
@@ -45950,7 +45980,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="27" customHeight="1">
       <c r="A53" s="17" t="n">
         <v>52</v>
       </c>
@@ -45992,7 +46022,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="27" customHeight="1">
       <c r="A54" s="17" t="n">
         <v>53</v>
       </c>
@@ -46034,7 +46064,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="27" customHeight="1">
       <c r="A55" s="17" t="n">
         <v>54</v>
       </c>
@@ -46076,7 +46106,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="27" customHeight="1">
       <c r="A56" s="17" t="n">
         <v>55</v>
       </c>
@@ -46118,7 +46148,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="27" customHeight="1">
       <c r="A57" s="17" t="n">
         <v>56</v>
       </c>
@@ -46160,7 +46190,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="27" customHeight="1">
       <c r="A58" s="17" t="n">
         <v>57</v>
       </c>
@@ -46202,7 +46232,7 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="27" customHeight="1">
       <c r="A59" s="17" t="n">
         <v>58</v>
       </c>
@@ -46244,7 +46274,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="40.5" customHeight="1">
       <c r="A60" s="17" t="n">
         <v>59</v>
       </c>
@@ -46286,7 +46316,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="27" customHeight="1">
       <c r="A61" s="17" t="n">
         <v>60</v>
       </c>
@@ -46328,7 +46358,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="27" customHeight="1">
       <c r="A62" s="17" t="n">
         <v>61</v>
       </c>
@@ -46370,7 +46400,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="27" customHeight="1">
       <c r="A63" s="17" t="n">
         <v>62</v>
       </c>
@@ -46412,7 +46442,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="27" customHeight="1">
       <c r="A64" s="17" t="n">
         <v>63</v>
       </c>
@@ -46454,7 +46484,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="27" customHeight="1">
       <c r="A65" s="17" t="n">
         <v>64</v>
       </c>
@@ -46496,7 +46526,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="27" customHeight="1">
       <c r="A66" s="17" t="n">
         <v>65</v>
       </c>
@@ -46538,7 +46568,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="27" customHeight="1">
       <c r="A67" s="17" t="n">
         <v>66</v>
       </c>
@@ -46580,7 +46610,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="27" customHeight="1">
       <c r="A68" s="17" t="n">
         <v>67</v>
       </c>
@@ -46622,7 +46652,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="27" customHeight="1">
       <c r="A69" s="17" t="n">
         <v>68</v>
       </c>
@@ -46664,7 +46694,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="27" customHeight="1">
       <c r="A70" s="17" t="n">
         <v>69</v>
       </c>
@@ -46706,7 +46736,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="27" customHeight="1">
       <c r="A71" s="17" t="n">
         <v>70</v>
       </c>
@@ -46748,7 +46778,7 @@
         </is>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="54" customHeight="1">
       <c r="A72" s="17" t="n">
         <v>71</v>
       </c>
@@ -46790,7 +46820,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="27" customHeight="1">
       <c r="A73" s="17" t="n">
         <v>72</v>
       </c>
@@ -46832,7 +46862,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="27" customHeight="1">
       <c r="A74" s="17" t="n">
         <v>73</v>
       </c>
@@ -46874,7 +46904,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="27" customHeight="1">
       <c r="A75" s="17" t="n">
         <v>74</v>
       </c>
@@ -46916,7 +46946,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="27" customHeight="1">
       <c r="A76" s="17" t="n">
         <v>75</v>
       </c>
@@ -46958,7 +46988,7 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="27" customHeight="1">
       <c r="A77" s="17" t="n">
         <v>76</v>
       </c>
@@ -47000,7 +47030,7 @@
         </is>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="27" customHeight="1">
       <c r="A78" s="17" t="n">
         <v>77</v>
       </c>
@@ -47042,7 +47072,7 @@
         </is>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="27" customHeight="1">
       <c r="A79" s="17" t="n">
         <v>78</v>
       </c>
@@ -47084,7 +47114,7 @@
         </is>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="27" customHeight="1">
       <c r="A80" s="17" t="n">
         <v>79</v>
       </c>
@@ -47126,7 +47156,7 @@
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="27" customHeight="1">
       <c r="A81" s="17" t="n">
         <v>80</v>
       </c>
@@ -47170,7 +47200,7 @@
         </is>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="27" customHeight="1">
       <c r="A82" s="17" t="n">
         <v>81</v>
       </c>
@@ -47212,7 +47242,7 @@
         </is>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="27" customHeight="1">
       <c r="A83" s="17" t="n">
         <v>82</v>
       </c>
@@ -47254,7 +47284,7 @@
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="27" customHeight="1">
       <c r="A84" s="17" t="n">
         <v>83</v>
       </c>
@@ -47296,7 +47326,7 @@
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="27" customHeight="1">
       <c r="A85" s="17" t="n">
         <v>84</v>
       </c>
@@ -47338,7 +47368,7 @@
         </is>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="27" customHeight="1">
       <c r="A86" s="17" t="n">
         <v>85</v>
       </c>
@@ -47380,7 +47410,7 @@
         </is>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="27" customHeight="1">
       <c r="A87" s="17" t="n">
         <v>86</v>
       </c>
@@ -47422,7 +47452,7 @@
         </is>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="27" customHeight="1">
       <c r="A88" s="17" t="n">
         <v>87</v>
       </c>
@@ -47464,7 +47494,7 @@
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="27" customHeight="1">
       <c r="A89" s="17" t="n">
         <v>88</v>
       </c>
@@ -47506,7 +47536,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="27" customHeight="1">
       <c r="A90" s="17" t="n">
         <v>89</v>
       </c>
@@ -47548,7 +47578,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="27" customHeight="1">
       <c r="A91" s="17" t="n">
         <v>90</v>
       </c>
@@ -47590,7 +47620,7 @@
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="27" customHeight="1">
       <c r="A92" s="17" t="n">
         <v>91</v>
       </c>
@@ -47632,7 +47662,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="27" customHeight="1">
       <c r="A93" s="17" t="n">
         <v>92</v>
       </c>
@@ -47660,7 +47690,7 @@
       <c r="G93" s="13" t="n"/>
       <c r="H93" s="14" t="inlineStr">
         <is>
-          <t>Expand Compound Power Semiconductors</t>
+          <t>Expand Compound GaN Semiconductors</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
@@ -47674,7 +47704,7 @@
         </is>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="27" customHeight="1">
       <c r="A94" s="17" t="n">
         <v>93</v>
       </c>
@@ -47702,7 +47732,7 @@
       <c r="G94" s="13" t="n"/>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>Expand Smart Manufacturing</t>
+          <t>Expand Smart Factory</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
@@ -47716,7 +47746,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="27" customHeight="1">
       <c r="A95" s="17" t="n">
         <v>94</v>
       </c>
@@ -47758,7 +47788,7 @@
         </is>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="27" customHeight="1">
       <c r="A96" s="17" t="n">
         <v>95</v>
       </c>
@@ -47800,7 +47830,7 @@
         </is>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="67.5" customHeight="1">
       <c r="A97" s="17" t="n">
         <v>96</v>
       </c>
@@ -47842,7 +47872,7 @@
         </is>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="27" customHeight="1">
       <c r="A98" s="17" t="n">
         <v>97</v>
       </c>
@@ -47884,7 +47914,7 @@
         </is>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="27" customHeight="1">
       <c r="A99" s="17" t="n">
         <v>98</v>
       </c>
@@ -47926,7 +47956,7 @@
         </is>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="27" customHeight="1">
       <c r="A100" s="17" t="n">
         <v>99</v>
       </c>
@@ -47968,7 +47998,7 @@
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="27" customHeight="1">
       <c r="A101" s="17" t="n">
         <v>100</v>
       </c>
@@ -48010,7 +48040,7 @@
         </is>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="27" customHeight="1">
       <c r="A102" s="17" t="n">
         <v>101</v>
       </c>
@@ -48052,7 +48082,7 @@
         </is>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="27" customHeight="1">
       <c r="A103" s="17" t="n">
         <v>102</v>
       </c>
@@ -48094,7 +48124,7 @@
         </is>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="27" customHeight="1">
       <c r="A104" s="17" t="n">
         <v>103</v>
       </c>
@@ -48136,7 +48166,7 @@
         </is>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="27" customHeight="1">
       <c r="A105" s="17" t="n">
         <v>104</v>
       </c>
@@ -48178,7 +48208,7 @@
         </is>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="27" customHeight="1">
       <c r="A106" s="17" t="n">
         <v>105</v>
       </c>
@@ -48220,7 +48250,7 @@
         </is>
       </c>
     </row>
-    <row r="107">
+    <row r="107" ht="27" customHeight="1">
       <c r="A107" s="17" t="n">
         <v>106</v>
       </c>
@@ -48262,7 +48292,7 @@
         </is>
       </c>
     </row>
-    <row r="108">
+    <row r="108" ht="27" customHeight="1">
       <c r="A108" s="17" t="n">
         <v>107</v>
       </c>
@@ -48304,7 +48334,7 @@
         </is>
       </c>
     </row>
-    <row r="109">
+    <row r="109" ht="27" customHeight="1">
       <c r="A109" s="17" t="n">
         <v>108</v>
       </c>
@@ -48346,7 +48376,7 @@
         </is>
       </c>
     </row>
-    <row r="110">
+    <row r="110" ht="27" customHeight="1">
       <c r="A110" s="17" t="n">
         <v>109</v>
       </c>
@@ -48388,7 +48418,7 @@
         </is>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="27" customHeight="1">
       <c r="A111" s="17" t="n">
         <v>110</v>
       </c>
@@ -48430,7 +48460,7 @@
         </is>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="27" customHeight="1">
       <c r="A112" s="17" t="n">
         <v>111</v>
       </c>
@@ -48472,7 +48502,7 @@
         </is>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="27" customHeight="1">
       <c r="A113" s="17" t="n">
         <v>112</v>
       </c>
@@ -48514,7 +48544,7 @@
         </is>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="27" customHeight="1">
       <c r="A114" s="17" t="n">
         <v>113</v>
       </c>
@@ -48556,7 +48586,7 @@
         </is>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="27" customHeight="1">
       <c r="A115" s="17" t="n">
         <v>114</v>
       </c>
@@ -48598,7 +48628,7 @@
         </is>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="27" customHeight="1">
       <c r="A116" s="17" t="n">
         <v>115</v>
       </c>
@@ -48642,7 +48672,7 @@
         </is>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="27" customHeight="1">
       <c r="A117" s="17" t="n">
         <v>116</v>
       </c>
@@ -48684,7 +48714,7 @@
         </is>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="27" customHeight="1">
       <c r="A118" s="17" t="n">
         <v>117</v>
       </c>
@@ -48728,7 +48758,7 @@
         </is>
       </c>
     </row>
-    <row r="119">
+    <row r="119" ht="27" customHeight="1">
       <c r="A119" s="17" t="n">
         <v>118</v>
       </c>
@@ -48770,7 +48800,7 @@
         </is>
       </c>
     </row>
-    <row r="120">
+    <row r="120" ht="27" customHeight="1">
       <c r="A120" s="17" t="n">
         <v>119</v>
       </c>
@@ -48814,7 +48844,7 @@
         </is>
       </c>
     </row>
-    <row r="121">
+    <row r="121" ht="27" customHeight="1">
       <c r="A121" s="17" t="n">
         <v>120</v>
       </c>
@@ -48858,7 +48888,7 @@
         </is>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="27" customHeight="1">
       <c r="A122" s="17" t="n">
         <v>121</v>
       </c>
@@ -48902,7 +48932,7 @@
         </is>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="27" customHeight="1">
       <c r="A123" s="17" t="n">
         <v>122</v>
       </c>
@@ -48946,7 +48976,7 @@
         </is>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="27" customHeight="1">
       <c r="A124" s="17" t="n">
         <v>123</v>
       </c>
@@ -48988,7 +49018,7 @@
         </is>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="27" customHeight="1">
       <c r="A125" s="17" t="n">
         <v>124</v>
       </c>
@@ -49030,7 +49060,7 @@
         </is>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="27" customHeight="1">
       <c r="A126" s="17" t="n">
         <v>125</v>
       </c>
@@ -49368,7 +49398,7 @@
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -49395,7 +49425,7 @@
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>Smart Manufacturing</t>
+          <t>Smart Factory</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -49411,7 +49441,7 @@
       </c>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -49454,7 +49484,7 @@
       </c>
     </row>
     <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -49497,7 +49527,7 @@
       </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -49524,7 +49554,7 @@
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Compound Power Semiconductors</t>
+          <t>Compound GaN Semiconductors</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -49540,7 +49570,7 @@
       </c>
     </row>
     <row r="7" ht="40.5" customHeight="1">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -49567,7 +49597,7 @@
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>About</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -49583,7 +49613,7 @@
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -49610,7 +49640,7 @@
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>About Us</t>
+          <t>Company Intro</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -50013,7 +50043,7 @@
       </c>
     </row>
     <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -50034,11 +50064,15 @@
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>지배구조</t>
+          <t>거버넌스</t>
         </is>
       </c>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="8" t="n"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
           <t>GNB · 메가 메뉴 · 전체 메뉴의 하위 이름과 같은 글</t>
@@ -50051,7 +50085,7 @@
       </c>
     </row>
     <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -50078,7 +50112,7 @@
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Reporting Channels</t>
+          <t>Reporting Center</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -50265,7 +50299,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="27" customHeight="1">
       <c r="A24" s="16" t="n">
         <v>23</v>
       </c>
@@ -50307,7 +50341,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="27" customHeight="1">
       <c r="A25" s="16" t="n">
         <v>24</v>
       </c>
@@ -50349,7 +50383,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="27" customHeight="1">
       <c r="A26" s="16" t="n">
         <v>25</v>
       </c>
@@ -50391,7 +50425,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="27" customHeight="1">
       <c r="A27" s="16" t="n">
         <v>26</v>
       </c>
@@ -50703,7 +50737,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="27" customHeight="1">
       <c r="A35" s="16" t="n">
         <v>34</v>
       </c>
@@ -53748,8 +53782,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="16" t="n">
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -53776,7 +53810,7 @@
       <c r="G2" s="7" t="n"/>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Smart Manufacturing</t>
+          <t>Smart Factory</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -53947,7 +53981,7 @@
       </c>
     </row>
     <row r="7" ht="27" customHeight="1">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -53974,7 +54008,7 @@
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Battery Formation</t>
+          <t>Secondary Battery Activation</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -54036,7 +54070,7 @@
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -54063,7 +54097,7 @@
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Automation Systems</t>
+          <t>Automation System</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -54107,7 +54141,7 @@
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Battery Materials</t>
+          <t>Secondary Battery Materials</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -55058,7 +55092,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="27" customHeight="1">
       <c r="A34" s="16" t="n">
         <v>33</v>
       </c>
@@ -55100,7 +55134,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="27" customHeight="1">
       <c r="A35" s="16" t="n">
         <v>34</v>
       </c>
@@ -55142,7 +55176,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="27" customHeight="1">
       <c r="A36" s="16" t="n">
         <v>35</v>
       </c>
@@ -55184,7 +55218,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="27" customHeight="1">
       <c r="A37" s="16" t="n">
         <v>36</v>
       </c>
@@ -55226,7 +55260,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="27" customHeight="1">
       <c r="A38" s="16" t="n">
         <v>37</v>
       </c>
@@ -55268,7 +55302,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="27" customHeight="1">
       <c r="A39" s="16" t="n">
         <v>38</v>
       </c>
@@ -55310,7 +55344,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="27" customHeight="1">
       <c r="A40" s="16" t="n">
         <v>39</v>
       </c>
@@ -55352,7 +55386,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="27" customHeight="1">
       <c r="A41" s="16" t="n">
         <v>40</v>
       </c>
@@ -55394,7 +55428,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="27" customHeight="1">
       <c r="A42" s="16" t="n">
         <v>41</v>
       </c>
@@ -55436,7 +55470,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="27" customHeight="1">
       <c r="A43" s="16" t="n">
         <v>42</v>
       </c>
@@ -55478,7 +55512,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="27" customHeight="1">
       <c r="A44" s="16" t="n">
         <v>43</v>
       </c>
@@ -55520,7 +55554,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="27" customHeight="1">
       <c r="A45" s="16" t="n">
         <v>44</v>
       </c>
@@ -55562,7 +55596,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="27" customHeight="1">
       <c r="A46" s="16" t="n">
         <v>45</v>
       </c>
@@ -55604,7 +55638,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="27" customHeight="1">
       <c r="A47" s="16" t="n">
         <v>46</v>
       </c>
@@ -55646,7 +55680,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="27" customHeight="1">
       <c r="A48" s="16" t="n">
         <v>47</v>
       </c>
@@ -55688,7 +55722,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="27" customHeight="1">
       <c r="A49" s="16" t="n">
         <v>48</v>
       </c>
@@ -55840,7 +55874,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="27" customHeight="1">
       <c r="A53" s="16" t="n">
         <v>52</v>
       </c>
@@ -55916,7 +55950,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="27" customHeight="1">
       <c r="A55" s="16" t="n">
         <v>54</v>
       </c>
@@ -55992,7 +56026,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="27" customHeight="1">
       <c r="A57" s="16" t="n">
         <v>56</v>
       </c>
@@ -56106,7 +56140,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="27" customHeight="1">
       <c r="A60" s="16" t="n">
         <v>59</v>
       </c>
@@ -56224,7 +56258,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="27" customHeight="1">
       <c r="A63" s="16" t="n">
         <v>62</v>
       </c>
@@ -56300,7 +56334,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="27" customHeight="1">
       <c r="A65" s="16" t="n">
         <v>64</v>
       </c>
@@ -57178,7 +57212,7 @@
         </is>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="27" customHeight="1">
       <c r="A88" s="16" t="n">
         <v>87</v>
       </c>
@@ -57220,7 +57254,7 @@
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="27" customHeight="1">
       <c r="A89" s="16" t="n">
         <v>88</v>
       </c>
@@ -57262,7 +57296,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="27" customHeight="1">
       <c r="A90" s="16" t="n">
         <v>89</v>
       </c>
@@ -57346,7 +57380,7 @@
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="27" customHeight="1">
       <c r="A92" s="16" t="n">
         <v>91</v>
       </c>
@@ -57388,7 +57422,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="27" customHeight="1">
       <c r="A93" s="16" t="n">
         <v>92</v>
       </c>
@@ -57430,7 +57464,7 @@
         </is>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="27" customHeight="1">
       <c r="A94" s="16" t="n">
         <v>93</v>
       </c>
@@ -57780,7 +57814,7 @@
         </is>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="27" customHeight="1">
       <c r="A103" s="16" t="n">
         <v>102</v>
       </c>
@@ -57822,7 +57856,7 @@
         </is>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="27" customHeight="1">
       <c r="A104" s="16" t="n">
         <v>103</v>
       </c>
@@ -57864,7 +57898,7 @@
         </is>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="27" customHeight="1">
       <c r="A105" s="16" t="n">
         <v>104</v>
       </c>
@@ -57906,7 +57940,7 @@
         </is>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="27" customHeight="1">
       <c r="A106" s="16" t="n">
         <v>105</v>
       </c>
@@ -57948,7 +57982,7 @@
         </is>
       </c>
     </row>
-    <row r="107">
+    <row r="107" ht="27" customHeight="1">
       <c r="A107" s="16" t="n">
         <v>106</v>
       </c>
@@ -57990,7 +58024,7 @@
         </is>
       </c>
     </row>
-    <row r="108">
+    <row r="108" ht="27" customHeight="1">
       <c r="A108" s="16" t="n">
         <v>107</v>
       </c>
@@ -58032,7 +58066,7 @@
         </is>
       </c>
     </row>
-    <row r="109">
+    <row r="109" ht="27" customHeight="1">
       <c r="A109" s="16" t="n">
         <v>108</v>
       </c>
@@ -58074,7 +58108,7 @@
         </is>
       </c>
     </row>
-    <row r="110">
+    <row r="110" ht="27" customHeight="1">
       <c r="A110" s="16" t="n">
         <v>109</v>
       </c>
@@ -58116,7 +58150,7 @@
         </is>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="27" customHeight="1">
       <c r="A111" s="16" t="n">
         <v>110</v>
       </c>
@@ -58158,7 +58192,7 @@
         </is>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="27" customHeight="1">
       <c r="A112" s="16" t="n">
         <v>111</v>
       </c>
@@ -58200,7 +58234,7 @@
         </is>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="27" customHeight="1">
       <c r="A113" s="16" t="n">
         <v>112</v>
       </c>
@@ -58242,7 +58276,7 @@
         </is>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="27" customHeight="1">
       <c r="A114" s="16" t="n">
         <v>113</v>
       </c>
@@ -58284,7 +58318,7 @@
         </is>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="27" customHeight="1">
       <c r="A115" s="16" t="n">
         <v>114</v>
       </c>
@@ -58326,7 +58360,7 @@
         </is>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="27" customHeight="1">
       <c r="A116" s="16" t="n">
         <v>115</v>
       </c>
@@ -58368,7 +58402,7 @@
         </is>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="27" customHeight="1">
       <c r="A117" s="16" t="n">
         <v>116</v>
       </c>
@@ -58520,7 +58554,7 @@
         </is>
       </c>
     </row>
-    <row r="121">
+    <row r="121" ht="27" customHeight="1">
       <c r="A121" s="16" t="n">
         <v>120</v>
       </c>
@@ -58596,7 +58630,7 @@
         </is>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="27" customHeight="1">
       <c r="A123" s="16" t="n">
         <v>122</v>
       </c>
@@ -58672,7 +58706,7 @@
         </is>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="27" customHeight="1">
       <c r="A125" s="16" t="n">
         <v>124</v>
       </c>
@@ -58748,7 +58782,7 @@
         </is>
       </c>
     </row>
-    <row r="127">
+    <row r="127" ht="27" customHeight="1">
       <c r="A127" s="16" t="n">
         <v>126</v>
       </c>
@@ -58824,7 +58858,7 @@
         </is>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="27" customHeight="1">
       <c r="A129" s="16" t="n">
         <v>128</v>
       </c>
@@ -59014,7 +59048,7 @@
         </is>
       </c>
     </row>
-    <row r="134">
+    <row r="134" ht="27" customHeight="1">
       <c r="A134" s="16" t="n">
         <v>133</v>
       </c>
@@ -59090,7 +59124,7 @@
         </is>
       </c>
     </row>
-    <row r="136">
+    <row r="136" ht="27" customHeight="1">
       <c r="A136" s="16" t="n">
         <v>135</v>
       </c>
@@ -59166,7 +59200,7 @@
         </is>
       </c>
     </row>
-    <row r="138">
+    <row r="138" ht="27" customHeight="1">
       <c r="A138" s="16" t="n">
         <v>137</v>
       </c>
@@ -59242,7 +59276,7 @@
         </is>
       </c>
     </row>
-    <row r="140">
+    <row r="140" ht="27" customHeight="1">
       <c r="A140" s="16" t="n">
         <v>139</v>
       </c>
@@ -59361,8 +59395,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="16" t="n">
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -60254,7 +60288,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="27" customHeight="1">
       <c r="A24" s="16" t="n">
         <v>23</v>
       </c>
@@ -60296,7 +60330,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="27" customHeight="1">
       <c r="A25" s="16" t="n">
         <v>24</v>
       </c>
@@ -60338,7 +60372,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="27" customHeight="1">
       <c r="A26" s="16" t="n">
         <v>25</v>
       </c>
@@ -60380,7 +60414,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="27" customHeight="1">
       <c r="A27" s="16" t="n">
         <v>26</v>
       </c>
@@ -60422,7 +60456,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="27" customHeight="1">
       <c r="A28" s="16" t="n">
         <v>27</v>
       </c>
@@ -60464,7 +60498,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="27" customHeight="1">
       <c r="A29" s="16" t="n">
         <v>28</v>
       </c>
@@ -62759,7 +62793,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="27" customHeight="1">
       <c r="A91" s="16" t="n">
         <v>90</v>
       </c>
@@ -62801,7 +62835,7 @@
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="27" customHeight="1">
       <c r="A92" s="16" t="n">
         <v>91</v>
       </c>
@@ -63283,7 +63317,7 @@
         </is>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="27" customHeight="1">
       <c r="A103" s="16" t="n">
         <v>102</v>
       </c>
@@ -63325,7 +63359,7 @@
         </is>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="27" customHeight="1">
       <c r="A104" s="16" t="n">
         <v>103</v>
       </c>
@@ -63750,7 +63784,7 @@
         </is>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="27" customHeight="1">
       <c r="A114" s="16" t="n">
         <v>113</v>
       </c>
@@ -64166,7 +64200,7 @@
         </is>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="27" customHeight="1">
       <c r="A124" s="16" t="n">
         <v>123</v>
       </c>
@@ -64574,7 +64608,7 @@
         </is>
       </c>
     </row>
-    <row r="134">
+    <row r="134" ht="27" customHeight="1">
       <c r="A134" s="16" t="n">
         <v>133</v>
       </c>
@@ -64948,7 +64982,7 @@
         </is>
       </c>
     </row>
-    <row r="143">
+    <row r="143" ht="27" customHeight="1">
       <c r="A143" s="16" t="n">
         <v>142</v>
       </c>
@@ -65222,7 +65256,7 @@
         </is>
       </c>
     </row>
-    <row r="150">
+    <row r="150" ht="27" customHeight="1">
       <c r="A150" s="16" t="n">
         <v>149</v>
       </c>
@@ -65638,7 +65672,7 @@
         </is>
       </c>
     </row>
-    <row r="160">
+    <row r="160" ht="27" customHeight="1">
       <c r="A160" s="16" t="n">
         <v>159</v>
       </c>
@@ -66054,7 +66088,7 @@
         </is>
       </c>
     </row>
-    <row r="170">
+    <row r="170" ht="27" customHeight="1">
       <c r="A170" s="16" t="n">
         <v>169</v>
       </c>
@@ -66547,7 +66581,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="27" customHeight="1">
       <c r="A2" s="16" t="n">
         <v>1</v>
       </c>
@@ -67306,7 +67340,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="27" customHeight="1">
       <c r="A21" s="16" t="n">
         <v>20</v>
       </c>
@@ -67390,7 +67424,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="27" customHeight="1">
       <c r="A23" s="16" t="n">
         <v>22</v>
       </c>
@@ -67432,7 +67466,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="27" customHeight="1">
       <c r="A24" s="16" t="n">
         <v>23</v>
       </c>
@@ -67474,7 +67508,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="27" customHeight="1">
       <c r="A25" s="16" t="n">
         <v>24</v>
       </c>
@@ -67516,7 +67550,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="27" customHeight="1">
       <c r="A26" s="16" t="n">
         <v>25</v>
       </c>
@@ -67600,7 +67634,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="27" customHeight="1">
       <c r="A28" s="16" t="n">
         <v>27</v>
       </c>
@@ -68477,7 +68511,7 @@
       <c r="G2" s="7" t="n"/>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Compound Power Semiconductors</t>
+          <t>Compound GaN Semiconductors</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -68918,7 +68952,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="27" customHeight="1">
       <c r="A14" s="16" t="n">
         <v>13</v>
       </c>
@@ -68960,7 +68994,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="27" customHeight="1">
       <c r="A15" s="16" t="n">
         <v>14</v>
       </c>
@@ -69002,7 +69036,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="27" customHeight="1">
       <c r="A16" s="16" t="n">
         <v>15</v>
       </c>
@@ -69410,7 +69444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -69475,7 +69509,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="27" customHeight="1">
       <c r="A2" s="16" t="n">
         <v>1</v>
       </c>
@@ -69517,8 +69551,8 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="16" t="n">
+    <row r="3" ht="27" customHeight="1">
+      <c r="A3" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -69545,7 +69579,7 @@
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>Smart Manufacturing</t>
+          <t>Smart Factory</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -69597,8 +69631,8 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="16" t="n">
+    <row r="5" ht="27" customHeight="1">
+      <c r="A5" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -69625,7 +69659,7 @@
       <c r="G5" s="7" t="n"/>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Battery Formation</t>
+          <t>Secondary Battery Activation</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -69677,7 +69711,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="27" customHeight="1">
       <c r="A7" s="16" t="n">
         <v>6</v>
       </c>
@@ -69705,7 +69739,7 @@
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Automation Systems</t>
+          <t>Automation System</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -69719,7 +69753,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="27" customHeight="1">
       <c r="A8" s="16" t="n">
         <v>7</v>
       </c>
@@ -69747,7 +69781,7 @@
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Battery Materials</t>
+          <t>Secondary Battery Materials</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -69805,8 +69839,8 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -69999,8 +70033,8 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="16" t="n">
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -70079,7 +70113,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="27" customHeight="1">
       <c r="A17" s="16" t="n">
         <v>16</v>
       </c>
@@ -70121,7 +70155,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="27" customHeight="1">
       <c r="A18" s="16" t="n">
         <v>17</v>
       </c>
@@ -70267,7 +70301,7 @@
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Compound Power Semiconductors</t>
+          <t>Compound GaN Semiconductors</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -70434,48 +70468,6 @@
       <c r="J25" s="9" t="inlineStr">
         <is>
           <t>/html/body/section/div/a[4]/div[2]/span[3]/span[2]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>본문</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>글</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>데스크톱(1280px 이상) 기준으로 디자인된 시안입니다.</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>This draft is designed for desktop (1280px and wider).</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>영문 초벌 번역(Claude, 2026-10-08) — 검토 필요</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[1]|text</t>
         </is>
       </c>
     </row>
@@ -70823,7 +70815,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="27" customHeight="1">
       <c r="A9" s="16" t="n">
         <v>8</v>
       </c>
@@ -70943,7 +70935,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="27" customHeight="1">
       <c r="A12" s="16" t="n">
         <v>11</v>
       </c>
@@ -71063,7 +71055,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="27" customHeight="1">
       <c r="A15" s="16" t="n">
         <v>14</v>
       </c>

--- a/content-export/국문영문글정리.xlsx
+++ b/content-export/국문영문글정리.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="9" activeTab="19" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
@@ -134,7 +134,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -186,6 +186,11 @@
         <fgColor theme="8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -232,7 +237,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -281,6 +286,15 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -648,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -876,6 +890,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -911,6 +926,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -939,6 +955,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -2054,7 +2071,7 @@
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="20" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -2532,7 +2549,7 @@
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="20" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -9604,7 +9621,7 @@
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="20" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -14175,7 +14192,7 @@
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="20" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -25311,7 +25328,7 @@
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="21" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -25332,13 +25349,13 @@
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>책임 있는 경영을 통해 더 나은 가치를 실현하겠습니다.</t>
+          <t>Sustainable Future with A-PRO</t>
         </is>
       </c>
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>We create greater value through responsible management.</t>
+          <t>Sustainable Future with A-PRO</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -27548,7 +27565,7 @@
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="21" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -27569,13 +27586,13 @@
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>책임 있는 경영을 통해 더 나은 가치를 실현하겠습니다.</t>
+          <t>Sustainable Future with A-PRO</t>
         </is>
       </c>
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>We create greater value through responsible management.</t>
+          <t>Sustainable Future with A-PRO</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -32311,7 +32328,7 @@
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="21" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -32332,13 +32349,13 @@
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>책임 있는 경영을 통해 더 나은 가치를 실현하겠습니다.</t>
+          <t>Sustainable Future with A-PRO</t>
         </is>
       </c>
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>We create greater value through responsible management.</t>
+          <t>Sustainable Future with A-PRO</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -38936,7 +38953,7 @@
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="21" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -38957,13 +38974,13 @@
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>책임 있는 경영을 통해 더 나은 가치를 실현하겠습니다.</t>
+          <t>Sustainable Future with A-PRO</t>
         </is>
       </c>
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>We create greater value through responsible management.</t>
+          <t>Sustainable Future with A-PRO</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -41109,7 +41126,7 @@
       </c>
     </row>
     <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="20" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -41151,7 +41168,7 @@
       </c>
     </row>
     <row r="6" ht="121.5" customHeight="1">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="20" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -41198,7 +41215,7 @@
       </c>
     </row>
     <row r="7" ht="121.5" customHeight="1">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="20" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -41245,7 +41262,7 @@
       </c>
     </row>
     <row r="8" ht="121.5" customHeight="1">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="20" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -41292,7 +41309,7 @@
       </c>
     </row>
     <row r="9" ht="135" customHeight="1">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="20" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -41459,7 +41476,7 @@
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="20" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -41544,7 +41561,7 @@
       </c>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="20" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -43042,7 +43059,7 @@
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="21" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -43063,13 +43080,13 @@
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>책임 있는 경영을 통해 더 나은 가치를 실현하겠습니다.</t>
+          <t>Sustainable Future with A-PRO</t>
         </is>
       </c>
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>We create greater value through responsible management.</t>
+          <t>Sustainable Future with A-PRO</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -49113,7 +49130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -49398,7 +49415,7 @@
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="20" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -49441,7 +49458,7 @@
       </c>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="20" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -49484,7 +49501,7 @@
       </c>
     </row>
     <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="20" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -49527,7 +49544,7 @@
       </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="20" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -49570,7 +49587,7 @@
       </c>
     </row>
     <row r="7" ht="40.5" customHeight="1">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="20" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -49613,7 +49630,7 @@
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="20" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -50043,7 +50060,7 @@
       </c>
     </row>
     <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="20" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -50085,7 +50102,7 @@
       </c>
     </row>
     <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="20" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -53783,7 +53800,7 @@
       </c>
     </row>
     <row r="2" ht="27" customHeight="1">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="20" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -53981,7 +53998,7 @@
       </c>
     </row>
     <row r="7" ht="27" customHeight="1">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="20" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -54070,7 +54087,7 @@
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="20" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -59396,7 +59413,7 @@
       </c>
     </row>
     <row r="2" ht="27" customHeight="1">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="20" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -69552,7 +69569,7 @@
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="20" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -69632,7 +69649,7 @@
       </c>
     </row>
     <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="20" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -69840,7 +69857,7 @@
       </c>
     </row>
     <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="20" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -70034,7 +70051,7 @@
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="20" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="inlineStr">

--- a/content-export/국문영문글정리.xlsx
+++ b/content-export/국문영문글정리.xlsx
@@ -656,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -884,6 +884,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -919,6 +920,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -947,6 +949,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -49138,7 +49141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -70671,13 +70674,13 @@
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>VISION 2030</t>
+          <t>Vision 2030</t>
         </is>
       </c>
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>VISION 2030</t>
+          <t>Vision 2030</t>
         </is>
       </c>
       <c r="I4" s="5" t="n"/>

--- a/content-export/국문영문글정리.xlsx
+++ b/content-export/국문영문글정리.xlsx
@@ -656,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -884,7 +884,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -920,7 +919,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -949,7 +947,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -43799,7 +43796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -49130,6 +49127,48 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="17" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>영문 보기 보충</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>화면 글 · 대체 글</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="n"/>
+      <c r="F127" s="12" t="inlineStr">
+        <is>
+          <t>공시자료</t>
+        </is>
+      </c>
+      <c r="G127" s="13" t="n"/>
+      <c r="H127" s="14" t="inlineStr">
+        <is>
+          <t>Disclosures</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t>영문 초벌 번역(Claude, 2026-10-12) — 검토 필요</t>
+        </is>
+      </c>
+      <c r="J127" s="11" t="inlineStr">
+        <is>
+          <t>i18n|보충</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -49141,7 +49180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>

--- a/content-export/국문영문글정리.xlsx
+++ b/content-export/국문영문글정리.xlsx
@@ -49149,13 +49149,13 @@
       <c r="E127" s="11" t="n"/>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>공시자료</t>
+          <t>DART 공시</t>
         </is>
       </c>
       <c r="G127" s="13" t="n"/>
       <c r="H127" s="14" t="inlineStr">
         <is>
-          <t>Disclosures</t>
+          <t>DART Disclosures</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">

--- a/content-export/국문영문글정리.xlsx
+++ b/content-export/국문영문글정리.xlsx
@@ -49356,7 +49356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -50868,16 +50868,16 @@
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>㈜에이프로(이하 '회사'라 함)은 이용자의 개인정보를 보호하고 이와 관련한 고충을 신속하고 원활하게 처리할 수 있도록 다음과 같이 개인정보 처리방침을 수립·공개합니다.</t>
+          <t>주식회사 에이프로(이하 '회사' 또는 '에이프로')는 정보주체의 자유와 권리 보호를 위해 「개인정보 보호법」 및 관계 법령이 정한 바를 준수하여 적법하게 개인정보를 처리하고 안전하게 관리하고 있습니다. 회사는 「개인정보 보호법」 제30조 및 2026년 개인정보보호위원회 「개인정보 처리방침 작성지침」에 따라 정보주체에게 개인정보 처리와 보호에 관한 절차 및 기준을 안내하고, 이와 관련한 고충을 신속하고 원활하게 처리할 수 있도록 다음과 같이 개인정보 처리방침을 수립·공개합니다.</t>
         </is>
       </c>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Co., Ltd. (hereinafter referred to as the "Company") establishes and discloses this Privacy Policy to protect the personal information of users and to process related grievances promptly and smoothly in accordance with the Personal Information Protection Act.</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12 처리방침 전면 개정(★ 에이프로 개인정보 처리방침_2026.10.12.docx) — 영문 미번역</t>
+        </is>
+      </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
           <t>policy|privacy|0|p</t>
@@ -50890,12 +50890,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제1조 개인정보의 처리 목적</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>조 제목</t>
+          <t>소제목</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -50904,21 +50904,17 @@
         </is>
       </c>
       <c r="E37" s="5" t="n"/>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>제1조 (개인정보의 처리 목적)</t>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>목차</t>
         </is>
       </c>
       <c r="G37" s="7" t="n"/>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Article 1 (Purpose of Processing Personal Information)</t>
-        </is>
-      </c>
+      <c r="H37" s="8" t="n"/>
       <c r="I37" s="5" t="n"/>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|1|h</t>
+          <t>policy|privacy|1|s</t>
         </is>
       </c>
     </row>
@@ -50928,7 +50924,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제1조 개인정보의 처리 목적</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -50944,15 +50940,11 @@
       <c r="E38" s="5" t="n"/>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>회사는 다음의 목적을 위하여 개인정보를 처리합니다. 처리하고 있는 개인정보는 다음의 목적 이외의 용도로는 이용되지 않으며, 이용 목적이 변경되는 경우에는 개인정보 보호법 제18조에 따라 별도의 동의를 받는 등 필요한 조치를 이행할 예정입니다.</t>
+          <t>1. 개인정보의 처리 목적</t>
         </is>
       </c>
       <c r="G38" s="7" t="n"/>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>The Company processes personal information for the following purposes. The personal information being processed will not be used for purposes other than the following, and if the purpose of use is changed, the Company will implement necessary measures, such as obtaining separate consent in accordance with Article 18 of the Personal Information Protection Act.</t>
-        </is>
-      </c>
+      <c r="H38" s="8" t="n"/>
       <c r="I38" s="5" t="n"/>
       <c r="J38" s="9" t="inlineStr">
         <is>
@@ -50966,7 +50958,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제1조 개인정보의 처리 목적</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -50982,15 +50974,11 @@
       <c r="E39" s="5" t="n"/>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>1. 홈페이지 회원가입 및 관리: 회원 가입의사 확인, 회원제 서비스 제공에 따른 본인 식별·인증, 회원자격 유지·관리, 서비스 부정이용 방지, 각종 고지·통지 등을 목적으로 개인정보를 처리합니다.</t>
+          <t>2. 처리하는 개인정보 항목 및 법적 근거</t>
         </is>
       </c>
       <c r="G39" s="7" t="n"/>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>Website Membership Registration and Management: Personal information is processed for the purposes of confirming the intention to join, identifying and authenticating individuals for membership services, maintaining and managing membership status, preventing unauthorized use of services, and delivering various notices and notifications.</t>
-        </is>
-      </c>
+      <c r="H39" s="8" t="n"/>
       <c r="I39" s="5" t="n"/>
       <c r="J39" s="9" t="inlineStr">
         <is>
@@ -51004,7 +50992,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제1조 개인정보의 처리 목적</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -51020,15 +51008,11 @@
       <c r="E40" s="5" t="n"/>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>2. 재화 또는 서비스 제공: 물품배송, 서비스 제공, 계약서·청구서 발송, 콘텐츠 제공, 맞춤 서비스 제공, 본인인증, 연령인증, 요금결제·정산 등을 목적으로 개인정보를 처리합니다.</t>
+          <t>3. 14세 미만 아동의 개인정보 처리에 관한 사항</t>
         </is>
       </c>
       <c r="G40" s="7" t="n"/>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>Provision of Goods or Services: Personal information is processed for the purposes of delivery of goods, provision of services, sending contracts and invoices, providing content, providing customized services, identity verification, age verification, and payment and settlement of fees.</t>
-        </is>
-      </c>
+      <c r="H40" s="8" t="n"/>
       <c r="I40" s="5" t="n"/>
       <c r="J40" s="9" t="inlineStr">
         <is>
@@ -51042,7 +51026,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제1조 개인정보의 처리 목적</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -51058,15 +51042,11 @@
       <c r="E41" s="5" t="n"/>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>3. 마케팅 및 광고에의 활용(선택): 신규 서비스(제품) 개발 및 맞춤 서비스 제공, 이벤트 및 광고성 정보 제공 및 참여기회 제공, 인구통계학적 특성에 따른 서비스 제공 및 광고 게재, 서비스의 유효성 확인, 접속빈도 파악 또는 회원의 서비스 이용에 대한 통계 등을 목적으로 개인정보를 처리합니다.</t>
+          <t>4. 개인정보의 처리 및 보유 기간</t>
         </is>
       </c>
       <c r="G41" s="7" t="n"/>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>Utilization for Marketing and Advertising (Optional): Personal information is processed for the purposes of developing new services (products) and providing customized services, providing opportunities to participate in events and promotional information, providing services and placing advertisements according to demographic characteristics, verifying service validity, identifying access frequency, or compiling statistics on members' service use.</t>
-        </is>
-      </c>
+      <c r="H41" s="8" t="n"/>
       <c r="I41" s="5" t="n"/>
       <c r="J41" s="9" t="inlineStr">
         <is>
@@ -51080,12 +51060,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제2조 개인정보의 처리 및 보유 기간</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>조 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -51094,21 +51074,17 @@
         </is>
       </c>
       <c r="E42" s="5" t="n"/>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>제2조 (개인정보의 처리 및 보유 기간)</t>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>5. 개인정보의 파기 절차 및 방법</t>
         </is>
       </c>
       <c r="G42" s="7" t="n"/>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>Article 2 (Processing and Retention Period of Personal Information)</t>
-        </is>
-      </c>
+      <c r="H42" s="8" t="n"/>
       <c r="I42" s="5" t="n"/>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|6|h</t>
+          <t>policy|privacy|6|p</t>
         </is>
       </c>
     </row>
@@ -51118,7 +51094,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제2조 개인정보의 처리 및 보유 기간</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -51134,15 +51110,11 @@
       <c r="E43" s="5" t="n"/>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>① 회사는 법령에 따른 개인정보 보유·이용기간 또는 정보주체로부터 개인정보를 수집 시에 동의받은 개인정보 보유 이용기간 내에서 개인정보를 처리·보유합니다.</t>
+          <t>6. 개인정보의 제3자 제공에 관한 사항</t>
         </is>
       </c>
       <c r="G43" s="7" t="n"/>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t>① The Company processes and retains personal information within the personal information retention and use period required by laws or the period agreed upon when collecting personal information from the information subject.</t>
-        </is>
-      </c>
+      <c r="H43" s="8" t="n"/>
       <c r="I43" s="5" t="n"/>
       <c r="J43" s="9" t="inlineStr">
         <is>
@@ -51156,7 +51128,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제2조 개인정보의 처리 및 보유 기간</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -51172,15 +51144,11 @@
       <c r="E44" s="5" t="n"/>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>② 각각의 개인정보 처리 및 보유 기간은 다음과 같습니다.</t>
+          <t>7. 추가적인 이용·제공 판단 기준</t>
         </is>
       </c>
       <c r="G44" s="7" t="n"/>
-      <c r="H44" s="8" t="inlineStr">
-        <is>
-          <t>② The respective personal information processing and retention periods are as follows:</t>
-        </is>
-      </c>
+      <c r="H44" s="8" t="n"/>
       <c r="I44" s="5" t="n"/>
       <c r="J44" s="9" t="inlineStr">
         <is>
@@ -51194,7 +51162,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제2조 개인정보의 처리 및 보유 기간</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -51210,15 +51178,11 @@
       <c r="E45" s="5" t="n"/>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>1. 홈페이지 회원 가입 및 관리: 홈페이지 탈퇴 시까지. 다만, 다음의 사유에 해당하는 경우에는 해당 사유 종료 시까지</t>
+          <t>8. 개인정보 처리업무의 위탁에 관한 사항</t>
         </is>
       </c>
       <c r="G45" s="7" t="n"/>
-      <c r="H45" s="8" t="inlineStr">
-        <is>
-          <t>Website Membership Registration and Management: Until the user withdraws from the website. However, in the following cases, until the termination of the relevant reason:</t>
-        </is>
-      </c>
+      <c r="H45" s="8" t="n"/>
       <c r="I45" s="5" t="n"/>
       <c r="J45" s="9" t="inlineStr">
         <is>
@@ -51232,7 +51196,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제2조 개인정보의 처리 및 보유 기간</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -51248,15 +51212,11 @@
       <c r="E46" s="5" t="n"/>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>A. 관계 법령 위반에 따른 수사·조사 등이 진행 중인 경우에는 해당 수사·조사 종료 시까지</t>
+          <t>9. 개인정보의 국외 수집 및 이전에 관한 사항</t>
         </is>
       </c>
       <c r="G46" s="7" t="n"/>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>A. In the event of an ongoing investigation or inquiry due to a violation of relevant laws: Until the end of the relevant investigation or inquiry.</t>
-        </is>
-      </c>
+      <c r="H46" s="8" t="n"/>
       <c r="I46" s="5" t="n"/>
       <c r="J46" s="9" t="inlineStr">
         <is>
@@ -51270,7 +51230,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제2조 개인정보의 처리 및 보유 기간</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -51286,15 +51246,11 @@
       <c r="E47" s="5" t="n"/>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>B. 홈페이지 이용에 따른 채권·채무관계 잔존 시에는 해당 채권·채무관계 정산 시까지</t>
+          <t>10. 생성형 인공지능(AI) 서비스 개인정보 처리에 관한 사항</t>
         </is>
       </c>
       <c r="G47" s="7" t="n"/>
-      <c r="H47" s="8" t="inlineStr">
-        <is>
-          <t>B. If a claim/debt relationship remains due to the use of the website: Until the settlement of the relevant claim/debt relationship.</t>
-        </is>
-      </c>
+      <c r="H47" s="8" t="n"/>
       <c r="I47" s="5" t="n"/>
       <c r="J47" s="9" t="inlineStr">
         <is>
@@ -51308,7 +51264,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제2조 개인정보의 처리 및 보유 기간</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -51324,15 +51280,11 @@
       <c r="E48" s="5" t="n"/>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>2. 전자상거래 등에서의 소비자 보호에 관한 법률에 따른 보존</t>
+          <t>11. 개인정보의 안전성 확보조치에 관한 사항</t>
         </is>
       </c>
       <c r="G48" s="7" t="n"/>
-      <c r="H48" s="8" t="inlineStr">
-        <is>
-          <t>Retention according to the Act on the Consumer Protection in Electronic Commerce, etc.:</t>
-        </is>
-      </c>
+      <c r="H48" s="8" t="n"/>
       <c r="I48" s="5" t="n"/>
       <c r="J48" s="9" t="inlineStr">
         <is>
@@ -51346,7 +51298,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제2조 개인정보의 처리 및 보유 기간</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -51362,15 +51314,11 @@
       <c r="E49" s="5" t="n"/>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>A. 표시/광고에 관한 기록: 6개월</t>
+          <t>12. 민감정보의 공개 가능성 및 비공개 선택 방법</t>
         </is>
       </c>
       <c r="G49" s="7" t="n"/>
-      <c r="H49" s="8" t="inlineStr">
-        <is>
-          <t>A. Records on labeling/advertising: 6 months</t>
-        </is>
-      </c>
+      <c r="H49" s="8" t="n"/>
       <c r="I49" s="5" t="n"/>
       <c r="J49" s="9" t="inlineStr">
         <is>
@@ -51384,7 +51332,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제2조 개인정보의 처리 및 보유 기간</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -51400,15 +51348,11 @@
       <c r="E50" s="5" t="n"/>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>B. 계약 또는 청약철회 등에 관한 기록: 5년</t>
+          <t>13. 가명정보 처리에 관한 사항</t>
         </is>
       </c>
       <c r="G50" s="7" t="n"/>
-      <c r="H50" s="8" t="inlineStr">
-        <is>
-          <t>B. Records on contracts or withdrawal of subscription: 5 years</t>
-        </is>
-      </c>
+      <c r="H50" s="8" t="n"/>
       <c r="I50" s="5" t="n"/>
       <c r="J50" s="9" t="inlineStr">
         <is>
@@ -51422,7 +51366,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제2조 개인정보의 처리 및 보유 기간</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -51438,15 +51382,11 @@
       <c r="E51" s="5" t="n"/>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>C. 대금결제 및 재화 등의 공급에 관한 기록: 5년</t>
+          <t>14. 개인정보 자동 수집 장치의 설치·운영 및 거부에 관한 사항</t>
         </is>
       </c>
       <c r="G51" s="7" t="n"/>
-      <c r="H51" s="8" t="inlineStr">
-        <is>
-          <t>C. Records on payment and supply of goods: 5 years</t>
-        </is>
-      </c>
+      <c r="H51" s="8" t="n"/>
       <c r="I51" s="5" t="n"/>
       <c r="J51" s="9" t="inlineStr">
         <is>
@@ -51460,7 +51400,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제2조 개인정보의 처리 및 보유 기간</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -51476,15 +51416,11 @@
       <c r="E52" s="5" t="n"/>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>D. 소비자의 불만 또는 분쟁처리에 관한 기록: 3년</t>
+          <t>15. 온라인 행태정보 수집·이용 및 거부에 관한 사항</t>
         </is>
       </c>
       <c r="G52" s="7" t="n"/>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>D. Records on consumer complaints or dispute resolution: 3 years</t>
-        </is>
-      </c>
+      <c r="H52" s="8" t="n"/>
       <c r="I52" s="5" t="n"/>
       <c r="J52" s="9" t="inlineStr">
         <is>
@@ -51498,12 +51434,12 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제3조 처리하는 개인정보의 항목</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>조 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -51512,21 +51448,17 @@
         </is>
       </c>
       <c r="E53" s="5" t="n"/>
-      <c r="F53" s="10" t="inlineStr">
-        <is>
-          <t>제3조 (처리하는 개인정보의 항목)</t>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>16. 정보주체와 법정대리인의 권리·의무 및 행사방법</t>
         </is>
       </c>
       <c r="G53" s="7" t="n"/>
-      <c r="H53" s="8" t="inlineStr">
-        <is>
-          <t>Article 3 (Items of Personal Information Processed)</t>
-        </is>
-      </c>
+      <c r="H53" s="8" t="n"/>
       <c r="I53" s="5" t="n"/>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|17|h</t>
+          <t>policy|privacy|17|p</t>
         </is>
       </c>
     </row>
@@ -51536,7 +51468,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제3조 처리하는 개인정보의 항목</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -51552,15 +51484,11 @@
       <c r="E54" s="5" t="n"/>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>회사는 다음의 개인정보 항목을 처리하고 있습니다.</t>
+          <t>17. 자동화된 결정에 관한 사항</t>
         </is>
       </c>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="8" t="inlineStr">
-        <is>
-          <t>The Company processes the following items of personal information:</t>
-        </is>
-      </c>
+      <c r="H54" s="8" t="n"/>
       <c r="I54" s="5" t="n"/>
       <c r="J54" s="9" t="inlineStr">
         <is>
@@ -51574,7 +51502,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제3조 처리하는 개인정보의 항목</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -51590,15 +51518,11 @@
       <c r="E55" s="5" t="n"/>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>1. 필수항목: 성명, 아이디, 비밀번호, 휴대전화번호, 이메일 주소</t>
+          <t>18. 개인정보 보호책임자 및 고충처리 부서</t>
         </is>
       </c>
       <c r="G55" s="7" t="n"/>
-      <c r="H55" s="8" t="inlineStr">
-        <is>
-          <t>Required Items: Name, ID, Password, Mobile phone number, Email address.</t>
-        </is>
-      </c>
+      <c r="H55" s="8" t="n"/>
       <c r="I55" s="5" t="n"/>
       <c r="J55" s="9" t="inlineStr">
         <is>
@@ -51612,7 +51536,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제3조 처리하는 개인정보의 항목</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -51628,15 +51552,11 @@
       <c r="E56" s="5" t="n"/>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>2. 선택항목: 생년월일, 성별, 주소, 관심분야</t>
+          <t>19. 국내대리인 지정에 관한 사항</t>
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="8" t="inlineStr">
-        <is>
-          <t>Optional Items: Date of birth, Gender, Address, Areas of interest.</t>
-        </is>
-      </c>
+      <c r="H56" s="8" t="n"/>
       <c r="I56" s="5" t="n"/>
       <c r="J56" s="9" t="inlineStr">
         <is>
@@ -51650,7 +51570,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제3조 처리하는 개인정보의 항목</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -51666,15 +51586,11 @@
       <c r="E57" s="5" t="n"/>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>3. 인터넷 서비스 이용 과정에서 아래 개인정보 항목이 자동으로 생성되어 수집될 수 있습니다.</t>
+          <t>20. 정보주체의 권익침해 구제방법</t>
         </is>
       </c>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="8" t="inlineStr">
-        <is>
-          <t>The following personal information items may be automatically generated and collected during the process of using internet services:</t>
-        </is>
-      </c>
+      <c r="H57" s="8" t="n"/>
       <c r="I57" s="5" t="n"/>
       <c r="J57" s="9" t="inlineStr">
         <is>
@@ -51688,7 +51604,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제3조 처리하는 개인정보의 항목</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -51704,15 +51620,11 @@
       <c r="E58" s="5" t="n"/>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>4. IP주소, 쿠키, MAC주소, 서비스 이용기록, 방문기록, 불량 이용기록 등</t>
+          <t>21. 영상정보처리기기 운영·관리에 관한 사항</t>
         </is>
       </c>
       <c r="G58" s="7" t="n"/>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t>IP address, Cookies, MAC address, service usage records, visit records, bad usage records, etc.</t>
-        </is>
-      </c>
+      <c r="H58" s="8" t="n"/>
       <c r="I58" s="5" t="n"/>
       <c r="J58" s="9" t="inlineStr">
         <is>
@@ -51726,12 +51638,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제4조 개인정보의 제3자 제공</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>조 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -51740,21 +51652,17 @@
         </is>
       </c>
       <c r="E59" s="5" t="n"/>
-      <c r="F59" s="10" t="inlineStr">
-        <is>
-          <t>제4조 (개인정보의 제3자 제공)</t>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>22. 개인정보 보호 자율적 활동 및 인증 현황</t>
         </is>
       </c>
       <c r="G59" s="7" t="n"/>
-      <c r="H59" s="8" t="inlineStr">
-        <is>
-          <t>Article 4 (Provision of Personal Information to Third Parties)</t>
-        </is>
-      </c>
+      <c r="H59" s="8" t="n"/>
       <c r="I59" s="5" t="n"/>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|23|h</t>
+          <t>policy|privacy|23|p</t>
         </is>
       </c>
     </row>
@@ -51764,12 +51672,12 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제4조 개인정보의 제3자 제공</t>
+          <t>개인정보처리방침 · 목차</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -51780,19 +51688,15 @@
       <c r="E60" s="5" t="n"/>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>회사는 이용자의 개인정보를 제1조(개인정보의 처리 목적)에서 명시한 범위 내에서만 처리하며, 이용자의 동의, 법률의 특별한 규정 등 개인정보 보호법 제17조 및 제18조에 해당하는 경우에만 개인정보를 제3자에게 제공합니다.</t>
+          <t>23. 개인정보 처리방침의 변경 및 이전 버전 관리</t>
         </is>
       </c>
       <c r="G60" s="7" t="n"/>
-      <c r="H60" s="8" t="inlineStr">
-        <is>
-          <t>The Company processes the personal information of users only within the scope specified in Article 1 (Purpose of Processing Personal Information), and provides personal information to third parties only in cases falling under Articles 17 and 18 of the Personal Information Protection Act, such as with the user's consent or special provisions of the law.</t>
-        </is>
-      </c>
+      <c r="H60" s="8" t="n"/>
       <c r="I60" s="5" t="n"/>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|24|li</t>
+          <t>policy|privacy|24|p</t>
         </is>
       </c>
     </row>
@@ -51802,12 +51706,12 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제4조 개인정보의 제3자 제공</t>
+          <t>개인정보처리방침 · 제1조 개인정보의 처리 목적</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>조 제목</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -51816,21 +51720,17 @@
         </is>
       </c>
       <c r="E61" s="5" t="n"/>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>현재 회사는 원칙적으로 이용자의 개인정보를 외부에 제공하지 않습니다.</t>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>제1조 (개인정보의 처리 목적)</t>
         </is>
       </c>
       <c r="G61" s="7" t="n"/>
-      <c r="H61" s="8" t="inlineStr">
-        <is>
-          <t>In principle, the Company does not provide users' personal information to external parties.</t>
-        </is>
-      </c>
+      <c r="H61" s="8" t="n"/>
       <c r="I61" s="5" t="n"/>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|25|li</t>
+          <t>policy|privacy|25|h</t>
         </is>
       </c>
     </row>
@@ -51840,12 +51740,12 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제5조 개인정보 처리의 위탁</t>
+          <t>개인정보처리방침 · 제1조 개인정보의 처리 목적</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>조 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -51854,21 +51754,17 @@
         </is>
       </c>
       <c r="E62" s="5" t="n"/>
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t>제5조 (개인정보 처리의 위탁)</t>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>회사는 다음의 목적을 위하여 최소한의 개인정보를 처리합니다. 처리하고 있는 개인정보는 다음의 목적 이외의 용도로는 이용되지 않으며, 이용 목적이 변경되는 경우에는 「개인정보 보호법」 제18조에 따라 별도의 동의를 받는 등 필요한 조치를 이행할 예정입니다.</t>
         </is>
       </c>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="8" t="inlineStr">
-        <is>
-          <t>Article 5 (Delegation of Personal Information Processing)</t>
-        </is>
-      </c>
+      <c r="H62" s="8" t="n"/>
       <c r="I62" s="5" t="n"/>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|26|h</t>
+          <t>policy|privacy|26|p</t>
         </is>
       </c>
     </row>
@@ -51878,12 +51774,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제5조 개인정보 처리의 위탁</t>
+          <t>개인정보처리방침 · 제1조 개인정보의 처리 목적</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -51894,19 +51790,15 @@
       <c r="E63" s="5" t="n"/>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>1. 회사는 현재 개인정보 처리업무를 위탁하고 있지 않습니다.</t>
+          <t>1. 회원 가입 및 관리: 회원 가입의사 확인, 회원제 서비스 제공에 따른 본인 식별·인증, 회원자격 유지·관리, 서비스 부정이용 방지.</t>
         </is>
       </c>
       <c r="G63" s="7" t="n"/>
-      <c r="H63" s="8" t="inlineStr">
-        <is>
-          <t>The Company does not currently entrust the processing of personal information to external parties.</t>
-        </is>
-      </c>
+      <c r="H63" s="8" t="n"/>
       <c r="I63" s="5" t="n"/>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|27|li</t>
+          <t>policy|privacy|27|p</t>
         </is>
       </c>
     </row>
@@ -51916,12 +51808,12 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제5조 개인정보 처리의 위탁</t>
+          <t>개인정보처리방침 · 제1조 개인정보의 처리 목적</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -51932,19 +51824,15 @@
       <c r="E64" s="5" t="n"/>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>2. 향후 회사는 위탁계약을 체결하는 경우, 개인정보 보호법 제26조에 따라 위탁업무 수행목적 외 개인정보 처리금지, 기술적·관리적 보호조치, 수탁자에 대한 관리·감독, 손해배상 등 책임에 관한 사항을 계약서 등 명문으로 규정할 예정입니다.</t>
+          <t>2. 재화 또는 서비스 제공: 물품 배송, 서비스 제공, 계약서·청구서 발송, 맞춤서비스 제공, 본인인증, 결제 및 정산.</t>
         </is>
       </c>
       <c r="G64" s="7" t="n"/>
-      <c r="H64" s="8" t="inlineStr">
-        <is>
-          <t>If the Company enters into an entrustment contract in the future, it will specify matters regarding the prohibition of personal information processing other than for the purpose of performing entrusted tasks, technical and managerial protection measures, management and supervision of the trustee, and liability such as compensation for damages in documents such as contracts in accordance with Article 26 of the Personal Information Protection Act.</t>
-        </is>
-      </c>
+      <c r="H64" s="8" t="n"/>
       <c r="I64" s="5" t="n"/>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|28|li</t>
+          <t>policy|privacy|28|p</t>
         </is>
       </c>
     </row>
@@ -51954,12 +51842,12 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제6조 정보주체의 권리·의무 및 그 행사방법</t>
+          <t>개인정보처리방침 · 제1조 개인정보의 처리 목적</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>조 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -51968,21 +51856,17 @@
         </is>
       </c>
       <c r="E65" s="5" t="n"/>
-      <c r="F65" s="10" t="inlineStr">
-        <is>
-          <t>제6조 (정보주체의 권리·의무 및 그 행사방법)</t>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>3. 고충 처리: 민원인의 신원 확인, 민원사항 확인, 사실조사를 위한 연락·통지, 처리결과 통보.</t>
         </is>
       </c>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="8" t="inlineStr">
-        <is>
-          <t>Article 6 (Rights and Obligations of Information Subjects and Methods of Exercise)</t>
-        </is>
-      </c>
+      <c r="H65" s="8" t="n"/>
       <c r="I65" s="5" t="n"/>
       <c r="J65" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|29|h</t>
+          <t>policy|privacy|29|p</t>
         </is>
       </c>
     </row>
@@ -51992,12 +51876,12 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제6조 정보주체의 권리·의무 및 그 행사방법</t>
+          <t>개인정보처리방침 · 제2조 처리하는 개인정보 항목 및 법적 근거</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>조 제목</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -52006,21 +51890,17 @@
         </is>
       </c>
       <c r="E66" s="5" t="n"/>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>정보주체는 회사에 대해 언제든지 개인정보 열람·정정·삭제·처리정지 요구 등의 권리를 행사할 수 있습니다.</t>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>제2조 (처리하는 개인정보 항목 및 법적 근거)</t>
         </is>
       </c>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="8" t="inlineStr">
-        <is>
-          <t>The information subject may exercise the right to request access to, correction of, deletion of, or suspension of processing of personal information at any time against the Company.</t>
-        </is>
-      </c>
+      <c r="H66" s="8" t="n"/>
       <c r="I66" s="5" t="n"/>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|30|li</t>
+          <t>policy|privacy|30|h</t>
         </is>
       </c>
     </row>
@@ -52030,12 +51910,12 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제6조 정보주체의 권리·의무 및 그 행사방법</t>
+          <t>개인정보처리방침 · 제2조 처리하는 개인정보 항목 및 법적 근거</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -52046,19 +51926,15 @@
       <c r="E67" s="5" t="n"/>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>제1항에 따른 권리 행사는 회사에 대해 서면, 전자우편, 모사전송(FAX) 등을 통하여 하실 수 있으며 회사는 이에 대해 지체 없이 조치하겠습니다.</t>
+          <t>회사는 관련 법령에 따라 정보주체의 동의 없이 처리하는 개인정보 항목과 동의를 받아 처리하는 개인정보 항목을 명확히 구분하여 공개합니다.</t>
         </is>
       </c>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>The exercise of rights pursuant to Paragraph 1 may be made in writing, by email, or by facsimile (FAX) to the Company, and the Company will take action without delay.</t>
-        </is>
-      </c>
+      <c r="H67" s="8" t="n"/>
       <c r="I67" s="5" t="n"/>
       <c r="J67" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|31|li</t>
+          <t>policy|privacy|31|p</t>
         </is>
       </c>
     </row>
@@ -52068,12 +51944,12 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제6조 정보주체의 권리·의무 및 그 행사방법</t>
+          <t>개인정보처리방침 · 제2조 처리하는 개인정보 항목 및 법적 근거</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -52084,19 +51960,15 @@
       <c r="E68" s="5" t="n"/>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>제1항에 따른 권리 행사는 정보주체의 법정대리인이나 위임을 받은 자 등 대리인을 통하여 하실 수 있습니다.</t>
+          <t>1. 정보주체의 동의 없이 처리하는 개인정보 항목</t>
         </is>
       </c>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>The exercise of rights under Paragraph 1 may be made through a legal representative of the information subject or a person who has been delegated.</t>
-        </is>
-      </c>
+      <c r="H68" s="8" t="n"/>
       <c r="I68" s="5" t="n"/>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|32|li</t>
+          <t>policy|privacy|32|p</t>
         </is>
       </c>
     </row>
@@ -52106,12 +51978,12 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제7조 개인정보의 파기</t>
+          <t>개인정보처리방침 · 제2조 처리하는 개인정보 항목 및 법적 근거</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>조 제목</t>
+          <t>목록</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -52120,21 +51992,17 @@
         </is>
       </c>
       <c r="E69" s="5" t="n"/>
-      <c r="F69" s="10" t="inlineStr">
-        <is>
-          <t>제7조 (개인정보의 파기)</t>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>• 회원 서비스 운영 및 계약 이행</t>
         </is>
       </c>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="8" t="inlineStr">
-        <is>
-          <t>Article 7 (Destruction of Personal Information)</t>
-        </is>
-      </c>
+      <c r="H69" s="8" t="n"/>
       <c r="I69" s="5" t="n"/>
       <c r="J69" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|33|h</t>
+          <t>policy|privacy|33|li</t>
         </is>
       </c>
     </row>
@@ -52144,7 +52012,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제7조 개인정보의 파기</t>
+          <t>개인정보처리방침 · 제2조 처리하는 개인정보 항목 및 법적 근거</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -52160,15 +52028,11 @@
       <c r="E70" s="5" t="n"/>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>회사는 개인정보 보유기간의 경과, 처리목적 달성 등 개인정보가 불필요하게 되었을 때에는 지체 없이 해당 개인정보를 파기합니다.</t>
+          <t>- 법적 근거: 「개인정보 보호법」 제15조 제1항 제4호(계약 체결·이행)</t>
         </is>
       </c>
       <c r="G70" s="7" t="n"/>
-      <c r="H70" s="8" t="inlineStr">
-        <is>
-          <t>The Company destroys personal information without delay when it becomes unnecessary, such as the expiration of the retention period or achievement of the processing purpose.</t>
-        </is>
-      </c>
+      <c r="H70" s="8" t="n"/>
       <c r="I70" s="5" t="n"/>
       <c r="J70" s="9" t="inlineStr">
         <is>
@@ -52182,7 +52046,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제7조 개인정보의 파기</t>
+          <t>개인정보처리방침 · 제2조 처리하는 개인정보 항목 및 법적 근거</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -52198,15 +52062,11 @@
       <c r="E71" s="5" t="n"/>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>전자적 파일 형태의 정보는 기록을 재생할 수 없는 기술적 방법을 사용하며, 종이 문서에 출력된 개인정보는 분쇄기로 분쇄하거나 소각을 통하여 파기합니다.</t>
+          <t>- 처리 항목: 성명, 이메일 주소, 아이디(ID), 암호화된 비밀번호, 휴대전화번호</t>
         </is>
       </c>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="8" t="inlineStr">
-        <is>
-          <t>Information in the form of electronic files shall be destroyed using technical methods that cannot reproduce records, and personal information printed on paper shall be destroyed by shredding or incineration.</t>
-        </is>
-      </c>
+      <c r="H71" s="8" t="n"/>
       <c r="I71" s="5" t="n"/>
       <c r="J71" s="9" t="inlineStr">
         <is>
@@ -52220,12 +52080,12 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제8조 개인정보의 안전성 확보 조치</t>
+          <t>개인정보처리방침 · 제2조 처리하는 개인정보 항목 및 법적 근거</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>조 제목</t>
+          <t>목록</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -52234,21 +52094,17 @@
         </is>
       </c>
       <c r="E72" s="5" t="n"/>
-      <c r="F72" s="10" t="inlineStr">
-        <is>
-          <t>제8조 (개인정보의 안전성 확보 조치)</t>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>• 서비스 이용 과정에서 자동 생성·수집되는 정보</t>
         </is>
       </c>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>Article 8 (Measures to Ensure the Safety of Personal Information)</t>
-        </is>
-      </c>
+      <c r="H72" s="8" t="n"/>
       <c r="I72" s="5" t="n"/>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|36|h</t>
+          <t>policy|privacy|36|li</t>
         </is>
       </c>
     </row>
@@ -52258,12 +52114,12 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제8조 개인정보의 안전성 확보 조치</t>
+          <t>개인정보처리방침 · 제2조 처리하는 개인정보 항목 및 법적 근거</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>소제목</t>
+          <t>목록</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -52274,19 +52130,15 @@
       <c r="E73" s="5" t="n"/>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>회사는 개인정보의 안전성 확보를 위해 다음과 같은 조치를 취하고 있습니다.</t>
+          <t>- 법적 근거: 「개인정보 보호법」 제15조 제1항 제4호(계약 체결·이행)</t>
         </is>
       </c>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>The Company takes the following measures to ensure the safety of personal information:</t>
-        </is>
-      </c>
+      <c r="H73" s="8" t="n"/>
       <c r="I73" s="5" t="n"/>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|37|s</t>
+          <t>policy|privacy|37|li</t>
         </is>
       </c>
     </row>
@@ -52296,7 +52148,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제8조 개인정보의 안전성 확보 조치</t>
+          <t>개인정보처리방침 · 제2조 처리하는 개인정보 항목 및 법적 근거</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -52312,15 +52164,11 @@
       <c r="E74" s="5" t="n"/>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>- 관리적 조치: 내부관리계획 수립·시행, 정기적 직원 교육 등</t>
+          <t>- 처리 항목: IP주소, 쿠키, 서비스 이용기록, 방문시각, 기기정보</t>
         </is>
       </c>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="8" t="inlineStr">
-        <is>
-          <t>Administrative Measures: Establishment and implementation of internal management plans, regular employee training, etc.</t>
-        </is>
-      </c>
+      <c r="H74" s="8" t="n"/>
       <c r="I74" s="5" t="n"/>
       <c r="J74" s="9" t="inlineStr">
         <is>
@@ -52334,12 +52182,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제8조 개인정보의 안전성 확보 조치</t>
+          <t>개인정보처리방침 · 제2조 처리하는 개인정보 항목 및 법적 근거</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -52350,19 +52198,15 @@
       <c r="E75" s="5" t="n"/>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>- 기술적 조치: 개인정보처리시스템 등의 접근권한 관리, 접근통제시스템 설치, 고유식별정보 등의 암호화, 보안프로그램 설치</t>
+          <t>2. 정보주체의 동의를 받아 처리하는 개인정보 항목</t>
         </is>
       </c>
       <c r="G75" s="7" t="n"/>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>Technical Measures: Management of access rights to personal information processing systems, installation of access control systems, encryption of unique identification information, and installation of security programs.</t>
-        </is>
-      </c>
+      <c r="H75" s="8" t="n"/>
       <c r="I75" s="5" t="n"/>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|39|li</t>
+          <t>policy|privacy|39|p</t>
         </is>
       </c>
     </row>
@@ -52372,7 +52216,7 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제8조 개인정보의 안전성 확보 조치</t>
+          <t>개인정보처리방침 · 제2조 처리하는 개인정보 항목 및 법적 근거</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -52388,15 +52232,11 @@
       <c r="E76" s="5" t="n"/>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>- 물리적 조치: 전산실, 자료보관실 등의 접근통제</t>
+          <t>• 마케팅 및 이벤트 정보 제공</t>
         </is>
       </c>
       <c r="G76" s="7" t="n"/>
-      <c r="H76" s="8" t="inlineStr">
-        <is>
-          <t>Physical Measures: Access control to computer rooms, data storage rooms, etc.</t>
-        </is>
-      </c>
+      <c r="H76" s="8" t="n"/>
       <c r="I76" s="5" t="n"/>
       <c r="J76" s="9" t="inlineStr">
         <is>
@@ -52410,12 +52250,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제9조 개인정보 자동 수집 장치의 설치·운영 및 거부에 관한 사항</t>
+          <t>개인정보처리방침 · 제2조 처리하는 개인정보 항목 및 법적 근거</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>조 제목</t>
+          <t>목록</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -52424,21 +52264,17 @@
         </is>
       </c>
       <c r="E77" s="5" t="n"/>
-      <c r="F77" s="10" t="inlineStr">
-        <is>
-          <t>제9조 (개인정보 자동 수집 장치의 설치·운영 및 거부에 관한 사항)</t>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>- 법적 근거: 「개인정보 보호법」 제15조 제1항 제1호(정보주체의 동의)</t>
         </is>
       </c>
       <c r="G77" s="7" t="n"/>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Article 9 (Installation/Operation of Automatic Personal Information Collection Devices and Matters Concerning Rejection)</t>
-        </is>
-      </c>
+      <c r="H77" s="8" t="n"/>
       <c r="I77" s="5" t="n"/>
       <c r="J77" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|41|h</t>
+          <t>policy|privacy|41|li</t>
         </is>
       </c>
     </row>
@@ -52448,7 +52284,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제9조 개인정보 자동 수집 장치의 설치·운영 및 거부에 관한 사항</t>
+          <t>개인정보처리방침 · 제2조 처리하는 개인정보 항목 및 법적 근거</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -52464,15 +52300,11 @@
       <c r="E78" s="5" t="n"/>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>회사는 이용자에게 개별적인 맞춤서비스를 제공하기 위해 이용정보를 저장하고 수시로 불러오는 ‘쿠키(cookie)’를 사용합니다.</t>
+          <t>- 수집 항목: 이메일 주소, 휴대전화번호, 마케팅 수신동의 여부</t>
         </is>
       </c>
       <c r="G78" s="7" t="n"/>
-      <c r="H78" s="8" t="inlineStr">
-        <is>
-          <t>The Company uses "cookies" to store and retrieve usage information from time to time to provide users with individual customized services.</t>
-        </is>
-      </c>
+      <c r="H78" s="8" t="n"/>
       <c r="I78" s="5" t="n"/>
       <c r="J78" s="9" t="inlineStr">
         <is>
@@ -52486,7 +52318,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제9조 개인정보 자동 수집 장치의 설치·운영 및 거부에 관한 사항</t>
+          <t>개인정보처리방침 · 제2조 처리하는 개인정보 항목 및 법적 근거</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -52502,15 +52334,11 @@
       <c r="E79" s="5" t="n"/>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>쿠키는 웹사이트를 운영하는데 이용되는 서버(http)가 이용자의 컴퓨터 브라우저에게 보내는 소량의 정보이며 이용자들의 PC 컴퓨터내의 하드디스크에 저장되기도 합니다.</t>
+          <t>- 보유 및 이용 기간: 회원 탈퇴 시 또는 동의 철회 시까지</t>
         </is>
       </c>
       <c r="G79" s="7" t="n"/>
-      <c r="H79" s="8" t="inlineStr">
-        <is>
-          <t>Cookies are small amounts of information sent by the server (http) used to operate the website to the user's computer browser and are sometimes stored on the hard disk of the user's PC.</t>
-        </is>
-      </c>
+      <c r="H79" s="8" t="n"/>
       <c r="I79" s="5" t="n"/>
       <c r="J79" s="9" t="inlineStr">
         <is>
@@ -52524,12 +52352,12 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제9조 개인정보 자동 수집 장치의 설치·운영 및 거부에 관한 사항</t>
+          <t>개인정보처리방침 · 제3조 14세 미만 아동의 개인정보 처리에 관한 사항</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>조 제목</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -52538,21 +52366,17 @@
         </is>
       </c>
       <c r="E80" s="5" t="n"/>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>· 쿠키의 사용 목적: 이용자가 방문한 각 서비스와 웹 사이트들에 대한 방문 및 이용형태, 인기 검색어, 보안접속 여부 등을 파악하여 이용자에게 최적화된 정보 제공을 위해 사용됩니다.</t>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>제3조 (14세 미만 아동의 개인정보 처리에 관한 사항)</t>
         </is>
       </c>
       <c r="G80" s="7" t="n"/>
-      <c r="H80" s="8" t="inlineStr">
-        <is>
-          <t>Purpose of use of cookies: They are used to provide optimized information to users by identifying the visit and usage patterns, popular search terms, and whether or not secure access is available for each service and website visited by the user.</t>
-        </is>
-      </c>
+      <c r="H80" s="8" t="n"/>
       <c r="I80" s="5" t="n"/>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|44|p</t>
+          <t>policy|privacy|44|h</t>
         </is>
       </c>
     </row>
@@ -52562,7 +52386,7 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제9조 개인정보 자동 수집 장치의 설치·운영 및 거부에 관한 사항</t>
+          <t>개인정보처리방침 · 제3조 14세 미만 아동의 개인정보 처리에 관한 사항</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -52578,15 +52402,11 @@
       <c r="E81" s="5" t="n"/>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>· 쿠키의 설치·운영 및 거부: 브라우저 상단의 도구 &gt; 인터넷 옵션 &gt; 개인정보 메뉴의 옵션 설정을 통해 쿠키 저장을 거부 할 수 있습니다. 쿠키 저장을 거부할 경우 맞춤형 서비스 이용에 어려움이 발생할 수 있습니다.</t>
+          <t>1. 회사는 원칙적으로 만 14세 미만 아동의 개인정보를 수집하지 않습니다.</t>
         </is>
       </c>
       <c r="G81" s="7" t="n"/>
-      <c r="H81" s="8" t="inlineStr">
-        <is>
-          <t>Installation, Operation, and Rejection of Cookies: You can refuse to store cookies through the option settings in the Tools &gt; Internet Options &gt; Privacy menu at the top of your browser. If you refuse to store cookies, you may experience difficulties in using customized services.</t>
-        </is>
-      </c>
+      <c r="H81" s="8" t="n"/>
       <c r="I81" s="5" t="n"/>
       <c r="J81" s="9" t="inlineStr">
         <is>
@@ -52600,12 +52420,12 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제10조 개인정보 보호책임자</t>
+          <t>개인정보처리방침 · 제3조 14세 미만 아동의 개인정보 처리에 관한 사항</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>조 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -52614,21 +52434,17 @@
         </is>
       </c>
       <c r="E82" s="5" t="n"/>
-      <c r="F82" s="10" t="inlineStr">
-        <is>
-          <t>제10조 (개인정보 보호책임자)</t>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>2. 만 14세 미만 아동의 개인정보를 수집·처리할 필요가 있는 경우, 법정대리인의 동의를 얻어 최소한의 정보만 수집하며 법정대리인의 성명, 연락처 등 최소한의 필수정보를 확인합니다.</t>
         </is>
       </c>
       <c r="G82" s="7" t="n"/>
-      <c r="H82" s="8" t="inlineStr">
-        <is>
-          <t>Article 10 (Privacy Officer)</t>
-        </is>
-      </c>
+      <c r="H82" s="8" t="n"/>
       <c r="I82" s="5" t="n"/>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|46|h</t>
+          <t>policy|privacy|46|p</t>
         </is>
       </c>
     </row>
@@ -52638,12 +52454,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제10조 개인정보 보호책임자</t>
+          <t>개인정보처리방침 · 제4조 개인정보의 처리 및 보유 기간</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>소제목</t>
+          <t>조 제목</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -52652,21 +52468,17 @@
         </is>
       </c>
       <c r="E83" s="5" t="n"/>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>회사는 개인정보 처리에 관한 업무를 총괄해서 책임지고, 개인정보 처리와 관련한 정보주체의 불만처리 및 피해구제 등을 위하여 아래와 같이 개인정보 보호책임자를 지정하고 있습니다.</t>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>제4조 (개인정보의 처리 및 보유 기간)</t>
         </is>
       </c>
       <c r="G83" s="7" t="n"/>
-      <c r="H83" s="8" t="inlineStr">
-        <is>
-          <t>The Company is responsible for the overall handling of personal information processing and has designated a Privacy Officer as follows to handle complaints and provide remedies for information subjects related to personal information processing.</t>
-        </is>
-      </c>
+      <c r="H83" s="8" t="n"/>
       <c r="I83" s="5" t="n"/>
       <c r="J83" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|47|s</t>
+          <t>policy|privacy|47|h</t>
         </is>
       </c>
     </row>
@@ -52676,12 +52488,12 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제10조 개인정보 보호책임자</t>
+          <t>개인정보처리방침 · 제4조 개인정보의 처리 및 보유 기간</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>소제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -52692,19 +52504,15 @@
       <c r="E84" s="5" t="n"/>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자</t>
+          <t>1. 회사는 법령에 따른 개인정보 보유·이용 기간 또는 정보주체로부터 개인정보 수집 시 동의받은 보유·이용 기간 내에서 개인정보를 처리·보유합니다.</t>
         </is>
       </c>
       <c r="G84" s="7" t="n"/>
-      <c r="H84" s="8" t="inlineStr">
-        <is>
-          <t>Privacy Officer</t>
-        </is>
-      </c>
+      <c r="H84" s="8" t="n"/>
       <c r="I84" s="5" t="n"/>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|48|s</t>
+          <t>policy|privacy|48|p</t>
         </is>
       </c>
     </row>
@@ -52714,12 +52522,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제10조 개인정보 보호책임자</t>
+          <t>개인정보처리방침 · 제4조 개인정보의 처리 및 보유 기간</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -52730,19 +52538,15 @@
       <c r="E85" s="5" t="n"/>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>- 성명: 김 상 호</t>
+          <t>2. 각각의 개인정보 처리 및 보유 기간은 다음과 같습니다.</t>
         </is>
       </c>
       <c r="G85" s="7" t="n"/>
-      <c r="H85" s="8" t="inlineStr">
-        <is>
-          <t>Name: Sang-ho Kim</t>
-        </is>
-      </c>
+      <c r="H85" s="8" t="n"/>
       <c r="I85" s="5" t="n"/>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|49|li</t>
+          <t>policy|privacy|49|p</t>
         </is>
       </c>
     </row>
@@ -52752,7 +52556,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제10조 개인정보 보호책임자</t>
+          <t>개인정보처리방침 · 제4조 개인정보의 처리 및 보유 기간</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -52768,15 +52572,11 @@
       <c r="E86" s="5" t="n"/>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>- 직책: 부 장</t>
+          <t>• 회원 가입 및 관리: 서비스 탈퇴 시까지 (단, 관계 법령 위반에 따른 수사·조사 진행 중인 경우 해당 수사·조사 종료 시까지)</t>
         </is>
       </c>
       <c r="G86" s="7" t="n"/>
-      <c r="H86" s="8" t="inlineStr">
-        <is>
-          <t>Position: Department Manager</t>
-        </is>
-      </c>
+      <c r="H86" s="8" t="n"/>
       <c r="I86" s="5" t="n"/>
       <c r="J86" s="9" t="inlineStr">
         <is>
@@ -52790,7 +52590,7 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제10조 개인정보 보호책임자</t>
+          <t>개인정보처리방침 · 제4조 개인정보의 처리 및 보유 기간</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -52806,15 +52606,11 @@
       <c r="E87" s="5" t="n"/>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>- 연락처: sangho.kim@aproele.com</t>
+          <t>• 전자상거래 등 관련 법령에 따른 보존:</t>
         </is>
       </c>
       <c r="G87" s="7" t="n"/>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t>Contact: sangho.kim@aproele.com</t>
-        </is>
-      </c>
+      <c r="H87" s="8" t="n"/>
       <c r="I87" s="5" t="n"/>
       <c r="J87" s="9" t="inlineStr">
         <is>
@@ -52828,7 +52624,7 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제10조 개인정보 보호책임자</t>
+          <t>개인정보처리방침 · 제4조 개인정보의 처리 및 보유 기간</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -52844,15 +52640,11 @@
       <c r="E88" s="5" t="n"/>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>※ 개인정보 보호 담당부서로 연결됩니다.</t>
+          <t>- 표시·광고에 관한 기록: 6개월</t>
         </is>
       </c>
       <c r="G88" s="7" t="n"/>
-      <c r="H88" s="8" t="inlineStr">
-        <is>
-          <t>※ You will be connected to the department in charge of personal information protection.</t>
-        </is>
-      </c>
+      <c r="H88" s="8" t="n"/>
       <c r="I88" s="5" t="n"/>
       <c r="J88" s="9" t="inlineStr">
         <is>
@@ -52866,12 +52658,12 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제11조 개인정보 열람청구</t>
+          <t>개인정보처리방침 · 제4조 개인정보의 처리 및 보유 기간</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>조 제목</t>
+          <t>목록</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -52880,21 +52672,17 @@
         </is>
       </c>
       <c r="E89" s="5" t="n"/>
-      <c r="F89" s="10" t="inlineStr">
-        <is>
-          <t>제11조 (개인정보 열람청구)</t>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>- 계약 또는 청약철회, 대금결제, 재화 등의 공급기록: 5년</t>
         </is>
       </c>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="8" t="inlineStr">
-        <is>
-          <t>Article 11 (Request for Access to Personal Information)</t>
-        </is>
-      </c>
+      <c r="H89" s="8" t="n"/>
       <c r="I89" s="5" t="n"/>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|53|h</t>
+          <t>policy|privacy|53|li</t>
         </is>
       </c>
     </row>
@@ -52904,12 +52692,12 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제11조 개인정보 열람청구</t>
+          <t>개인정보처리방침 · 제4조 개인정보의 처리 및 보유 기간</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>목록</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -52920,19 +52708,15 @@
       <c r="E90" s="5" t="n"/>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>정보주체는 개인정보 보호법 제35조에 따른 개인정보의 열람 청구를 아래의 부서에 할 수 있습니다.</t>
+          <t>- 소비자의 불만 또는 분쟁처리에 관한 기록: 3년</t>
         </is>
       </c>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="8" t="inlineStr">
-        <is>
-          <t>Information subjects may request access to personal information under Article 35 of the Personal Information Protection Act to the following department:</t>
-        </is>
-      </c>
+      <c r="H90" s="8" t="n"/>
       <c r="I90" s="5" t="n"/>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|54|p</t>
+          <t>policy|privacy|54|li</t>
         </is>
       </c>
     </row>
@@ -52942,12 +52726,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제11조 개인정보 열람청구</t>
+          <t>개인정보처리방침 · 제5조 개인정보의 파기 절차 및 방법</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>조 제목</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -52956,21 +52740,17 @@
         </is>
       </c>
       <c r="E91" s="5" t="n"/>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>- 부서명: AI/정보보안팀</t>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>제5조 (개인정보의 파기 절차 및 방법)</t>
         </is>
       </c>
       <c r="G91" s="7" t="n"/>
-      <c r="H91" s="8" t="inlineStr">
-        <is>
-          <t>Department: AI/Information Security Team</t>
-        </is>
-      </c>
+      <c r="H91" s="8" t="n"/>
       <c r="I91" s="5" t="n"/>
       <c r="J91" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|55|li</t>
+          <t>policy|privacy|55|h</t>
         </is>
       </c>
     </row>
@@ -52980,12 +52760,12 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제11조 개인정보 열람청구</t>
+          <t>개인정보처리방침 · 제5조 개인정보의 파기 절차 및 방법</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -52996,19 +52776,15 @@
       <c r="E92" s="5" t="n"/>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>- 담당자: 강 민 석</t>
+          <t>1. 회사는 개인정보 보유기간의 경과, 처리목적 달성 등 개인정보가 불필요하게 되었을 때에는 지체 없이 해당 개인정보를 파기합니다.</t>
         </is>
       </c>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="8" t="inlineStr">
-        <is>
-          <t>Person in Charge: Min-seok Kang</t>
-        </is>
-      </c>
+      <c r="H92" s="8" t="n"/>
       <c r="I92" s="5" t="n"/>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|56|li</t>
+          <t>policy|privacy|56|p</t>
         </is>
       </c>
     </row>
@@ -53018,12 +52794,12 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제11조 개인정보 열람청구</t>
+          <t>개인정보처리방침 · 제5조 개인정보의 파기 절차 및 방법</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -53034,19 +52810,15 @@
       <c r="E93" s="5" t="n"/>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>- 연락처: aproeleit@aproele.com</t>
+          <t>2. 파기 절차: 회사는 파기 사유가 발생한 개인정보를 선정하고, 회사의 개인정보 보호책임자의 승인을 받아 개인정보를 파기합니다.</t>
         </is>
       </c>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="8" t="inlineStr">
-        <is>
-          <t>Contact: aproeleit@aproele.com</t>
-        </is>
-      </c>
+      <c r="H93" s="8" t="n"/>
       <c r="I93" s="5" t="n"/>
       <c r="J93" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|57|li</t>
+          <t>policy|privacy|57|p</t>
         </is>
       </c>
     </row>
@@ -53056,12 +52828,12 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제12조 권익침해 구제방법</t>
+          <t>개인정보처리방침 · 제5조 개인정보의 파기 절차 및 방법</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>조 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -53070,21 +52842,17 @@
         </is>
       </c>
       <c r="E94" s="5" t="n"/>
-      <c r="F94" s="10" t="inlineStr">
-        <is>
-          <t>제12조 (권익침해 구제방법)</t>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>3. 파기 방법: 전자적 파일 형태의 정보는 기록을 재생할 수 없는 기술적 방법을 사용하여 삭제하며, 종이 문서에 기록된 개인정보는 분쇄기로 분쇄하거나 소각합니다.</t>
         </is>
       </c>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="8" t="inlineStr">
-        <is>
-          <t>Article 12 (Remedies for Infringement of Rights)</t>
-        </is>
-      </c>
+      <c r="H94" s="8" t="n"/>
       <c r="I94" s="5" t="n"/>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|58|h</t>
+          <t>policy|privacy|58|p</t>
         </is>
       </c>
     </row>
@@ -53094,12 +52862,12 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제12조 권익침해 구제방법</t>
+          <t>개인정보처리방침 · 제6조 개인정보의 제3자 제공에 관한 사항</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>조 제목</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -53108,21 +52876,17 @@
         </is>
       </c>
       <c r="E95" s="5" t="n"/>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>정보주체는 아래의 기관에 대해 개인정보 침해에 대한 피해구제, 상담 등을 문의하실 수 있습니다.</t>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>제6조 (개인정보의 제3자 제공에 관한 사항)</t>
         </is>
       </c>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="8" t="inlineStr">
-        <is>
-          <t>Information subjects may inquire with the following organizations for remedies and consultations regarding personal information infringement:</t>
-        </is>
-      </c>
+      <c r="H95" s="8" t="n"/>
       <c r="I95" s="5" t="n"/>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|59|p</t>
+          <t>policy|privacy|59|h</t>
         </is>
       </c>
     </row>
@@ -53132,12 +52896,12 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제12조 권익침해 구제방법</t>
+          <t>개인정보처리방침 · 제6조 개인정보의 제3자 제공에 관한 사항</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -53148,19 +52912,15 @@
       <c r="E96" s="5" t="n"/>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>- 개인정보 침해신고센터 (privacy.kisa.or.kr / 국번없이 118)</t>
+          <t>1. 회사는 정보주체의 동의, 법률의 특별한 규정 등 「개인정보 보호법」 제17조 및 제18조에 해당하는 경우에만 개인정보를 제3자에게 제공합니다.</t>
         </is>
       </c>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="8" t="inlineStr">
-        <is>
-          <t>Personal Information Infringement Report Center (privacy.kisa.or.kr / Dial 118 without area code)</t>
-        </is>
-      </c>
+      <c r="H96" s="8" t="n"/>
       <c r="I96" s="5" t="n"/>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|60|li</t>
+          <t>policy|privacy|60|p</t>
         </is>
       </c>
     </row>
@@ -53170,12 +52930,12 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제12조 권익침해 구제방법</t>
+          <t>개인정보처리방침 · 제6조 개인정보의 제3자 제공에 관한 사항</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -53186,19 +52946,15 @@
       <c r="E97" s="5" t="n"/>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>- 개인정보 분쟁조정위원회 (koprc.go.kr / 국번없이 1833-6972)</t>
+          <t>2. 회사는 원칙적으로 이용자의 개인정보를 외부에 제공하지 않으며, 제3자 제공이 발생하는 경우에는 제공받는 자, 제공 목적, 제공 항목, 보유·이용 기간을 명시하여 사전에 동의를 구합니다.</t>
         </is>
       </c>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="8" t="inlineStr">
-        <is>
-          <t>Personal Information Dispute Mediation Committee (koprc.go.kr / Dial 1833-6972 without area code)</t>
-        </is>
-      </c>
+      <c r="H97" s="8" t="n"/>
       <c r="I97" s="5" t="n"/>
       <c r="J97" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|61|li</t>
+          <t>policy|privacy|61|p</t>
         </is>
       </c>
     </row>
@@ -53208,12 +52964,12 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제12조 권익침해 구제방법</t>
+          <t>개인정보처리방침 · 제7조 추가적인 이용·제공 판단 기준</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>조 제목</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -53222,21 +52978,17 @@
         </is>
       </c>
       <c r="E98" s="5" t="n"/>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>- 대검찰청 사이버수사과 (spo.go.kr / 국번없이 1301)</t>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>제7조 (추가적인 이용·제공 판단 기준)</t>
         </is>
       </c>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="8" t="inlineStr">
-        <is>
-          <t>Supreme Prosecutors' Office Cyber Investigation Division (spo.go.kr / Dial 1301 without area code)</t>
-        </is>
-      </c>
+      <c r="H98" s="8" t="n"/>
       <c r="I98" s="5" t="n"/>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|62|li</t>
+          <t>policy|privacy|62|h</t>
         </is>
       </c>
     </row>
@@ -53246,12 +52998,12 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 제12조 권익침해 구제방법</t>
+          <t>개인정보처리방침 · 제7조 추가적인 이용·제공 판단 기준</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -53262,19 +53014,15 @@
       <c r="E99" s="5" t="n"/>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>- 경찰청 사이버수사국 (cyberbureau.police.go.kr / 국번없이 182)</t>
+          <t>회사는 「개인정보 보호법」 제15조 제3항 및 제17조 제4항, 동법 시행령 제14조의2에 따라 정보주체의 동의 없이 개인정보를 추가적으로 이용 또는 제공하는 경우 다음 각 호의 사항을 엄격히 고려합니다.</t>
         </is>
       </c>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="8" t="inlineStr">
-        <is>
-          <t>National Police Agency Cyber Bureau (cyberbureau.police.go.kr / Dial 182 without area code)</t>
-        </is>
-      </c>
+      <c r="H99" s="8" t="n"/>
       <c r="I99" s="5" t="n"/>
       <c r="J99" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|63|li</t>
+          <t>policy|privacy|63|p</t>
         </is>
       </c>
     </row>
@@ -53284,12 +53032,12 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 부칙</t>
+          <t>개인정보처리방침 · 제7조 추가적인 이용·제공 판단 기준</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>조 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -53298,21 +53046,17 @@
         </is>
       </c>
       <c r="E100" s="5" t="n"/>
-      <c r="F100" s="10" t="inlineStr">
-        <is>
-          <t>부 칙</t>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>1. 당초 수집 목적과 합리적으로 관련되어 있는지 여부</t>
         </is>
       </c>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="8" t="inlineStr">
-        <is>
-          <t>Addendum</t>
-        </is>
-      </c>
+      <c r="H100" s="8" t="n"/>
       <c r="I100" s="5" t="n"/>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>policy|privacy|64|h</t>
+          <t>policy|privacy|64|p</t>
         </is>
       </c>
     </row>
@@ -53322,7 +53066,7 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>개인정보처리방침 · 부칙</t>
+          <t>개인정보처리방침 · 제7조 추가적인 이용·제공 판단 기준</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -53338,15 +53082,11 @@
       <c r="E101" s="5" t="n"/>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>0. 이 지침은 2025년 12월 23일부터 시행한다.</t>
+          <t>2. 개인정보를 수집한 정황 또는 처리 관행에 비추어 볼 때 추가적인 이용·제공에 대한 예측 가능성이 있는지 여부</t>
         </is>
       </c>
       <c r="G101" s="7" t="n"/>
-      <c r="H101" s="8" t="inlineStr">
-        <is>
-          <t>This policy shall take effect on December 23, 2025.</t>
-        </is>
-      </c>
+      <c r="H101" s="8" t="n"/>
       <c r="I101" s="5" t="n"/>
       <c r="J101" s="9" t="inlineStr">
         <is>
@@ -53360,7 +53100,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>이메일무단수집거부</t>
+          <t>개인정보처리방침 · 제7조 추가적인 이용·제공 판단 기준</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -53376,19 +53116,15 @@
       <c r="E102" s="5" t="n"/>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>㈜에이프로는 본 홈페이지에 게시된 이메일 주소가 전자우편 수집 프로그램이나 그 밖의 기술적 장치를 이용하여 무단으로 수집되는 것을 거부합니다.</t>
+          <t>3. 정보주체의 이익을 부당하게 침해하는지 여부</t>
         </is>
       </c>
       <c r="G102" s="7" t="n"/>
-      <c r="H102" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Co., Ltd. rejects the unauthorized collection of email addresses posted on this website through the use of automated email collection programs or other technical devices. Please be advised that any violation of this policy may result in criminal punishment under the "Act on Promotion of Information and Communications Network Utilization and Information Protection, etc."</t>
-        </is>
-      </c>
+      <c r="H102" s="8" t="n"/>
       <c r="I102" s="5" t="n"/>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>policy|email|0|p</t>
+          <t>policy|privacy|66|p</t>
         </is>
       </c>
     </row>
@@ -53398,7 +53134,7 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>이메일무단수집거부</t>
+          <t>개인정보처리방침 · 제7조 추가적인 이용·제공 판단 기준</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
@@ -53414,19 +53150,15 @@
       <c r="E103" s="5" t="n"/>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>이를 위반할 시 「정보통신망 이용촉진 및 정보보호 등에 관한 법률」에 의해 형사 처벌될 수 있음을 유념하시기 바랍니다.</t>
+          <t>4. 가명처리 또는 암호화 등 안전성 확보에 필요한 조치를 하였는지 여부</t>
         </is>
       </c>
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="8" t="n"/>
-      <c r="I103" s="5" t="inlineStr">
-        <is>
-          <t>영문은 위 줄에 합쳐져 있음</t>
-        </is>
-      </c>
+      <c r="I103" s="5" t="n"/>
       <c r="J103" s="9" t="inlineStr">
         <is>
-          <t>policy|email|1|p</t>
+          <t>policy|privacy|67|p</t>
         </is>
       </c>
     </row>
@@ -53436,12 +53168,12 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>이메일무단수집거부</t>
+          <t>개인정보처리방침 · 제8조 개인정보 처리업무의 위탁에 관한 사항</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>소제목</t>
+          <t>조 제목</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -53450,21 +53182,17 @@
         </is>
       </c>
       <c r="E104" s="5" t="n"/>
-      <c r="F104" s="6" t="inlineStr">
-        <is>
-          <t>[관련 법령: 정보통신망 이용촉진 및 정보보호 등에 관한 법률]</t>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>제8조 (개인정보 처리업무의 위탁에 관한 사항)</t>
         </is>
       </c>
       <c r="G104" s="7" t="n"/>
-      <c r="H104" s="8" t="inlineStr">
-        <is>
-          <t>[Relevant Law: Act on Promotion of Information and Communications Network Utilization and Information Protection, etc.]</t>
-        </is>
-      </c>
+      <c r="H104" s="8" t="n"/>
       <c r="I104" s="5" t="n"/>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>policy|email|2|s</t>
+          <t>policy|privacy|68|h</t>
         </is>
       </c>
     </row>
@@ -53474,12 +53202,12 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>이메일무단수집거부</t>
+          <t>개인정보처리방침 · 제8조 개인정보 처리업무의 위탁에 관한 사항</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>소제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -53490,19 +53218,15 @@
       <c r="E105" s="5" t="n"/>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>제50조의 2 (전자우편주소의 무단 수집행위 등 금지)</t>
+          <t>1. 회사는 이용자의 개인정보 처리업무를 외부에 위탁하지 않고 직접 처리 및 관리하고 있습니다.</t>
         </is>
       </c>
       <c r="G105" s="7" t="n"/>
-      <c r="H105" s="8" t="inlineStr">
-        <is>
-          <t>Article 50-2 (Prohibition of Unauthorized Collection of E-mail Addresses, etc.)</t>
-        </is>
-      </c>
+      <c r="H105" s="8" t="n"/>
       <c r="I105" s="5" t="n"/>
       <c r="J105" s="9" t="inlineStr">
         <is>
-          <t>policy|email|3|s</t>
+          <t>policy|privacy|69|p</t>
         </is>
       </c>
     </row>
@@ -53512,7 +53236,7 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>이메일무단수집거부</t>
+          <t>개인정보처리방침 · 제8조 개인정보 처리업무의 위탁에 관한 사항</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
@@ -53528,19 +53252,15 @@
       <c r="E106" s="5" t="n"/>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>누구든지 전자우편주소의 수집을 거부하는 의사가 명시된 인터넷 홈페이지에서 자동으로 전자우편주소를 수집하는 프로그램 그 밖의 기술적 장치를 이용하여 전자우편주소를 수집하여서는 아니 된다.</t>
+          <t>2. 향후 원활한 서비스 제공을 위해 개인정보 처리업무를 외부에 위탁하게 될 경우, 위탁받는 자(수탁자)와 위탁하는 업무의 내용을 본 개인정보 처리방침을 통해 지체 없이 공개하고 법령에 따른 관리·감독을 수행하겠습니다.</t>
         </is>
       </c>
       <c r="G106" s="7" t="n"/>
-      <c r="H106" s="8" t="inlineStr">
-        <is>
-          <t>No person shall collect e-mail addresses from an Internet website where the intention to refuse the collection of e-mail addresses is manifested, by using a program or other technical device that automatically collects e-mail addresses.</t>
-        </is>
-      </c>
+      <c r="H106" s="8" t="n"/>
       <c r="I106" s="5" t="n"/>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>policy|email|4|p</t>
+          <t>policy|privacy|70|p</t>
         </is>
       </c>
     </row>
@@ -53550,12 +53270,12 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>이메일무단수집거부</t>
+          <t>개인정보처리방침 · 제9조 개인정보의 국외 수집 및 이전에 관한 사항</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>조 제목</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -53564,21 +53284,17 @@
         </is>
       </c>
       <c r="E107" s="5" t="n"/>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>누구든지 제1항의 규정을 위반하여 수집된 전자우편주소를 판매·유통하여서는 아니 된다.</t>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>제9조 (개인정보의 국외 수집 및 이전에 관한 사항)</t>
         </is>
       </c>
       <c r="G107" s="7" t="n"/>
-      <c r="H107" s="8" t="inlineStr">
-        <is>
-          <t>No person shall sell or distribute e-mail addresses collected in violation of Paragraph 1.</t>
-        </is>
-      </c>
+      <c r="H107" s="8" t="n"/>
       <c r="I107" s="5" t="n"/>
       <c r="J107" s="9" t="inlineStr">
         <is>
-          <t>policy|email|5|p</t>
+          <t>policy|privacy|71|h</t>
         </is>
       </c>
     </row>
@@ -53588,7 +53304,7 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>이메일무단수집거부</t>
+          <t>개인정보처리방침 · 제9조 개인정보의 국외 수집 및 이전에 관한 사항</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -53604,19 +53320,15 @@
       <c r="E108" s="5" t="n"/>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>누구든지 제1항 및 제2항의 규정에 의하여 수집·판매 및 유통이 금지된 전자우편주소임을 알고 이를 정보전송에 이용하여서는 아니 된다.</t>
+          <t>1. 회사는 이용자의 개인정보를 국외로 이전(제공, 조회, 처리위탁, 보관)하거나 국외에서 수집하여 처리하지 않습니다.</t>
         </is>
       </c>
       <c r="G108" s="7" t="n"/>
-      <c r="H108" s="8" t="inlineStr">
-        <is>
-          <t>No person shall use e-mail addresses for transmitting information, knowing that such e-mail addresses are those whose collection, sale, or distribution is prohibited under Paragraphs 1 and 2.</t>
-        </is>
-      </c>
+      <c r="H108" s="8" t="n"/>
       <c r="I108" s="5" t="n"/>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>policy|email|6|p</t>
+          <t>policy|privacy|72|p</t>
         </is>
       </c>
     </row>
@@ -53626,7 +53338,7 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>이메일무단수집거부</t>
+          <t>개인정보처리방침 · 제9조 개인정보의 국외 수집 및 이전에 관한 사항</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
@@ -53642,19 +53354,15 @@
       <c r="E109" s="5" t="n"/>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>제74조 (벌칙)</t>
+          <t>2. 모든 개인정보는 국내에 위치한 회사의 안전한 데이터 센터 및 자체 보안 시스템 내에서만 저장 및 처리됩니다.</t>
         </is>
       </c>
       <c r="G109" s="7" t="n"/>
-      <c r="H109" s="8" t="inlineStr">
-        <is>
-          <t>Article 74 (Penal Provisions)</t>
-        </is>
-      </c>
+      <c r="H109" s="8" t="n"/>
       <c r="I109" s="5" t="n"/>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>policy|email|7|p</t>
+          <t>policy|privacy|73|p</t>
         </is>
       </c>
     </row>
@@ -53664,12 +53372,12 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>이메일무단수집거부</t>
+          <t>개인정보처리방침 · 제10조 생성형 인공지능(AI) 서비스 개인정보 처리에 관한 사항</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>조 제목</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -53678,21 +53386,17 @@
         </is>
       </c>
       <c r="E110" s="5" t="n"/>
-      <c r="F110" s="6" t="inlineStr">
-        <is>
-          <t>다음 각호의 어느 하나에 해당하는 자는 1년 이하의 징역 또는 1천만 원 이하의 벌금에 처한다.</t>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>제10조 (생성형 인공지능(AI) 서비스 개인정보 처리에 관한 사항)</t>
         </is>
       </c>
       <c r="G110" s="7" t="n"/>
-      <c r="H110" s="8" t="inlineStr">
-        <is>
-          <t>Any person who falls under any of the following shall be punished by imprisonment with labor for not more than one year or by a fine not exceeding 10 million won:</t>
-        </is>
-      </c>
+      <c r="H110" s="8" t="n"/>
       <c r="I110" s="5" t="n"/>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>policy|email|8|p</t>
+          <t>policy|privacy|74|h</t>
         </is>
       </c>
     </row>
@@ -53702,7 +53406,7 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>이메일무단수집거부</t>
+          <t>개인정보처리방침 · 제10조 생성형 인공지능(AI) 서비스 개인정보 처리에 관한 사항</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
@@ -53718,19 +53422,15 @@
       <c r="E111" s="5" t="n"/>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>제50조의 2의 규정을 위반하여 전자우편 주소를 수집·판매·유통하거나 정보 전송에 이용한 자</t>
+          <t>1. 회사는 이용자에게 대화형 챗봇, 콘텐츠 자동 생성 등 생성형 인공지능(AI) 서비스를 제공하지 않으며, 이에 따라 생성형 AI 서비스 운영을 위한 개인정보를 수집·처리하지 않습니다.</t>
         </is>
       </c>
       <c r="G111" s="7" t="n"/>
-      <c r="H111" s="8" t="inlineStr">
-        <is>
-          <t>A person who collects, sells, distributes, or uses e-mail addresses for information transmission in violation of Article 50-2.</t>
-        </is>
-      </c>
+      <c r="H111" s="8" t="n"/>
       <c r="I111" s="5" t="n"/>
       <c r="J111" s="9" t="inlineStr">
         <is>
-          <t>policy|email|9|p</t>
+          <t>policy|privacy|75|p</t>
         </is>
       </c>
     </row>
@@ -53740,7 +53440,7 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>이메일무단수집거부</t>
+          <t>개인정보처리방침 · 제10조 생성형 인공지능(AI) 서비스 개인정보 처리에 관한 사항</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -53756,17 +53456,2097 @@
       <c r="E112" s="5" t="n"/>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>게시일: 2025년 12월 23일</t>
+          <t>2. 향후 회사가 생성형 AI 기반 서비스를 도입·운영하게 될 경우, 관련 법령 및 2026년 「생성형 인공지능(AI) 서비스 개인정보 처리방침 작성지침」에 따라 개인정보 처리 현황, 프롬프트 보관 정책, AI 모델 학습 활용 여부 및 정보주체의 학습 거부권(Opt-out) 행사 방법 등을 사전에 명확히 고지하겠습니다.</t>
         </is>
       </c>
       <c r="G112" s="7" t="n"/>
-      <c r="H112" s="8" t="inlineStr">
-        <is>
-          <t>Date of Publication: December 23, 2025</t>
-        </is>
-      </c>
+      <c r="H112" s="8" t="n"/>
       <c r="I112" s="5" t="n"/>
       <c r="J112" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|76|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제11조 개인정보의 안전성 확보조치에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>조 제목</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="n"/>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>제11조 (개인정보의 안전성 확보조치에 관한 사항)</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="n"/>
+      <c r="H113" s="8" t="n"/>
+      <c r="I113" s="5" t="n"/>
+      <c r="J113" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|77|h</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제11조 개인정보의 안전성 확보조치에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="n"/>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>회사는 「개인정보 보호법」 제29조에 따라 개인정보의 안전성 확보를 위해 다음과 같은 관리적·기술적·물리적 조치를 취하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="n"/>
+      <c r="H114" s="8" t="n"/>
+      <c r="I114" s="5" t="n"/>
+      <c r="J114" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|78|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제11조 개인정보의 안전성 확보조치에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n"/>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>1. 관리적 조치: 내부관리계획 수립·시행, 정기적 임직원 개인정보 보호 교육.</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="n"/>
+      <c r="H115" s="8" t="n"/>
+      <c r="I115" s="5" t="n"/>
+      <c r="J115" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|79|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제11조 개인정보의 안전성 확보조치에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="n"/>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>2. 기술적 조치: 개인정보처리시스템 접근권한 관리, 접근통제시스템 운영, 고유식별정보 암호화, 보안프로그램 설치 및 주기적 점검.</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="n"/>
+      <c r="H116" s="8" t="n"/>
+      <c r="I116" s="5" t="n"/>
+      <c r="J116" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|80|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제11조 개인정보의 안전성 확보조치에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="n"/>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>3. 물리적 조치: 전산실 및 자료보관실의 접근통제.</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="n"/>
+      <c r="H117" s="8" t="n"/>
+      <c r="I117" s="5" t="n"/>
+      <c r="J117" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|81|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제12조 민감정보의 공개 가능성 및 비공개 선택 방법</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>조 제목</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="n"/>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t>제12조 (민감정보의 공개 가능성 및 비공개 선택 방법)</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="n"/>
+      <c r="H118" s="8" t="n"/>
+      <c r="I118" s="5" t="n"/>
+      <c r="J118" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|82|h</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제12조 민감정보의 공개 가능성 및 비공개 선택 방법</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="n"/>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>1. 회사가 제공하는 서비스 중 게시판 등 이용자 간 공개 영역에 게시글을 작성할 경우, 이용자가 직접 입력한 민감정보가 타인에게 공개될 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="n"/>
+      <c r="H119" s="8" t="n"/>
+      <c r="I119" s="5" t="n"/>
+      <c r="J119" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|83|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제12조 민감정보의 공개 가능성 및 비공개 선택 방법</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n"/>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>2. 이용자는 게시글 작성 시 비공개 설정을 선택하거나 작성 후 수정·삭제 기능을 통해 민감정보 노출을 방지할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="n"/>
+      <c r="H120" s="8" t="n"/>
+      <c r="I120" s="5" t="n"/>
+      <c r="J120" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|84|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제13조 가명정보 처리에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>조 제목</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="n"/>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t>제13조 (가명정보 처리에 관한 사항)</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="n"/>
+      <c r="H121" s="8" t="n"/>
+      <c r="I121" s="5" t="n"/>
+      <c r="J121" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|85|h</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제13조 가명정보 처리에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n"/>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>1. 회사는 「개인정보 보호법」 제28조의2에 따라 서비스 이용 통계 분석 및 품질 개선(과학적 연구)을 위하여 개인정보를 가명처리하여 활용할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="n"/>
+      <c r="H122" s="8" t="n"/>
+      <c r="I122" s="5" t="n"/>
+      <c r="J122" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|86|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제13조 가명정보 처리에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="n"/>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>2. 가명정보를 처리하는 경우 가명정보와 추가정보의 분리 보관, 접근 권한 분리, 처리기록 보관 등 법률에서 정한 안전성 확보조치를 엄격히 준수합니다.</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="n"/>
+      <c r="H123" s="8" t="n"/>
+      <c r="I123" s="5" t="n"/>
+      <c r="J123" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|87|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제14조 개인정보 자동 수집 장치의 설치·운영 및 거부에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>조 제목</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="n"/>
+      <c r="F124" s="10" t="inlineStr">
+        <is>
+          <t>제14조 (개인정보 자동 수집 장치의 설치·운영 및 거부에 관한 사항)</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="n"/>
+      <c r="H124" s="8" t="n"/>
+      <c r="I124" s="5" t="n"/>
+      <c r="J124" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|88|h</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제14조 개인정보 자동 수집 장치의 설치·운영 및 거부에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="n"/>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>1. 회사는 이용자에게 개별적인 맞춤형 서비스를 제공하기 위해 정보를 저장하고 수시로 불러오는 '쿠키(cookie)'를 사용합니다.</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="n"/>
+      <c r="H125" s="8" t="n"/>
+      <c r="I125" s="5" t="n"/>
+      <c r="J125" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|89|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제14조 개인정보 자동 수집 장치의 설치·운영 및 거부에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="n"/>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>2. 쿠키 설정 및 거부 방법: 웹브라우저 상단 [설정] &gt; [개인정보 및 보안] &gt; [쿠키 및 기타 사이트 데이터] 메뉴를 통해 쿠키 저장을 거부할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="n"/>
+      <c r="H126" s="8" t="n"/>
+      <c r="I126" s="5" t="n"/>
+      <c r="J126" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|90|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제15조 온라인 행태정보 수집·이용 및 거부에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>조 제목</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="n"/>
+      <c r="F127" s="10" t="inlineStr">
+        <is>
+          <t>제15조 (온라인 행태정보 수집·이용 및 거부에 관한 사항)</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="n"/>
+      <c r="H127" s="8" t="n"/>
+      <c r="I127" s="5" t="n"/>
+      <c r="J127" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|91|h</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제15조 온라인 행태정보 수집·이용 및 거부에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="n"/>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>회사는 이용자의 방문기록 등 제한된 행태정보를 이용해 맞춤형 혜택을 안내할 수 있으며, 이용자는 브라우저 보안 설정을 통해 행태정보 수집 동의를 철회하거나 거부할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="n"/>
+      <c r="H128" s="8" t="n"/>
+      <c r="I128" s="5" t="n"/>
+      <c r="J128" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|92|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제16조 정보주체와 법정대리인의 권리·의무 및 그 행사방법</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>조 제목</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="n"/>
+      <c r="F129" s="10" t="inlineStr">
+        <is>
+          <t>제16조 (정보주체와 법정대리인의 권리·의무 및 그 행사방법)</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="n"/>
+      <c r="H129" s="8" t="n"/>
+      <c r="I129" s="5" t="n"/>
+      <c r="J129" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|93|h</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제16조 정보주체와 법정대리인의 권리·의무 및 그 행사방법</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="n"/>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>1. 정보주체는 회사에 대해 언제든지 개인정보 열람·정정·삭제·처리정지 요구 및 전송요구권을 행사할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="n"/>
+      <c r="H130" s="8" t="n"/>
+      <c r="I130" s="5" t="n"/>
+      <c r="J130" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|94|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제16조 정보주체와 법정대리인의 권리·의무 및 그 행사방법</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="n"/>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>2. 권리 행사는 회사에 대해 서면, 이메일, 전화 등을 통해 하실 수 있으며 회사는 이에 대해 지체 없이 조치하겠습니다.</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="n"/>
+      <c r="H131" s="8" t="n"/>
+      <c r="I131" s="5" t="n"/>
+      <c r="J131" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|95|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제17조 자동화된 결정에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>조 제목</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="n"/>
+      <c r="F132" s="10" t="inlineStr">
+        <is>
+          <t>제17조 (자동화된 결정에 관한 사항)</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="n"/>
+      <c r="H132" s="8" t="n"/>
+      <c r="I132" s="5" t="n"/>
+      <c r="J132" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|96|h</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제17조 자동화된 결정에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="n"/>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>1. 회사는 인공지능 등 완전히 자동화된 시스템을 통해 정보주체의 권리·의무에 중대한 영향을 미치는 결정을 내리지 않습니다.</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="n"/>
+      <c r="H133" s="8" t="n"/>
+      <c r="I133" s="5" t="n"/>
+      <c r="J133" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|97|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제17조 자동화된 결정에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="n"/>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>2. 향후 자동화된 결정이 도입될 경우, 결정 기준 및 절차를 사전에 공개하고 이의제기 및 설명요구 절차를 제공하겠습니다.</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="n"/>
+      <c r="H134" s="8" t="n"/>
+      <c r="I134" s="5" t="n"/>
+      <c r="J134" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|98|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제18조 개인정보 보호책임자 및 고충처리 부서</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>조 제목</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="n"/>
+      <c r="F135" s="10" t="inlineStr">
+        <is>
+          <t>제18조 (개인정보 보호책임자 및 고충처리 부서)</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="n"/>
+      <c r="H135" s="8" t="n"/>
+      <c r="I135" s="5" t="n"/>
+      <c r="J135" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|99|h</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제18조 개인정보 보호책임자 및 고충처리 부서</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n"/>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>회사는 개인정보 처리에 관한 업무를 총괄해서 책임지고, 개인정보 처리와 관련한 정보주체의 고충처리 및 피해구제 등을 위하여 아래와 같이 개인정보 보호책임자 및 담당부서를 지정하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="n"/>
+      <c r="H136" s="8" t="n"/>
+      <c r="I136" s="5" t="n"/>
+      <c r="J136" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|100|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제18조 개인정보 보호책임자 및 고충처리 부서</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>소제목</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n"/>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>개인정보 보호책임자 (CPO)</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="n"/>
+      <c r="H137" s="8" t="n"/>
+      <c r="I137" s="5" t="n"/>
+      <c r="J137" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|101|s</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제18조 개인정보 보호책임자 및 고충처리 부서</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n"/>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>• 성명: 김 상 호</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="n"/>
+      <c r="H138" s="8" t="n"/>
+      <c r="I138" s="5" t="n"/>
+      <c r="J138" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|102|li</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제18조 개인정보 보호책임자 및 고충처리 부서</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n"/>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>• 직책: AI정보보안부 부장</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="n"/>
+      <c r="H139" s="8" t="n"/>
+      <c r="I139" s="5" t="n"/>
+      <c r="J139" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|103|li</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제18조 개인정보 보호책임자 및 고충처리 부서</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n"/>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>• 연락처: sangho.kim@aproele.com</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="n"/>
+      <c r="H140" s="8" t="n"/>
+      <c r="I140" s="5" t="n"/>
+      <c r="J140" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|104|li</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제18조 개인정보 보호책임자 및 고충처리 부서</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>소제목</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="n"/>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>개인정보 보호 담당부서</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="n"/>
+      <c r="H141" s="8" t="n"/>
+      <c r="I141" s="5" t="n"/>
+      <c r="J141" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|105|s</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제18조 개인정보 보호책임자 및 고충처리 부서</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="n"/>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>• 부서명: AI정보보안팀</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="n"/>
+      <c r="H142" s="8" t="n"/>
+      <c r="I142" s="5" t="n"/>
+      <c r="J142" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|106|li</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제18조 개인정보 보호책임자 및 고충처리 부서</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="n"/>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>• 담당자: 강민석 프로</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="n"/>
+      <c r="H143" s="8" t="n"/>
+      <c r="I143" s="5" t="n"/>
+      <c r="J143" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|107|li</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제18조 개인정보 보호책임자 및 고충처리 부서</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="n"/>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>• 문의처: aproeleit@aproele.com</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="n"/>
+      <c r="H144" s="8" t="n"/>
+      <c r="I144" s="5" t="n"/>
+      <c r="J144" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|108|li</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제19조 국내대리인 지정에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>조 제목</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="n"/>
+      <c r="F145" s="10" t="inlineStr">
+        <is>
+          <t>제19조 (국내대리인 지정에 관한 사항)</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="n"/>
+      <c r="H145" s="8" t="n"/>
+      <c r="I145" s="5" t="n"/>
+      <c r="J145" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|109|h</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제19조 국내대리인 지정에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="n"/>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>회사는 국내에 본사를 둔 법인으로서 「개인정보 보호법」 제39조의11에 따른 국내대리인 지정 의무 대상에 해당하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="n"/>
+      <c r="H146" s="8" t="n"/>
+      <c r="I146" s="5" t="n"/>
+      <c r="J146" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|110|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제20조 정보주체의 권익침해 구제방법</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>조 제목</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="n"/>
+      <c r="F147" s="10" t="inlineStr">
+        <is>
+          <t>제20조 (정보주체의 권익침해 구제방법)</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="n"/>
+      <c r="H147" s="8" t="n"/>
+      <c r="I147" s="5" t="n"/>
+      <c r="J147" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|111|h</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제20조 정보주체의 권익침해 구제방법</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="n"/>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>정보주체는 개인정보침해로 인한 구제를 받기 위하여 아래의 기관에 분쟁해결이나 상담 등을 신청할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="n"/>
+      <c r="H148" s="8" t="n"/>
+      <c r="I148" s="5" t="n"/>
+      <c r="J148" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|112|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제20조 정보주체의 권익침해 구제방법</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n"/>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>• 개인정보 분쟁조정위원회: (국번없이) 1833-6972 (www.kopico.go.kr)</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="n"/>
+      <c r="H149" s="8" t="n"/>
+      <c r="I149" s="5" t="n"/>
+      <c r="J149" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|113|li</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제20조 정보주체의 권익침해 구제방법</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="n"/>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>• 개인정보침해신고센터: (국번없이) 118 (privacy.kisa.or.kr)</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="n"/>
+      <c r="H150" s="8" t="n"/>
+      <c r="I150" s="5" t="n"/>
+      <c r="J150" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|114|li</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제20조 정보주체의 권익침해 구제방법</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="n"/>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>• 대검찰청: (국번없이) 1301 (www.spo.go.kr)</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="n"/>
+      <c r="H151" s="8" t="n"/>
+      <c r="I151" s="5" t="n"/>
+      <c r="J151" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|115|li</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제20조 정보주체의 권익침해 구제방법</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="n"/>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>• 경찰청: (국번없이) 182 (ecrm.police.go.kr)</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="n"/>
+      <c r="H152" s="8" t="n"/>
+      <c r="I152" s="5" t="n"/>
+      <c r="J152" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|116|li</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제20조 정보주체의 권익침해 구제방법</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="n"/>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>• 아동·청소년 지우개(잊힐 권리) 서비스: (전화) 02-2135-8362 / (누리집) privacy.go.kr/delete.do</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="n"/>
+      <c r="H153" s="8" t="n"/>
+      <c r="I153" s="5" t="n"/>
+      <c r="J153" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|117|li</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제21조 영상정보처리기기 운영·관리에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>조 제목</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="n"/>
+      <c r="F154" s="10" t="inlineStr">
+        <is>
+          <t>제21조 (영상정보처리기기 운영·관리에 관한 사항)</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="n"/>
+      <c r="H154" s="8" t="n"/>
+      <c r="I154" s="5" t="n"/>
+      <c r="J154" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|118|h</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제21조 영상정보처리기기 운영·관리에 관한 사항</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="n"/>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>회사는 시설 보안 및 화재 예방을 위해 고정형 영상정보처리기기(CCTV)를 운영하고 있으며, 세부 설치 수량 및 촬영 범위는 사업장 안내판을 통해 고지하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="n"/>
+      <c r="H155" s="8" t="n"/>
+      <c r="I155" s="5" t="n"/>
+      <c r="J155" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|119|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제22조 개인정보 보호 자율적 활동 및 인증 현황</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>조 제목</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="n"/>
+      <c r="F156" s="10" t="inlineStr">
+        <is>
+          <t>제22조 (개인정보 보호 자율적 활동 및 인증 현황)</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="n"/>
+      <c r="H156" s="8" t="n"/>
+      <c r="I156" s="5" t="n"/>
+      <c r="J156" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|120|h</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제22조 개인정보 보호 자율적 활동 및 인증 현황</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="n"/>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>1. 회사는 현재 ISMS-P 등 별도의 외부 개인정보 보호 인증을 보유하고 있지 않습니다.</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="n"/>
+      <c r="H157" s="8" t="n"/>
+      <c r="I157" s="5" t="n"/>
+      <c r="J157" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|121|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제22조 개인정보 보호 자율적 활동 및 인증 현황</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="n"/>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>2. 회사는 외부 인증 미보유와 관계없이 이용자의 개인정보를 안전하게 보호하기 위하여 내부 보안성 검토, 주기적인 기술적 보안점검 및 자율적 개인정보 보호 강화 활동을 지속적으로 수행하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="G158" s="7" t="n"/>
+      <c r="H158" s="8" t="n"/>
+      <c r="I158" s="5" t="n"/>
+      <c r="J158" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|122|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제23조 개인정보 처리방침의 변경 및 이전 버전 관리</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>조 제목</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="n"/>
+      <c r="F159" s="10" t="inlineStr">
+        <is>
+          <t>제23조 (개인정보 처리방침의 변경 및 이전 버전 관리)</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="n"/>
+      <c r="H159" s="8" t="n"/>
+      <c r="I159" s="5" t="n"/>
+      <c r="J159" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|123|h</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제23조 개인정보 처리방침의 변경 및 이전 버전 관리</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="n"/>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>1. 이 개인정보 처리방침은 2026년 10월 12일부터 적용됩니다.</t>
+        </is>
+      </c>
+      <c r="G160" s="7" t="n"/>
+      <c r="H160" s="8" t="n"/>
+      <c r="I160" s="5" t="n"/>
+      <c r="J160" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|124|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 · 제23조 개인정보 처리방침의 변경 및 이전 버전 관리</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="n"/>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>2. 회사가 개인정보 처리방침을 개정하는 경우 개정 최소 7일 전부터 공지사항을 통해 고지하며, 정보주체의 권리에 중대한 영향을 미치는 변경이 있는 경우 개정 전·후 비교표를 작성하여 별도로 안내합니다.</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="n"/>
+      <c r="H161" s="8" t="n"/>
+      <c r="I161" s="5" t="n"/>
+      <c r="J161" s="9" t="inlineStr">
+        <is>
+          <t>policy|privacy|125|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>이메일무단수집거부</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="n"/>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>㈜에이프로는 본 홈페이지에 게시된 이메일 주소가 전자우편 수집 프로그램이나 그 밖의 기술적 장치를 이용하여 무단으로 수집되는 것을 거부합니다.</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="n"/>
+      <c r="H162" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Co., Ltd. rejects the unauthorized collection of email addresses posted on this website through the use of automated email collection programs or other technical devices. Please be advised that any violation of this policy may result in criminal punishment under the "Act on Promotion of Information and Communications Network Utilization and Information Protection, etc."</t>
+        </is>
+      </c>
+      <c r="I162" s="5" t="n"/>
+      <c r="J162" s="9" t="inlineStr">
+        <is>
+          <t>policy|email|0|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>이메일무단수집거부</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="n"/>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>이를 위반할 시 「정보통신망 이용촉진 및 정보보호 등에 관한 법률」에 의해 형사 처벌될 수 있음을 유념하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="n"/>
+      <c r="H163" s="8" t="n"/>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
+          <t>영문은 위 줄에 합쳐져 있음</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="inlineStr">
+        <is>
+          <t>policy|email|1|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>이메일무단수집거부</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>소제목</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="n"/>
+      <c r="F164" s="6" t="inlineStr">
+        <is>
+          <t>[관련 법령: 정보통신망 이용촉진 및 정보보호 등에 관한 법률]</t>
+        </is>
+      </c>
+      <c r="G164" s="7" t="n"/>
+      <c r="H164" s="8" t="inlineStr">
+        <is>
+          <t>[Relevant Law: Act on Promotion of Information and Communications Network Utilization and Information Protection, etc.]</t>
+        </is>
+      </c>
+      <c r="I164" s="5" t="n"/>
+      <c r="J164" s="9" t="inlineStr">
+        <is>
+          <t>policy|email|2|s</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>이메일무단수집거부</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>소제목</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="n"/>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>제50조의 2 (전자우편주소의 무단 수집행위 등 금지)</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="n"/>
+      <c r="H165" s="8" t="inlineStr">
+        <is>
+          <t>Article 50-2 (Prohibition of Unauthorized Collection of E-mail Addresses, etc.)</t>
+        </is>
+      </c>
+      <c r="I165" s="5" t="n"/>
+      <c r="J165" s="9" t="inlineStr">
+        <is>
+          <t>policy|email|3|s</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>이메일무단수집거부</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="n"/>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>누구든지 전자우편주소의 수집을 거부하는 의사가 명시된 인터넷 홈페이지에서 자동으로 전자우편주소를 수집하는 프로그램 그 밖의 기술적 장치를 이용하여 전자우편주소를 수집하여서는 아니 된다.</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="n"/>
+      <c r="H166" s="8" t="inlineStr">
+        <is>
+          <t>No person shall collect e-mail addresses from an Internet website where the intention to refuse the collection of e-mail addresses is manifested, by using a program or other technical device that automatically collects e-mail addresses.</t>
+        </is>
+      </c>
+      <c r="I166" s="5" t="n"/>
+      <c r="J166" s="9" t="inlineStr">
+        <is>
+          <t>policy|email|4|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>이메일무단수집거부</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="n"/>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t>누구든지 제1항의 규정을 위반하여 수집된 전자우편주소를 판매·유통하여서는 아니 된다.</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="n"/>
+      <c r="H167" s="8" t="inlineStr">
+        <is>
+          <t>No person shall sell or distribute e-mail addresses collected in violation of Paragraph 1.</t>
+        </is>
+      </c>
+      <c r="I167" s="5" t="n"/>
+      <c r="J167" s="9" t="inlineStr">
+        <is>
+          <t>policy|email|5|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>이메일무단수집거부</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="n"/>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>누구든지 제1항 및 제2항의 규정에 의하여 수집·판매 및 유통이 금지된 전자우편주소임을 알고 이를 정보전송에 이용하여서는 아니 된다.</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="n"/>
+      <c r="H168" s="8" t="inlineStr">
+        <is>
+          <t>No person shall use e-mail addresses for transmitting information, knowing that such e-mail addresses are those whose collection, sale, or distribution is prohibited under Paragraphs 1 and 2.</t>
+        </is>
+      </c>
+      <c r="I168" s="5" t="n"/>
+      <c r="J168" s="9" t="inlineStr">
+        <is>
+          <t>policy|email|6|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>이메일무단수집거부</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="n"/>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>제74조 (벌칙)</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="n"/>
+      <c r="H169" s="8" t="inlineStr">
+        <is>
+          <t>Article 74 (Penal Provisions)</t>
+        </is>
+      </c>
+      <c r="I169" s="5" t="n"/>
+      <c r="J169" s="9" t="inlineStr">
+        <is>
+          <t>policy|email|7|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>이메일무단수집거부</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="n"/>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>다음 각호의 어느 하나에 해당하는 자는 1년 이하의 징역 또는 1천만 원 이하의 벌금에 처한다.</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="n"/>
+      <c r="H170" s="8" t="inlineStr">
+        <is>
+          <t>Any person who falls under any of the following shall be punished by imprisonment with labor for not more than one year or by a fine not exceeding 10 million won:</t>
+        </is>
+      </c>
+      <c r="I170" s="5" t="n"/>
+      <c r="J170" s="9" t="inlineStr">
+        <is>
+          <t>policy|email|8|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>이메일무단수집거부</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="n"/>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>제50조의 2의 규정을 위반하여 전자우편 주소를 수집·판매·유통하거나 정보 전송에 이용한 자</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="n"/>
+      <c r="H171" s="8" t="inlineStr">
+        <is>
+          <t>A person who collects, sells, distributes, or uses e-mail addresses for information transmission in violation of Article 50-2.</t>
+        </is>
+      </c>
+      <c r="I171" s="5" t="n"/>
+      <c r="J171" s="9" t="inlineStr">
+        <is>
+          <t>policy|email|9|p</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>이메일무단수집거부</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="n"/>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>게시일: 2025년 12월 23일</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="n"/>
+      <c r="H172" s="8" t="inlineStr">
+        <is>
+          <t>Date of Publication: December 23, 2025</t>
+        </is>
+      </c>
+      <c r="I172" s="5" t="n"/>
+      <c r="J172" s="9" t="inlineStr">
         <is>
           <t>policy|email|10|p</t>
         </is>

--- a/content-export/국문영문글정리.xlsx
+++ b/content-export/국문영문글정리.xlsx
@@ -45822,29 +45822,29 @@
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>알림 메시지</t>
+          <t>문의 폼</t>
         </is>
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>실패 — 자동등록방지 안 함</t>
+          <t>입력칸 안내 — 숫자 그림 읽어 주기(aria-label)</t>
         </is>
       </c>
       <c r="D53" s="21" t="inlineStr">
         <is>
-          <t>알림</t>
+          <t>숨김글</t>
         </is>
       </c>
       <c r="E53" s="21" t="n"/>
       <c r="F53" s="22" t="inlineStr">
         <is>
-          <t>자동등록방지 확인을 마친 뒤 다시 눌러 주세요.</t>
+          <t>자동등록방지 숫자 그림</t>
         </is>
       </c>
       <c r="G53" s="23" t="n"/>
       <c r="H53" s="24" t="inlineStr">
         <is>
-          <t>Please complete the CAPTCHA check and try again.</t>
+          <t>CAPTCHA image</t>
         </is>
       </c>
       <c r="I53" s="22" t="inlineStr">

--- a/content-export/국문영문글정리.xlsx
+++ b/content-export/국문영문글정리.xlsx
@@ -44957,15 +44957,19 @@
           <t>IR</t>
         </is>
       </c>
-      <c r="G29" s="23" t="n"/>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>IR / PR</t>
+        </is>
+      </c>
       <c r="H29" s="24" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>IR / PR</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
         <is>
-          <t>값: ir — 이 값으로 수신 메일이 갈립니다('메일 발송' 시트 참고)</t>
+          <t>2026-10-23 변경 — 관리자 화면 'IR/PR' · 문의처 카드 'IR / PR' 과 맞춤 (값: ir 그대로)</t>
         </is>
       </c>
       <c r="J29" s="25" t="n"/>
@@ -45443,15 +45447,19 @@
           <t>문의가 접수되었습니다. 담당자가 확인 후 sales@aproele.com으로 답변 드리겠습니다.</t>
         </is>
       </c>
-      <c r="G42" s="23" t="n"/>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>문의가 접수되었습니다. 담당자가 확인 후 답변 드리겠습니다.</t>
+        </is>
+      </c>
       <c r="H42" s="24" t="inlineStr">
         <is>
-          <t>Your inquiry has been received. Our representative will review it and respond to sales@aproele.com.</t>
+          <t>Your inquiry has been received. Our representative will review it and respond.</t>
         </is>
       </c>
       <c r="I42" s="22" t="inlineStr">
         <is>
-          <t>문장 안에 sales@aproele.com 이 박혀 있음 — 결정된 수신 메일과 같으므로 그대로 쓰면 됩니다. 나중에 수신 메일을 바꾸면 이 문구도 함께 고쳐야 합니다</t>
+          <t>2026-10-23 변경 — 받는 주소는 관리자 설정을 따르므로 문구에서 주소를 뺌</t>
         </is>
       </c>
       <c r="J42" s="25" t="n"/>
